--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人生年表'!$A$1:$L$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'デビューの経緯'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'傷・タトゥー'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'影響'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'影響'!$A$1:$J$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'歌の種'!$A$1:$I$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'歌詞の試作'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'近況'!$A$1:$F$16</definedName>
@@ -638,6 +638,26 @@
         <t>どの組のメンバーか（アーティストのタブの ID）</t>
       </text>
     </comment>
+    <comment ref="A33" authorId="0" shapeId="0">
+      <text>
+        <t>デビューまでに働いてきた仕事。時期・場所・仕事の中身・そこで覚えたこと</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0">
+      <text>
+        <t>実際の機種名を書いてよい（例 1982 年製のポリシンセ）。作曲の指示文には機種名は渡さない</t>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0">
+      <text>
+        <t>弾き方・叩き方・歌い方の具体的な癖（右手のミュート、ゴーストノート など）</t>
+      </text>
+    </comment>
+    <comment ref="A45" authorId="0" shapeId="0">
+      <text>
+        <t>実在のアーティスト名を書いてよい欄（作曲の指示文には渡さない）</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -663,6 +683,21 @@
     <author>EtherArchi</author>
   </authors>
   <commentList>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>その影響が今の音のどこに出ているか。声・演奏・曲の形・見た目など</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>EtherArchi</author>
+  </authors>
+  <commentList>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>○ を付けると、まだ歌にしていない新しい出来事から順に、毎週の曲のテーマになる</t>
@@ -672,7 +707,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>EtherArchi</author>
@@ -692,7 +727,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>EtherArchi</author>
@@ -727,7 +762,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>EtherArchi</author>
@@ -1170,7 +1205,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>1 列 = 1 人。年齢・見た目・性格・話し方・家族・好き嫌い（縦型）</t>
+          <t>1 列 = 1 人。年齢・見た目・性格・話し方・家族・仕事・楽器と演奏・好き嫌い（縦型）</t>
         </is>
       </c>
       <c r="D15" s="13">
@@ -4611,22 +4646,22 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>温かいアナログ・ポリシンセのパッド、交互 16 分のアルペジオシンセ、ゲートリバーブのスネア、丸く太いシンセベース、薄いテープヒスとワウ・フラッター、遠くで鳴るコーラスのかかったクリーンギター 1 本、ラジオのチューニングノイズ</t>
+          <t>温かいアナログ・ポリシンセのパッド（遅い立ち上がりとゆるいコーラスの揺れ）、交互 16 分のアルペジオシンセ、1980 年代のドラムマシンのスネアにゲートリバーブ、丸く太いシンセベース、細く少し硬い 80 年代の安価なポリシンセのベル音（サビの対旋律）、薄いテープヒスとワウ・フラッター、遠くで鳴るコーラスのかかったクリーンギター 1 本、ラジオのチューニングノイズ</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>シングルコイルのエレキギターのクリーンなカッティング、指弾きのエレキベース（フラットワウンド弦の丸い音）、生ドラム（締まったスネアと 16 分のハイハット）、柔らかい鐘のようなエレクトリックピアノ（薄く）、12 弦アコースティックギター（サビの裏で薄く）、タンバリンとシェイカー</t>
+          <t>シングルコイルのエレキギターのクリーンなカッティング（薄いコーラスで少し揺らす）、指弾きのエレキベース（フラットワウンド弦の丸く短い音・ブリッジ側のミュート）、1970 年代のドラムキットと木胴の乾いたスネア（16 分のハイハットと A メロのクロススティック）、柔らかい鐘のようなエレクトリックピアノ（薄く）、1970 年前後の 12 弦アコースティックギター（サビの裏で薄く）、タンバリンとシェイカー</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>指弾きのスチール弦アコースティックギター（小ぶりのパーラー型）、足踏みハーモニウムの持続音、アップライトベース、ブラシのスネアとフロアタム、マンドリンの細い刻み、チェロ 1 本の長い音、雨と木の軋みのフィールド録音（薄く）</t>
+          <t>指弾きのスチール弦アコースティックギター（変則チューニングで開放弦を鳴らし続ける・親指の低音）、小ぶりのマホガニーのギターのやわらかいストローク、足踏みリードオルガンの持続音（5 度のドローン）、アップライトベース、ブラシのスネアとフロアタム、マンドリンの細い刻みと 3 度の重音、チェロ 1 本の長い音、雨と木の軋みのフィールド録音（薄く）</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>柔らかい四つ打ちキック、ローズ系のエレピ（9th と 11th のコード）、息と声の切れ端（ピッチ変化つき）、丸いサブベース、テープの揺れとかすかなレコードノイズ、工房の実音（カッター・定規・紙やすり・レーザーカッターの換気扇）、ハイライフ風のクリーンギター（2 音のリフだけ）、16 分で揺れ続けるシェイカーとリムショット</t>
+          <t>柔らかい四つ打ちキック、1970 年代のエレクトリックピアノ（9th と 11th のコード・弱めの打鍵）、息と声の切れ端（ピッチ変化つき）、丸いサブベース、テープの揺れとかすかなレコードノイズ、工房の実音（カッター・定規・紙やすり・レーザーカッターの換気扇）、フラット弦のこもったクリーンギター（ハイライフ風の 2 音のリフだけ）、16 分で揺れ続けるシェイカーとリムショット</t>
         </is>
       </c>
     </row>
@@ -6582,27 +6617,27 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7226,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>DECLAN MOTH is Declan Twomey, a Cork-born baritone who has spent ten years working nights in Toronto — first driving a bakery van at 2 a.m., now running the overnight desk at a small community radio station. As a boy who wouldn't sleep, he rode along on his grandfather's late drives around Cork's ring road, a box of cassettes taped off late-night radio at his feet; when his grandfather died, those 43 tapes crossed the Atlantic in a shoebox, and their hiss is still in every mix. His songs are slow, warm synthwave for the stretch between last call and first light: analog pads, a gated snare, a voice that sounds like it's riding in the passenger seat, and always a time on the clock. Put it on when you're driving home and everyone else is asleep.</t>
+          <t>DECLAN MOTH is Declan Twomey, a Cork-born baritone who has spent ten years working nights in Toronto — first driving a newspaper delivery van at 2 a.m., now running the overnight desk at a small community radio station. As a boy who wouldn't sleep, he rode along on his grandfather's late drives around Cork's ring road, a box of cassettes taped off late-night radio at his feet; when his grandfather died, those 43 tapes crossed the Atlantic in a shoebox, and their hiss is still in every mix. His songs are slow, warm synthwave for the stretch between last call and first light: analog pads, a gated snare, a voice that sounds like it's riding in the passenger seat, and always a time on the clock. Put it on when you're driving home and everyone else is asleep.</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -7295,7 +7330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8561,7 +8596,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>■ 好きなもの</t>
+          <t>■ 仕事</t>
         </is>
       </c>
       <c r="B32" s="29" t="n"/>
@@ -8576,451 +8611,1045 @@
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>好きなこと</t>
+          <t>デビューまでの仕事・アルバイト</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>日の出の 10 分前の空、夜明け前の空いたガソリンスタンド、魔法瓶のココア、道路標識の書体</t>
+          <t>15 歳の夏（2017 年）は高校の同級生 Callie の家の果樹園で 1 週間だけ梨の収穫を手伝い、脚立の上で夜明けの冷たさと手の皮の硬さを覚えた。16 歳（2018 年）からはフッドリバーのダウンタウンのパン屋で週末の朝 5 時から 11 時まで働き、時給は 11 ドル弱で、店主夫婦から生地の発酵を時計ではなく指で確かめることを教わった。高校を出た 2020 年から 2022 年 3 月までは同じ店で朝 4 時半からの仕込みを週 5 日（時給 13 ドル前後）こなし、オンラインの授業は午後に回した。2021 年 1 月に天板で左手の甲を火傷してからは、熱い物を持つ前に必ず声に出して確認する癖がついた。2022 年 4 月から翌年 2 月は函館の朝市で祖母が長く勤めた乾物屋の店番を朝 5 時から昼まで週 6 日（時給 900 円ほど）務め、スルメや昆布の量り売りと観光客への英語の案内を受け持った。そこで、決まった時間に店を開けること自体が誰かへの約束になると知った。</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>夜の空いた高速、カセットのラベルを手書きすること、雨上がりのオレンジの街灯、パン屋の一番窯の匂い</t>
+          <t>15 歳の夏（2008 年）、メイフィールドの近所の青果店で自転車の配達をした。時給 6 ユーロほどで、土曜の朝 7 時から箱を坂の上の家々へ運び、重い箱ほど先に下ろす段取りを覚えた。工科カレッジ時代（2011〜2015 年）は週末に市内のパブで演奏の音響を手伝い、1 晩 50 ユーロで朝の 2 時までケーブルを巻き、夜は地元のコミュニティラジオで深夜の送出番を無給で務めた。卒業後の 2015〜2016 年はリトル・アイランドの物流倉庫で 22 時から朝 6 時までの夜勤のピッキングを続け、時給 10 ユーロ少しの仕事で夜の体の使い方を覚えた。2016 年秋にトロントへ渡ってからは朝刊の配送バンの運転手になり、午前 1 時に印刷所で積み込んで 6 時までに西側の売店やガソリンスタンドやレイクショア沿いのカフェに配った（1 晩いくらの請負で、凍った冬の朝は手袋の中で指が動かなかった）。配達表に毎晩の到着時刻を書き込む習慣がそのまま『夜の日誌』になり、2018 年夏にハーバーライト FM の夜勤の技術担当に移った。</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>ガソリンスタンドのホットパイ、空港線の高架を昼に下から見上げること、いとこの結婚式のカラオケ、0.3 mm のシャープペン</t>
+          <t>2015〜2016 年（17〜18 歳）は Sunshine のガソリンスタンドで土曜の朝 6 時から 6 時間のレジ番をし、未成年の時給は 13 ドルほどだった。パイの保温器の補充をしながら、トラックの運転手が毎週同じ時間に同じものを買っていくことを覚えた。2018〜2019 年は西部のショッピングセンターの楽器店で週末だけ働き（時給 23 ドル）、弦の張り替えと試奏の客の相手をしながら、ギターごとの鳴りの違いを毎日聴き比べた。2022〜2023 年は中心街の大手設計事務所の新卒の設計者として、ショッピングセンターの改修と立体駐車場の図面を週 55 時間描き、残業代の出ない月給の重さと、スロープの勾配や床のレベルの数字を体で覚えた。2024 年 3 月に辞めて半年ほど休んだあと、10 月にタヴの親方の紹介で小さな工務店の増築のパースを 1 枚描いたのが、今のフリーランスの始まりになった。</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>方眼ノート、他人の家の台所、0.5 mm の芯で引く細い線、長距離バスの窓際の席</t>
+          <t>2014〜2016 年の高校時代は、土曜の朝にサンパウロの父の勤める日系スーパーの総菜売り場で、パック詰めと値札貼りを手伝った（時給は当時の最低賃金ほど）。メルボルンの 1 年目の 2017 年は父の貯金の学費に頼りながら、週末だけ大学の図書館で返却本の棚戻しをした。2018〜2021 年は Carlton のラーメン店で留学生の上限の週 20 時間、厨房の盛り付けとホールを担当し（時給 24 ドルほど）、伝票が鳴る間隔と店員同士の掛け声の掛け合いを覚えた。ロックダウン中の 2020〜2021 年は店が持ち帰りだけになって勤務が週 8 時間に減り、構造の講師の研究で古い社会住宅の図面を CAD で描き起こす仕事を在宅で請けた。2022 年に修士を出て、Collingwood の中規模の設計事務所に入った。</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>朝 6 時の現場の静けさ、切ったばかりの木材の匂い、父とラグビーを見ること、ドラムのチューニング</t>
+          <t>8 歳から Napier の父の現場で週末に釘拾いと掃除をし、小遣いは 1 日 10 ドルだった。2012〜2016 年は Frankston で週末に父の現場を手伝い、15 歳からは手元として現金で時給 15 ドルほどもらって、木材を運ぶ順番と現場の段取りを覚えた。2017〜2021 年の大学時代は学費の一部を払うため土曜と長期休みに住宅の現場で働き（時給 25 ドル前後）、2021 年に父が腰を痛めると、週末に父の顧客のデッキや戸の仕事を代わりに仕上げた。2022〜2024 年は湾岸の住宅地を回る小さな工務店の大人向けの見習い大工として、Coburg から車で通って朝 7 時から 15 時半まで現場に出て、週 1 日は北部の職業訓練校に通った。給料は同級生の半分以下だったが、2024 年に資格を取るまでに、墨出しと水平と垂直の確かめ方を体に入れた。</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>羊毛の脂（ラノリン）の匂い、雨の日の窓辺で編むこと、砂利道を走るタイヤの音、市場が終わったあとの片付け</t>
+          <t>寄宿学校の休みには実家の牧場で子羊の断尾や囲いの掃除を手伝い、給金の代わりに毛刈りの季節の小遣いを父からもらっていた。2013〜2016 年の大学の夏休みは毛刈り隊のルーシー（下働き）として 12 週間南島の牧場を回り、朝 7 時から夕方 5 時まで 2 時間ずつ 4 区切り（ランと呼ぶ）の作業で、床の羊毛を集めて台に広げ、汚れを除いて等級ごとに分けることを覚えた。2017 年はロンドン・ハックニーのパブの厨房で半年、時給 7 ポンドほどで皿洗いと仕込みをし、閉店後の深夜 1 時まで立ち続ける体力と、急かされても手順を崩さないことを身につけた。2018 年 5 月からはペンリンの毛糸店で週 5 日、店の 2 階に住み込みで働き、コーンウォールの漁師の家に伝わるガンジーの編み目の図案を店主から教わった。2019〜2021 年はオタゴの実家で牧場を手伝いながら地域の手芸店で週 3 日働き、2021 年 9 月にペンリンの毛糸店へ戻ったあと、2022 年に独立した。</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>朝の満ち潮の音、鉋屑の匂い、ギグ漕ぎの掛け声、雨の日のボートヤードのラジオ</t>
+          <t>5 歳から父の作業場で鉋屑を掃く係をし、10 代の夏休みには幼なじみの家のロブスター漁の小舟で籠に餌を詰める手伝いをして、1 日 20 ポンドほどをもらった。2008 年に学校を出て父の作業場の見習いになり、朝 7 時半から夕方まで板を削り、継ぎ目に麻と油を詰める古い船の直し方を覚えたが、2009 年の不況で注文が半分になった。2010〜2012 年はファルマスの専門学校で舟艇づくりを学びながら、週末はファルマスのパブでグラス集めのアルバイトをした。2012 年からペンリン川沿いのボートヤードで週 5 日、朝 7 時半から午後 4 時まで、楡の板で 6 人漕ぎのギグを新造・修理し、肋材を蒸気で曲げる段取りと、潮の時刻に合わせて船を出し入れする暮らしを身につけた。2020 年春からの一時帰休の間は、借りた納屋で 1 人で小さな手漕ぎ船を作って過ごした。</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>夜行バスの最前列の左の席、カッターの刃を替える瞬間、中庭のある建物の平面図を眺めること、誰もいない日曜の朝の工房</t>
+          <t>16 歳になった 2013 年から、ラウンドヘイの近所のスーパーで土曜の朝 7 時からの品出しをした。時給は 4 ポンドに届かず、棚の列を端からそろえる単調さが嫌いではなかった。大学の 2〜3 年（2016〜2018 年）は学期中の週 2 晩、学部のレーザーカッター室で受付と切断データの確認をし、夏休みはリーズの父の病院の薬剤部で在庫の段ボールを開けてラベルを貼る短期の仕事をした。2018〜2019 年はクラーケンウェルの設計事務所で Part I の実務研修生として働き、年収は 2 万ポンド強。締め切り前は地下の模型室で終電を逃し、1:500 のボリューム模型を一晩で 3 案作る速さを覚えた。2019 年 7 月からはハックニー・ウィックの工房の見習い（日給 90 ポンドから）で、2020 年のロックダウン中は一時帰休で給料の 8 割を受け取りながら夜に曲を作り、2021 年の再開後は集合住宅や設計競技の模型を担当してきた。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>好きな言葉</t>
+          <t>今の仕事と働き方</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>first light、したっけ、clear and dry（父の無線の路面状況）、おはよう</t>
+          <t>2023 年 3 月から工業地区の卸のベーカリーで配送ドライバーをしていて、月曜から金曜の週 5 日・午前 3 時半に積み込みを始め、市内 20 軒のカフェを回って朝 8 時半〜9 時に戻る（時給 21 ドル）。職場はオーブンの熱と粉の匂いでいつも暖かく、主任パン職人の Marisol たちとはスペイン語と英語の混ざった短いあいさつだけで動く。2026 年 10 月からバンが静かな電気の新車になり、ルート中は鼻歌をスマートフォンの音声メモに吹き込んでいる。昼に 2 時間眠って午後 1 時から 4 時を作曲に当て、レーベルとの打ち合わせは配送明けの朝 9 時だけにしている。</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>grand（上等・大丈夫）、the small hours（夜更けの数時間）、go easy（無理するなよ）</t>
+          <t>ハーバーライト FM の夜勤の技術担当として、火曜から金曜の週 4 日、19 時から翌 3 時まで送出室に座る。送信機の遠隔監視・自動送出の切り替え・無音の警報への対応・機器の修理が仕事で、木曜の深夜 2 時からは自分の番組『Moth Hours』を生で出す。自動送出に任せられる 0 時から 2 時のあいだに局の古い制作室でスケッチを録り、休憩には『夜の日誌』の 1 行を直す。日曜と月曜は休みで、昼過ぎに起きてから夕方までの 3 時間を自宅の窓際の机での曲作りに充てている。</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>load path（力の流れ）、Sige、halfway、good enough</t>
+          <t>Footscray の自分の部屋で、小さな工務店向けの増築や住宅の 3D パースを月・火・水・金の 9 時〜17 時に作る。1 枚 400〜900 ドルで、月の稼ぎには波がある。木曜は 15 時半〜18 時に Footscray の地域センターで 8〜12 歳の子どもギター教室を 2 クラス持つ。リハは火曜の夜と土曜の昼で、毎朝 9 時前の 30 分を鼻歌のボイスメモと歌詞の 1 行に使い、パースの書き出しを待つ間にギターを弾く。</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>habitável（住める）、やらまいか、span（スパン）、saudade</t>
+          <t>Collingwood の中規模の設計事務所で、木造の中層の社会住宅の住戸の平面と、車いすで使える台所や浴室の詳細を担当している。月曜〜木曜の 8 時半〜18 時の 4 日勤務で、Brunswick から自転車で 25 分。火曜はリハのため 17 時半に事務所を出る。金曜はバンドの日と決めて、午前に次の曲の断面図を描き、午後は録音の整理と配信の事務をする。</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Sweet as、plumb（垂直）、Faʻafetai、load-bearing（荷重を受ける）</t>
+          <t>見習いを終えたあとも同じ親方の工務店に残り、湾岸の住宅地でデッキと増築を担当している。月曜〜金曜の 7 時〜15 時半で、渋滞を避けて Coburg を朝 6 時前に出て、6 時半には静かな現場に着く。土曜の昼のリハのため土曜の現場は断り、火曜は 18 時半に工具をバンに積んだまま工場へ直行する。昼休みの 15 分はバンの運転席で練習パッドを叩く。</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>mend（繕う）、fleece（ひと刈り分の羊毛）、cast on（編み始める）、southerly（南風）</t>
+          <t>ガンジーの受注製作と草木染めの毛糸の販売で暮らし、今は 4 着の注文を抱えている（1 着に 6〜7 週間かかる）。平日は朝 8 時から昼まで台所で毛糸を染めて発送し、ゲシンがボートヤードに出ない木曜と金曜の午後は網小屋で録音する。毎晩 8 時から 10 時まで暖炉の前で編み、週 1 回はそれをそのまま配信にしている。土曜は朝 6 時半にトゥルーロへ出て屋台を立て、昼過ぎまで売りながら合間に 2 人で歌う。</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>hiraeth（ウェールズ語で帰れない場所への想い）、cwtch（ウェールズ語で抱きしめること・安心できる場所）、fair wind（順風）</t>
+          <t>2025 年からボートヤードの勤務は月曜〜水曜の週 3 日で、朝 7 時半から午後 4 時まで、主にギグと古い木の船の修理を受け持つ。木曜と金曜は午前に個人から頼まれた小さな修理や端材の小物づくりをし、午後は網小屋でアイラと録音する。土曜はアイラの屋台の横でギターを弾き、日曜の朝はギグ漕ぎクラブの練習でペンリン川を漕ぐ。月に 1 度は 5 時間半かけてソルヴァへ帰り、父と作業場を片付ける。</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>hollow、headroom（余裕・天井の高さ）、Ɛyɛ（大丈夫・いいね〔トウィ語〕）、plan view（真上から見た図）</t>
+          <t>ハックニー・ウィックの運河沿いの模型工房で、月曜から金曜の週 5 日、9 時半から 18 時まで働く。いまは集合住宅の 1:200 の模型の主担当で、職人 6 人がレーザーカッターの換気扇の音の中で黙々と手を動かしている。定時のあと 21 時半まで残り、人が帰った作業場で実音を録ったり自分用の部屋の模型を作ったりしてから、自転車で 15 分のレイトンの屋根裏へ 22 時に戻り、2 時まで曲を作る。レーベルの昼の打ち合わせは月 1 回だけ半休を取り、締め切り前の土曜出勤の週は夜行バスの車内を制作の時間に充てる。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>好きな色</t>
+          <t>仕事が音楽にくれたもの</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>夜明け前の群青、除雪車のアンバー、梨の花の白</t>
+          <t>配送ラックを並べるときの車輪の一定の刻みと、20 軒をほぼ同じ間隔で回るルートの周期が、曲の背骨にしている 8 分のアルペジオとまっすぐな 8 ビートの感覚になった。ルート表の時刻・通りの名前・合鍵の数のように、気持ちより物と数字で書く歌詞の癖も仕事から来ている。テンポを決めるときは、84 号線を東へ走りながら窓の外のマイル標識が流れる速さに合わせる。</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>ナトリウム灯のオレンジ、瓶の深い緑、夜明け前の紺</t>
+          <t>送出の仕事で一番恐れるのは無音で、曲が急に途切れない作り方と、どの曲にも薄い地のノイズを敷く癖はここから来ている。配達表と放送日誌に時刻を書き続けた 10 年が、毎曲に 1 つ時刻を入れる歌詞と、イントロで時刻と場所を言う語りになった。午前 3 時の高速の継ぎ目が一定の間隔で鳴る音が、テンポを 92〜104 に保つ体の物差しになっている。</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>道路標識の緑、ガムテープの銀、色あせたオレンジ</t>
+          <t>パースの書き出しを待つ 20〜40 分が、鼻歌のメロディがいちばん生まれる時間になった。子どもの教室で 3 つのコードと手拍子だけで 1 曲を教えるうちに、カッティングを少ない音に削る癖がついた。立体駐車場の図面で覚えた kerb・ramp・level のような言葉と、ガソリンスタンドのレシートの裏に書く習慣が、歌詞の具体語の元になっている。</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>テラコッタ、浜松の団地の階段の水色、ユーカリの灰緑</t>
+          <t>同じ住戸のプランを階ごとに少しずつ変えて積む社会住宅の設計が、2 番で 1 小節だけ変える曲の組み立て方になった。台所に車いすが回れる 1.5 m の円を必ず描くように、ベースラインにも歌のための空きを必ず残す。ラーメン店の厨房の掛け声の掛け合いが、ハモりで短い 1 行を返す感覚のもとになっている。</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>未塗装のユーカリ材の赤茶、曇りの日のネイピアの海の灰青、安全ベストのオレンジ</t>
+          <t>釘打ちとビス留めの一定の間隔が、16 分を急がずに刻む体の時計になった。2 回測ってから切る現場の習慣が、テンポを決める前に必ずメトロノームで 2 回確かめるやり方につながっている。デッキの板の間に 5 mm の隙間を残すように、音と音の間にも隙間を残す。</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>生成り（未染色の羊毛）、ハリエニシダの黄、濡れたスレートの青灰</t>
+          <t>毛刈り小屋の 2 時間ずつの区切りと編み目を数える習慣から、小節を数えなくても体で曲の長さを測れる。編み針が 1 目ずつ目を移す手の拍はワイパーの往復とほぼ同じ速さで、2 人の曲の 84〜98 BPM の揺れの基準になっている。歌詞の言葉は、毛糸のラベル・染めの材料・編み目の名前（鹿の子・はしご・縄編み）など、仕事の手元から拾われる。</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>タールの黒、ペンキの剥げた船の緑、霧の朝の白</t>
+          <t>鉋を引く長い 1 拍と戻す短い 1 拍が、親指で低音弦を弾く指弾きの型の元になった。ギグを漕ぐ掛け声の『引いて・戻して』を 2 拍で数える癖から、8 分音符が少しだけ跳ねる揺れが生まれた。接着剤が乾くのを待ち、潮が満ちるのを待つ時間感覚が、間奏を急いで埋めない余白になっている。</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>バルサ材の生成り、古い高速の街灯の琥珀色、ケンテ布の深い緑</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>好きな食べ物</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>祖母のイカめし、マリオンベリーのパイ、父が焼く分厚いハッシュブラウン、函館の塩ラーメン</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>コークのスパイス・ビーフ（クリスマスの塩漬け牛）、母のブラウンブレッド、イネスの店のエッグタルト、深夜営業の中華料理店の炒飯</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>母のシニガン（タマリンドの酸っぱいスープ）、サービスエリアのミートパイ、ハロハロ、Footscray のバインミー</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>ポン・デ・ケージョ、母のブラジル風ヤキソバ（とろみのある餡かけ）、浜松の餃子、フェイジョアーダ</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>おばのパルサミ（タロの葉のココナッツクリーム包み）、新聞紙に包んだフィッシュ＆チップス、ホーキーポーキー（ハニカムトフィー入りのアイス）、ミートパイ</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>母のやり方のラム肉のロースト、ホーキーポーキー味のアイスクリーム、祖母のオランダ風パンケーキ、コーンウォールのサフランパン</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>母のカウル（羊と根菜のウェールズのスープ）、ウェルシュケーキ、焼いた鯖、ラバーブレッド（海藻のペースト）</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>母のライトスープとフフ、ケレウェレ（香辛料で揚げたプランテン）、日曜のローストとヨークシャー・プディング、サービスエリアのミルク多めの紅茶</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>■ 嫌いなもの</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="29" t="n"/>
-      <c r="E37" s="29" t="n"/>
-      <c r="F37" s="29" t="n"/>
-      <c r="G37" s="29" t="n"/>
-      <c r="H37" s="29" t="n"/>
-      <c r="I37" s="29" t="n"/>
+          <t>カッターの刃がグレーボードを抜ける乾いた音、鋼尺を作業台に置く音、紙やすりの 16 分の往復が、そのまま打楽器の音色とシェイカーの揺れになった。レーザーカッターの換気扇のうなりは曲の底に敷く低い持続音の手本で、縮尺を変えて同じ形を作り直す感覚が 16 小節単位で 1 つずつ足し引きする編曲になっている。アラスデアの『急ぐな』は、テンポを上げずに密度で頂点を作る癖として残っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>■ 楽器と演奏</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>使う楽器（メイン）</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Roland GAIA SH-01（2010 年発売の 37 鍵シンセ／13 歳の誕生日に父がフッドリバーの質屋で買ってきた中古）、KORG minilogue（2016 年発売の 37 鍵 4 音アナログシンセ／2024 年秋にポートランドの楽器店で中古を配送の給料を貯めて購入）、Squier Classic Vibe '50s Telecaster（2022 年に函館の楽器店で浩平に選んでもらった中古）</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>ローランド Juno-106（1985 年製・2019 年秋にクイーン・ストリートの中古楽器店で分割払いで購入／壊れていたボイスチップを局の先輩と交換した）、コルグ Poly-800（1980 年代半ば製・15 歳の夏に青果店の配達の貯金でコークの中古品店で買った最初の鍵盤）、ローランド TR-707（1980 年代半ば製・2020 年春にデニースの知人の物置から譲ってもらったドラムマシン）</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>1990 年代前半の日本製フェンダー・ストラトキャスター ST62 3 トーンサンバースト（2019 年に勤め先の楽器店で下取り品を社員割引で購入）、1970 年前後のヤマハ FG-230 赤ラベルの 12 弦アコースティック（2021 年のロックダウン中に個人売買で 450 ドル）、ヤマハ FG700S（2012 年に父が中古で買ってくれた最初のギター・今は教室用）</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>1983 年製のフェンダー・ジャパン プレシジョン・ベース PB62 JV シリアル（2019 年にメルボルンの中古楽器店でラーメン店の給料 2 か月分）、ブラジル製の Giannini のエレキベース（14 歳のときサンパウロの楽器店の店主から安く譲られた・メルボルンに持ってきた 1 本目）、短いスケールの Squier Bronco Bass（2023 年のロードトリップ用に中古で）</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>1978 年製のラディックのドラムキット 22・13・16 インチ（2019 年に Frankston の個人売買で父と見に行って 900 ドル）、自作のスポッテッドガム材の胴の 14×5.5 インチのスネア（2024 年に現場の余り材で組んだ）、パテ（サモアの木の割れ目太鼓・2018 年に Napier のおじから譲られた）</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>1950 年代製の Martin 0-15（オール・マホガニーの小型ギター／2018 年に毛糸店の店主から亡き夫の形見として譲られた）、Yamaha FG700S（2013 年にダニーデンの楽器店で中古で購入／毛刈り隊の旅とフラットのパーティに持ち歩いた）、Hohner Special 20 のハーモニカ（G と D の 2 本／父の車のダッシュボードに入っていたものをもらった）</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>1974 年製の Guild D-35（2013 年にファルマスの楽器店で中古で購入／ボートヤードの最初の夏の稼ぎで）、1980 年代製の中古の Yamaha FG シリーズ（2004 年・14 歳でハヴァフォードウェストの楽器店で 60 ポンドで購入／今は変則チューニング専用）、1910 年代の Estey 製の足踏みリードオルガン（ソルヴァ近くの閉じた礼拝堂から譲り受けて網小屋の 2 階に置く）、Eastman MD305 のマンドリン（2017 年にパブのセッションのフィドル弾きから中古で譲ってもらった）</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>1978 年製の Rhodes Mark I Stage 73（2025 年の屋根裏への引っ越しに合わせてウォルサムストウの個人売買で傷だらけのものを 900 ポンドで買い・アラスデアと 2 人で階段を担ぎ上げた）、Roland SP-404MKII（2022 年秋に初めてラジオのゲスト枠に呼ばれた記念に新品で購入・夜行バスの膝の上の相棒）、Novation Launchkey Mini MK3 と Ableton Live（2020 年の一時帰休中に給料の残りで揃えた・25 鍵で鞄に入る）、Zoom H5 フィールドレコーダー（2021 年に工房の実音を録るため中古で購入）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>嫌いなこと</t>
+          <t>ほかに弾ける楽器</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>夜 9 時以降の打ち合わせ、遅刻、霧が晴れない 3 月の朝、「で結局どっちの人なの？」と聞かれること</t>
+          <t>ヤマハのアップライトピアノ（中学の合唱部の練習室で伴奏の代役をした）、グロッケンシュピール（高校のミュージカルの裏方で叩いた）、タンバリンと手拍子（デモの打楽器は自分で録る）、祖父の家にあった古いハーモニカ（函館で 10 歳のころに吹いた）</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>空港の出発ロビー、蛍光灯のちらつき、人の話の途中で携帯を見ること、急かされる打ち合わせ</t>
+          <t>エレキギター（1990 年代のスクワイヤーのストラトキャスター／コナーに借りたまま 8 年）、アップライトピアノ（中等学校の音楽室で放課後に独学）、エレキベース（カレッジの実習で録音用に少し）、ティン・ホイッスル（小学校で習った・今はコークの家族の前でだけ吹く）</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>ガラス張りの会議室、自分の声の録音を 1 人で聴くこと、意見を急かされること</t>
+          <t>ウクレレ（子ども教室で使う）、エレクトリックピアノ（コードを押さえてメロディを探す程度）、エレキベース（デモで仮のラインを弾く程度）、タンバリン、ハーモニカ（C の 1 本だけ）</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>議題のない会議、窓のない部屋、大音量の店</t>
+          <t>鍵盤ハーモニカ（浜松の小学校で習った）、エレクトリックピアノ（アレンジのデモでコードを確かめる）、アコースティックギター、カヴァキーニョ（父のものを少し）、パンデイロ</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>遅刻、図面だけ描いて現場を見ない人、大声で値切る客</t>
+          <t>カホン（自作）、ウクレレ（教会の集まりで伴奏する程度）、タンバリンとシェイカー、エレキベース（教会の礼拝で代役をする程度）、ピアノ（賛美歌のコードを押さえる程度）</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>急かされること、手仕事を「ただの趣味」と片付けられること、使い捨てのプラスチック包装</t>
+          <t>ウクレレ（地区の学校の音楽の授業で）、ティンホイッスル（パブのセッションで覚えた）、ピアノ（合唱部でアルトの音を取る程度）、足踏みハーモニウム（ゲシンの楽器で持続音だけ）</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>グラスファイバーの粉、まだ使える船を燃やすこと、細い県道で後ろから煽ってくる車</t>
+          <t>アイリッシュ・ブズーキ（セッションで借りて弾く）、ボーラン（セッションで覚えた）、ピアノ（礼拝堂で母の合唱の音取りを手伝う程度）、ハーモニカ（アイラのものを借りて）</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>打ち合わせ直前に変わる縮尺、スピーカーフォンで話す人、空いた席に荷物を置く人、急かされて引く線</t>
+          <t>Squier のテレキャスター（2021 年にウォルサムストウの中古楽器店で・ハイライフ風の 2 音のリフ専用）、Korg minilogue（2023 年に中古で・丸いサブベースとパッドの下地）、工房の道具（鋼尺・紙やすり・カッティングマット・替え刃のケース）を手で鳴らす、フィルムケースに模型用の砂を詰めた手作りのシェイカー、教会ホールのアップライトピアノ（帰省のたびに礼拝のあとで少しだけ）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>嫌いな言葉</t>
+          <t>機材・録音の道具</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Where are you really from?、日本語お上手ですね、どうせ</t>
+          <t>録音は Focusrite Scarlett 2i2（第 3 世代）と Audio-Technica AT2020 で、声は自宅の出窓の前に毛布を吊るして録る。DAW は 2022 年に函館で浩平から教わった REAPER で、ミックスの確認は Sony MDR-7506 と配送バンのスピーカーの両方で行う。ギターは Boss DD-8 と Boss RV-6 だけを通し、歪みのペダルは持っていない。歌のメモはスマートフォンの音声メモに日付と日の出時刻を付けて残す。</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>hustle（もっと稼げ）、content（作品をコンテンツと呼ぶこと）、back home（どっちの家のことか分からなくなる）</t>
+          <t>15 歳から使っている 4 トラックのカセットレコーダー TASCAM 424 MKIII Portastudio と、2026 年 10 月に局から持ち帰ってよいと言われた業務用カセットデッキ TASCAM 122MKII が録音の要で、祖父の 43 本のテープは 122MKII のヘッドの角度を 1 本ずつ合わせてデジタル化した。歌は放送用のダイナミックマイク Shure SM7B を Focusrite Scarlett 2i2 につなぎ、DAW は REAPER。ギターには BOSS CE-2 のコーラスだけを掛け、車内やガーディナーの継ぎ目の音は Zoom H5 で録っている。ライブでは祖父の 1980 年代のソニーのラジカセを再生専用に置き、テープの断片をその場で流す。</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>deliverables（成果物）、just quickly（ちょっとだけ）、synergy</t>
+          <t>アンプは 2018 年に勤め先の楽器店の中古で買った Roland JC-40 で、クリーンとコーラスの広がりが基準。足元は Boss CE-2（1980 年代のコーラス）・MXR Dyna Comp・Boss DD-3 の 3 つだけ。家の録音は Focusrite Scarlett 2i2 と Shure SM58 で Logic Pro に録り、歌はコートの詰まった洋服だんすに頭を入れて録る。鼻歌はスマホのボイスメモに 1 日 3〜10 本ためる。</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>exotic、where are you really from、just vibes</t>
+          <t>弦は La Bella のフラットワウンド 760FS を 1 年以上張り替えずに使う。足元は MXR M87 のコンプと Tech 21 SansAmp Bass Driver DI の 2 つだけで、リハでは Ampeg BA-115、サービスエリアでは電池で鳴る Roland Micro Cube Bass RX を使う。家では Focusrite Scarlett Solo に直接つないで Reaper に録る。断面図は 5 mm 方眼のノートと 0.5 mm のシャープペンで描く。</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>just a tradie（ただの職人）、unskilled、hustle</t>
+          <t>シンバルは Zildjian K の 14 インチのハイハットと、教会のおじのお下がりの Paiste 2002 の 20 インチのライド。スティックは Vic Firth 7A のヒッコリーで、ブラシは Vic Firth Heritage Brush。バンドの録音は工場で RØDE NT5 を 2 本オーバーヘッドに、スネアに Shure SM57・キックに AKG D112 を置き、Focusrite Scarlett 18i8 で Reaper に録る。バンには Evans RealFeel の練習パッドと Boss DB-90 のメトロノームを常に積んでいる。</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>“quick fix”（その場しのぎ）、“just a hobby”（ただの趣味）</t>
+          <t>配信と声のメモは Rode NT-USB 1 本と iPhone の標準の録音アプリ。網小屋ではゲシンが組んだ録音の道具を一緒に使う。ギターの弦は D'Addario EJ16（フォスファーブロンズのライト）で、張り替えは 3〜4 か月に 1 回と遅い。カポは Kyser の古いものを 2 フレットに付けたままにしている。</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>“disposable”（使い捨て）、“upgrade”（新品に替えること）</t>
+          <t>網小屋の録音は Focusrite Scarlett 4i4（第 3 世代）と DAW の Reaper を中古のノートパソコンで動かす。マイクは Audio-Technica AT4040 1 本を 2 人で挟んで声を録り、Rode NT5 の 2 本を XY に組んでギターとオルガンを録る。父から譲られた TASCAM 424 MkII のカセット 4 トラックに、ハミングと雨音だけを一度通して戻すこともある。</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>just（『ちょっと作るだけ』と仕事を小さく言う言い方）、hobby、content（作品を『コンテンツ』と呼ぶ言い方）</t>
+          <t>制作は MacBook Air（M1・2020 年）と Ableton Live 12 Suite で、最初の曲は 14 歳のときに父のお下がりのノートパソコンと無料の LMMS で作った。オーディオインターフェースは Focusrite Scarlett 2i2（第 3 世代）、息とハミングはクローゼットの服の間に立てた Rode NT1 で録る。テープの揺れとかすかなノイズは XLN Audio の RC-20 Retro Color で足し、夜は首に掛けた Sony MDR-7506 で聴き、屋根裏では小さな IK Multimedia iLoud Micro Monitor を小音量で鳴らす。夜行バスでは MacBook Air と Launchkey Mini と SP-404MKII を膝に載せ、Zoom H5 を窓際に置いてエンジンのうなりを録る。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>嫌いな色</t>
+          <t>演奏方法・奏法の癖</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>蛍光ピンク、3 月のポートランドの濁った灰色</t>
+          <t>シンセは右手でアルペジエーターをラッチして 8 分・上行・ゲート短めに固定し、左手は低い鍵盤でルートを 1 小節に 1 回だけ押さえる。和音は 3 度を上に置いた開いた形で、高い声の帯域をふさがないよう真ん中の 1 オクターブを空けておく。サビの直前で左手をフィルターのつまみに移し、2 小節かけてゆっくり開いてから、サビ頭で一度だけ少し戻すのが癖。サスティンペダルは使わず、音の切れ目はリリースの短さで作る。ギターはピックを浅く持ち、右手の付け根で 2〜3 本の弦を軽くミュートして 16 分の短いカッティングを裏拍寄りに置き、弦は鳴らし切らない。歌いながら弾くときは、歌の子音を拍の頭に置き、鍵盤とギターはわずかに後ろへずらしてぶつからないようにする。</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>蛍光灯の青白い白、蛍光のライムグリーン</t>
+          <t>パッドは左手で根音と 5 度と 9 度を開いて押さえ、右手は 3 度を上の方にだけ置いて低音域を濁らせない。和音を替えるときは指を半拍遅れて離し、次の和音とわずかに重ねてアタックの遅い音色の切れ目を消し、サビでは左手でフィルターのつまみをゆっくり上げて明るさだけで盛り上げる。アルペジオは 16 分の上下交互を機械に任せ、自分は右手で 2 小節ごとに 1 音だけ和音の構成音を差し替えて動きを作る。ドラムマシンのスネアは 2・4 拍目で数ミリ秒後ろに置き、ハイハットは 8 分で強弱を交互にしてゴーストのような弱い音を混ぜる。祖父のテープからサンプルを切るときは、声の前後に 0.2 秒ほどヒスを残して切り、頭を少しだけフェードインさせて継ぎ目を聞こえなくする。歌はマイクから拳 1 つの距離で口元を少し斜めに外し、破裂音を息で逃がしながら語るように置く。</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>ショールームのような純白、蛍光の黄緑</t>
+          <t>右手は弦に当てない瞬間も 16 分で上下に振り続け、当てるか空振りするかで刻みを作る。左手は 1〜3 弦の 3 音だけの小さな 7th や 9th の和音を 7〜10 フレットあたりで押さえ、指の力を抜いた瞬間に音を切る左手ミュートでカッティングの跳ねを出す。ピックは 0.6 mm の薄いものを浅く持ち、裏拍のアクセントは手首ではなく肘から少し強く振って出す。歌いながら弾くときは言葉と同じく拍の少し後ろに和音を置き、サビでは 12 弦に持ち替えて開放弦を残したアルペジオで広げる。チューニングは標準でカポはほとんど使わず、左手の人差し指の付け根の傷が目に入ると、急がず 1 拍待つ合図にしている。</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>蛍光ピンク、光沢のある金色</t>
+          <t>右手は人差し指と中指の 2 本で弾き、親指をピックアップに乗せて、A メロはネック寄りで丸く、サビはブリッジ寄りで硬めにと弾く場所を変える。ブリッジの下に薄いスポンジを挟んで余韻を短くし、右手の小指側で弦に軽く触れるミュートで 16 分の短い音を切る。ゴーストノートは左手の指を弦に乗せただけで弾く詰まった音で入れ、キックと揃えるのはサビだけ、A メロではわざと 1 拍目を外してシンコペーションで入る。サビの直前に 1 オクターブ上へスライドしてから 1 拍目でルートに戻るのが癖で、オクターブと 10 度で跳ねるラインを好む。チューニングは標準で、低い D が要る曲だけ 4 弦を下げる。弾きながらキノの 3 度上を歌うので、ハモりの小節ではベースを 2 分音符に減らして声を守る。</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>光沢のある黒、くすんだ紫</t>
+          <t>マッチドグリップで、ハイハットは右手 1 本で 16 分を刻み、拍の最後の 16 分だけ少し強く当てて跳ねを出す。スネアのゴーストノートはスティックの先を 2 cm ほどしか上げずに置き、2 拍 4 拍の本打ちはわずかに後ろに座らせる。キックはかかとを下ろしたまま踏み、ベースと揃えて踏むのはサビだけにする。A メロはスネアの縁を叩くクロススティックで、サビで左足のハイハットを少し開けて広げ、フィルは 1 拍以内に収める。スネアは高めに締め、打面の端に小さく畳んだ布をテープで貼って余韻を短くする。サービスエリアではキックとスネアとハイハットだけにし、静かな曲はブラシで円を描くように擦る。</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>蛍光ピンク、化学染料の真っ青</t>
+          <t>ピックは使わず、右手の親指の腹で下へ、人差し指の爪の背で上へ払うやわらかいストロークで、手首ではなく肘から腕全体を揺らして弾く（2023 年の腱鞘炎のあとに手首を守るために変えた）。左手は G・Cadd9・D・Em7 のように薬指と小指を 2 弦と 1 弦の 3 フレットに置いたままの形を好み、セーハの和音はほとんど使わない。カポを 2 フレットか 4 フレットに付けて、自分の声が一番やわらかく鳴る A や B の調に合わせる。言葉の頭を下へのストロークにそろえ、行の終わりは弦を押さえる力をふっと抜いて音を切る。歌は子音を弱く母音を長めに取り、上のハモりは主旋律から 3 度上を平行にたどり、行末の 1 音だけ 6 度に開く癖がある。</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>ネオンの緑、光沢のある銀</t>
+          <t>右手は爪を短く切った素手の指弾きで、親指が 6 弦と 4 弦を交互に弾き続け、人差し指と中指で上の 2 弦をつまむ。親指は鉋を引くように 2 拍目と 4 拍目をわずかに長く押し、右の手のひらの側面で低音弦を軽くミュートして、打楽器の代わりにする。チューニングは DADGAD とドロップ D が中心で、開放弦の D と A を鳴らし続けたまま、左手は 2〜3 本の指で中の声部だけを動かす。オルガンは両足でゆっくり均等に踏み、左手で D と A の 5 度を伸ばしたまま、右手で 3 音の和音を声の下に置く（ストップはやわらかい 1 つだけ）。マンドリンはトレモロをほとんど使わず、2 拍目と 4 拍目の短い刻みと、アイラの上ハモと同じ 3 度の重音を細く弾く。歌うときは行末の下ハモを半拍遅れて着地させ、語尾を息で滲ませる。</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>蛍光ピンク、ショールームの真っ白</t>
+          <t>毎晩最初の 10 分は息とハミングだけを録り、波形がゼロを横切る点で 1 拍ずつ切って、頭と尻に数ミリ秒のフェードを付ける。切れ端は半音単位でピッチを変えるが声の芯の太さは補正せず、サンプラーのパッドを右手の指 2 本で叩いて並べ、左手はフィルターのつまみに置いたまま開け閉めする。エレピは左手で根音を抜いた 9th と 11th の和音を押さえ、親指で 3 度を軽く添えて、拍のほんの少し後ろに置く。打鍵は弱めで高音の金属的な響きを出さず、サステインペダルは半分だけ踏んで小節の頭で必ず一度上げる。ドラムはキックだけを格子にきっちり置き、裏打ちのハイハットは 56% 前後のスウィング、リムショットのゴーストノートは強さ 30〜40 で散らし、シェイカーはパッドで手弾きして量子化せず少し遅らせる。ギターはピックを使わず親指と人差し指でつまむように弾き、3 度か 6 度離れた 2 音だけを裏拍に置いて、右手の小指側の手のひらで弦を軽くミュートする。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>嫌いな食べ物</t>
+          <t>演奏の強み</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>冷めたフライドポテト、甘すぎるシリアル</t>
+          <t>同じアルペジオを 4 分以上揺れずに鳴らし続けられ、テンポ感が体に入っている。フィルターの開け閉めだけで曲の夜明けを作る耳があり、サビの入りの明るさの差がはっきり出る。音色を選ぶのが速く、イントロの 2 小節で朝だと分かる音を見つけるのがうまい。</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>甘すぎるコーヒー飲料、メープル味のスナック（同僚が毎年すすめてくる）</t>
+          <t>音色を作る耳と、和音から和音へ声部を最短で動かすつなぎ方が一番の強み。テンポを体で保つ感覚が強く、バックトラックに合わせて生でパッドを重ねても揺れない。テープの劣化やヒスを『汚れ』ではなく音の温度として扱え、録った素材を曲の地に馴染ませるのがうまい。</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>冷めたフライドポテト、ドリアン</t>
+          <t>歌いながらでも 16 分の刻みが崩れず、声とギターが同じ揺れ方をする。音数の少ないカッティングで隙間を作り、ビアのベースとタヴのハイハットの間に正確に座れる。サービスエリアのように音が返らない屋外でも右手の振りを止めないので、3 人のテンポの芯になる。</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>甘すぎるアイシング、豪州の黒い酵母ペーストの塗りすぎ</t>
+          <t>歌うようなベースラインで、曲の骨組みと主旋律の両方を支えられる。指弾きの粒がそろっていて、16 分のシンコペーションでもタヴのキックと噛み合う。弾きながら 3 度上のハモりを正確に歌える。</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>生の玉ねぎ、甘いポップコーン</t>
+          <t>テンポが揺れず、急がないのに前へ進むグルーヴ。サビの 1 拍目でベースとキックを合わせる確かさで、3 人の演奏を 1 つにまとめる。叩きながらでも低い声のユニゾンを崩さない。</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>缶詰のグリーンピース、甘すぎるファッジ</t>
+          <t>メトロノームなしでも 1 曲を通してテンポが揺れず、編みながらでも歌いながらでも同じ揺れを保てる。初めて聴いた旋律に、その場で上のハモりを付けるのが速く正確。</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>スライスされたプロセスチーズ、冷めたチップス</t>
+          <t>指弾きの低音の反復を一切崩さずに、その上で下ハモを歌い続けられる。人の旋律の下で、その声が一番よく鳴る内側の和音を探し当てるのが得意。オルガンの持続音で、少人数でも部屋が満ちる厚みを作れる。</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>ぬるくなった缶コーヒー、ミント味のお菓子</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>■ メモ</t>
-        </is>
-      </c>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="29" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="29" t="n"/>
-      <c r="H42" s="29" t="n"/>
-      <c r="I42" s="29" t="n"/>
+          <t>1 拍の息の切れ端を、言葉が無くても気持ちが伝わる長さで切るタイミングの勘。4 時間鳴らしても耳が疲れない密度に、引き算で整えられること。他人のステムから 1 語と 1 つの息を選び出し、元の曲の場面を壊さずに夜の長距離用の道へ組み直すリミックスで一番光る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>音と演奏の好み</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>倍音の多い明るいノコギリ波を少し丸めた音と、短く減衰する高いベルの音が好き。テンポは 110〜116 の前のめりにならない 8 分で、部屋鳴りは少なめの乾いた録り方を好む。ギターは細めの弦を張ったクリーンな音で、ピックは薄いもの。録るのは朝の光が入る午後の早い時間で、夜には録らない。</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>アタックの遅い温かいパッドと、ほんの少しピッチの揺れたコーラスの音色が好き。部屋鳴りは小さく乾いた方がよく、歌のガイドは駐車場に停めた車の中で録る（布張りの座席が音を吸うから）。テンポは 92〜104 の歩くより少し速いくらいで、録音は一度カセットに通してから戻す。</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>ネック側と真ん中のピックアップを混ぜた、少し鼻にかかったクリーンの音が好き。弦は細めの 10〜46 を 2 週間ごとに替え、張って 3 日目くらいの落ち着いたきらめきがいちばん好み。テンポは 112〜120 の昼の速さで、録るときはアンプから 1 m 離して部屋の響きを少し入れる。</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>フラットワウンド弦の丸く短い音と、指で弾いたときの木の鳴りが好き。テンポは 116〜124 の跳ねる速さ。アンプのマイクより、ラインで録った芯のある音に部屋の響きを少し混ぜる録り方を好む。</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>乾いて短く鳴る木の胴の音と、余韻の少ない締まったスネアが好き。テンポは 112〜118 の、少し後ろに座れる速さ。天井の高い元工場の部屋鳴りを、オーバーヘッドのマイク 2 本で少しだけ録るのが好み。</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>マホガニーの小さなギターの、乾いて丸い中音が好き。弦は張り替えたばかりの金属的な鳴りより、少しくすんだ頃の音を好む。テンポは 88〜96 BPM ほどの、歩くより少し速い揺れ。木の床と梁のある部屋で、マイクから 30cm ほど離れて息ごと録られるのが好き。</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>乾いた木の胴が深く鳴る、低音の太いギターの音が好き。弦は錆び始めるまで替えず、テンポは 80 BPM 台前半のゆっくりした揺れを好む。録音は網小屋の木の梁と床の響きごと、一発録りで残したい。雨と木の軋みが入っても消さない。</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>丸くて少し暗い鍵盤の音色と、角の取れた柔らかいキックが好き。テンポは 104〜118 BPM の、急がずに前へ進む帯域。息は 30 cm ほど離れた狭くて響かない場所で録り、ギターはフラット弦でこもった音にする。部屋鳴りよりも、工房や車内の換気扇のような遠くの持続音を背景に敷くほうを好む。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
         <is>
+          <t>演奏の苦手</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>両手が別々のリズムで動く速いフレーズと、楽譜の初見は苦手。ギターはセーハの和音と即興のソロがほとんどできない。</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>速い単音のソロや、楽譜を見てすぐに弾くことは苦手。歌いながら左手で動きの多いベースを弾くと、どちらかが崩れる。</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>速い単音のギターソロと、歪ませた音で長く伸ばす弾き方が苦手で、ソロの場面はたいていビアのベースに譲る。</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>スラップや指板の上の速い早弾きは苦手。和音が複雑な曲では、ハモりに気を取られてベースが平たくなる。</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>速いツーバスや、拍子が変わり続ける複雑な曲は苦手。手数の多い派手なフィルを求められると体が固くなる。</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>セーハの和音と速い単音のフレーズは苦手で、腱鞘炎以降は長く弾くと手首が痛む。緊張するとテンポを前へ急がせてしまう。</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>速い単音のリードやピックでの早弾きは苦手で、人前で主旋律を 1 人で歌うと声が細くなる。放っておくとテンポを遅くしすぎる。</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>鍵盤の速いパッセージと楽譜の初見は苦手で、和音は耳と指の形で覚えている。人前での即興は今も緊張し、ライブでは段取りを決めた順番から外れられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>音楽の学び方・練習</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>ほぼ独学で、父のカセットや好きな曲のシンセのフレーズを耳でコピーして覚えた。コミュニティカレッジのオンラインの音楽理論で和音の名前を整理し、函館では浩平に録音とミックスの基本を教わった。毎日午後 1 時からの最初の 20 分は 8 小節の耳コピ・次の 10 分は合唱部で習った子音の発声練習と決めている。</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>楽器は独学で、子どもの頃から祖父のテープや深夜ラジオの曲を耳で拾って弾いてきた。カレッジの音響・メディア技術科で録音とミックスの基礎を学び、今は毎日シフトの前に 30 分、好きな曲の音色を 1 つだけ耳で作り直す。帰りの車では、低い音から 5 音の音階をハミングして声を温めてから眠る。</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>2012 年からいとこの部屋で耳コピで覚え、教則本はほとんど使っていない。毎朝メトロノームを 60 に落として 16 分の空振りカッティングを 10 分、そのあと好きな曲を 1 曲だけ耳でコピーする。子どもの教室で教えることが、自分の弾き方を言葉で見直す練習になっている。</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>14 歳でサンパウロの楽器店の店主に 1 年間レッスンを受け、あとは父のレコードの耳コピで覚えた。毎晩寝る前に 20 分、メトロノームを 2 拍 4 拍だけ鳴らして指弾きの粒をそろえる。気になったベースラインは、まず方眼ノートに図として写してから弾く。</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>8 歳から教会のおじに耳で習い、Frankston の中等学校のステージバンドで初めて楽譜を読んだ。現場の昼休みにバンの中で練習パッドを 15 分、メトロノームを 2 拍 4 拍だけ鳴らして叩く。日曜に教会の若い子に教えることで、自分の基本も毎週見直している。</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>独学。父の車のカセットや上級生に借りた CD のハモりを耳でまねて覚え、ギターは寄宿学校で上級生に教わった 3 つのコードから広げた。今は毎朝、染め鍋が温まるまでの 20 分にハミングで音階を上下し、夜は編みながら新しい曲の歌詞を口の中で繰り返す。</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>ギターは独学で、父の作業場のレコードを耳で追って変則チューニングと指の型を覚えた。歌は子どもの頃に礼拝堂で母から階名の楽譜（トニック・ソルファ）で音を取ることを教わった。今はボートヤードの昼休みに 15 分ギターを触り、木曜のセッションで新しい伝承曲を 1 曲ずつ覚える。</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>8〜9 歳の頃にリーズの教会のピアノ奏者に数か月だけ手ほどきを受けたほかは独学。週に 1 曲、父のハイライフのレコードかシカゴのハウスから 4 小節の和音を耳で取り、エレピで左手の形だけを覚えて自分の曲に移す。毎晩 22 時に録る 10 分の息とハミングが日課で、ファンミの番組の前月には『踊れるか・眠れるか』の 2 択を想定して同じ曲をテンポ違いで 2 本作る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>好きなアーティスト（実在）</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>宇多田ヒカル、Tears for Fears、CHVRCHES、The Postal Service、Kraftwerk、Japanese Breakfast、Carly Rae Jepsen、Robyn、Glen Campbell</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>The Blue Nile、Leonard Cohen、Bryan Ferry、Depeche Mode、Talk Talk、Kavinsky、Chromatics、The Midnight、The Weeknd</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Air Supply、Eraserheads、Steely Dan、Phoenix、Paul Kelly、Mac DeMarco、Rivermaya、Ben&amp;Ben、The Go-Betweens</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Marcos Valle、Mariya Takeuchi、Tatsuro Yamashita、Azymuth、Tim Maia、Jorge Ben Jor、Taeko Ohnuki、Tame Impala、Carol Kaye</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Fat Freddy's Drop、Crowded House、Vulfpeck、Bill Withers、Hiatus Kaiyote、The Black Seeds、Six60、Daryl Hall &amp; John Oates</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Crowded House、The Chills、Gillian Welch、The Unthanks、Tiny Ruins、Marlon Williams、Aldous Harding、Emmylou Harris、The Be Good Tanyas</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>John Martyn、Meic Stevens、Nic Jones、Damien Rice、Bert Jansch、Nick Drake、The Waterboys、Cerys Matthews、Martin Carthy</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Burial、Larry Heard、Four Tet、Aphex Twin、Nils Frahm、Ebo Taylor、E.T. Mensah、Floating Points、Caribou</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>■ 好きなもの</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="E46" s="29" t="n"/>
+      <c r="F46" s="29" t="n"/>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="29" t="n"/>
+      <c r="I46" s="29" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>好きなこと</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>日の出の 10 分前の空、夜明け前の空いたガソリンスタンド、魔法瓶のココア、道路標識の書体</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>夜の空いた高速、カセットのラベルを手書きすること、雨上がりのオレンジの街灯、パン屋の一番窯の匂い</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>ガソリンスタンドのホットパイ、空港線の高架を昼に下から見上げること、いとこの結婚式のカラオケ、0.3 mm のシャープペン</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>方眼ノート、他人の家の台所、0.5 mm の芯で引く細い線、長距離バスの窓際の席</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>朝 6 時の現場の静けさ、切ったばかりの木材の匂い、父とラグビーを見ること、ドラムのチューニング</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>羊毛の脂（ラノリン）の匂い、雨の日の窓辺で編むこと、砂利道を走るタイヤの音、市場が終わったあとの片付け</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>朝の満ち潮の音、鉋屑の匂い、ギグ漕ぎの掛け声、雨の日のボートヤードのラジオ</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>夜行バスの最前列の左の席、カッターの刃を替える瞬間、中庭のある建物の平面図を眺めること、誰もいない日曜の朝の工房</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>好きな言葉</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>first light、したっけ、clear and dry（父の無線の路面状況）、おはよう</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>grand（上等・大丈夫）、the small hours（夜更けの数時間）、go easy（無理するなよ）</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>load path（力の流れ）、Sige、halfway、good enough</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>habitável（住める）、やらまいか、span（スパン）、saudade</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Sweet as、plumb（垂直）、Faʻafetai、load-bearing（荷重を受ける）</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>mend（繕う）、fleece（ひと刈り分の羊毛）、cast on（編み始める）、southerly（南風）</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>hiraeth（ウェールズ語で帰れない場所への想い）、cwtch（ウェールズ語で抱きしめること・安心できる場所）、fair wind（順風）</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>hollow、headroom（余裕・天井の高さ）、Ɛyɛ（大丈夫・いいね〔トウィ語〕）、plan view（真上から見た図）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>好きな色</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>夜明け前の群青、除雪車のアンバー、梨の花の白</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>ナトリウム灯のオレンジ、瓶の深い緑、夜明け前の紺</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>道路標識の緑、ガムテープの銀、色あせたオレンジ</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>テラコッタ、浜松の団地の階段の水色、ユーカリの灰緑</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>未塗装のユーカリ材の赤茶、曇りの日のネイピアの海の灰青、安全ベストのオレンジ</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>生成り（未染色の羊毛）、ハリエニシダの黄、濡れたスレートの青灰</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>タールの黒、ペンキの剥げた船の緑、霧の朝の白</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>バルサ材の生成り、古い高速の街灯の琥珀色、ケンテ布の深い緑</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>好きな食べ物</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>祖母のイカめし、マリオンベリーのパイ、父が焼く分厚いハッシュブラウン、函館の塩ラーメン</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>コークのスパイス・ビーフ（クリスマスの塩漬け牛）、母のブラウンブレッド、イネスの店のエッグタルト、深夜営業の中華料理店の炒飯</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>母のシニガン（タマリンドの酸っぱいスープ）、サービスエリアのミートパイ、ハロハロ、Footscray のバインミー</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>ポン・デ・ケージョ、母のブラジル風ヤキソバ（とろみのある餡かけ）、浜松の餃子、フェイジョアーダ</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>おばのパルサミ（タロの葉のココナッツクリーム包み）、新聞紙に包んだフィッシュ＆チップス、ホーキーポーキー（ハニカムトフィー入りのアイス）、ミートパイ</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>母のやり方のラム肉のロースト、ホーキーポーキー味のアイスクリーム、祖母のオランダ風パンケーキ、コーンウォールのサフランパン</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>母のカウル（羊と根菜のウェールズのスープ）、ウェルシュケーキ、焼いた鯖、ラバーブレッド（海藻のペースト）</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>母のライトスープとフフ、ケレウェレ（香辛料で揚げたプランテン）、日曜のローストとヨークシャー・プディング、サービスエリアのミルク多めの紅茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>■ 嫌いなもの</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="29" t="n"/>
+      <c r="I51" s="29" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>嫌いなこと</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>夜 9 時以降の打ち合わせ、遅刻、霧が晴れない 3 月の朝、「で結局どっちの人なの？」と聞かれること</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>空港の出発ロビー、蛍光灯のちらつき、人の話の途中で携帯を見ること、急かされる打ち合わせ</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>ガラス張りの会議室、自分の声の録音を 1 人で聴くこと、意見を急かされること</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>議題のない会議、窓のない部屋、大音量の店</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>遅刻、図面だけ描いて現場を見ない人、大声で値切る客</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>急かされること、手仕事を「ただの趣味」と片付けられること、使い捨てのプラスチック包装</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>グラスファイバーの粉、まだ使える船を燃やすこと、細い県道で後ろから煽ってくる車</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>打ち合わせ直前に変わる縮尺、スピーカーフォンで話す人、空いた席に荷物を置く人、急かされて引く線</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>嫌いな言葉</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Where are you really from?、日本語お上手ですね、どうせ</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>hustle（もっと稼げ）、content（作品をコンテンツと呼ぶこと）、back home（どっちの家のことか分からなくなる）</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>deliverables（成果物）、just quickly（ちょっとだけ）、synergy</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>exotic、where are you really from、just vibes</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>just a tradie（ただの職人）、unskilled、hustle</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>“quick fix”（その場しのぎ）、“just a hobby”（ただの趣味）</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>“disposable”（使い捨て）、“upgrade”（新品に替えること）</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>just（『ちょっと作るだけ』と仕事を小さく言う言い方）、hobby、content（作品を『コンテンツ』と呼ぶ言い方）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>嫌いな色</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>蛍光ピンク、3 月のポートランドの濁った灰色</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>蛍光灯の青白い白、蛍光のライムグリーン</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>ショールームのような純白、蛍光の黄緑</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>蛍光ピンク、光沢のある金色</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>光沢のある黒、くすんだ紫</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>蛍光ピンク、化学染料の真っ青</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>ネオンの緑、光沢のある銀</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>蛍光ピンク、ショールームの真っ白</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>嫌いな食べ物</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>冷めたフライドポテト、甘すぎるシリアル</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>甘すぎるコーヒー飲料、メープル味のスナック（同僚が毎年すすめてくる）</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>冷めたフライドポテト、ドリアン</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>甘すぎるアイシング、豪州の黒い酵母ペーストの塗りすぎ</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>生の玉ねぎ、甘いポップコーン</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>缶詰のグリーンピース、甘すぎるファッジ</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>スライスされたプロセスチーズ、冷めたチップス</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>ぬるくなった缶コーヒー、ミント味のお菓子</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>■ メモ</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="29" t="n"/>
+      <c r="E56" s="29" t="n"/>
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="29" t="n"/>
+      <c r="H56" s="29" t="n"/>
+      <c r="I56" s="29" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>顔は出さない。手はよく日焼けしていて、左手の甲に小さな火傷の跡がある（撮影ではそのまま写す）。</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>アイルランド国籍。カナダ永住権は 2020 年に取得。酒はほとんど飲まず、運転する夜は一切飲まない。</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>声の固定はキノ。父のトラックと Hume Freeway がいちばん大きな歌の源。</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>曲の骨組みの担当。ハモりは常にキノの 3 度上。浜松の団地とサンパウロの記憶が、移り住む歌の源。</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>グルーヴと運転と予算の担当。3 人の中で唯一、実物の片持ちのデッキを施工している。</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>デュオの中心。言葉と日々の手触りを持ち込む人。結婚後も姓はレニーのまま。人前で話すのはアイラ。</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>曲の骨組みと和音を作る人。ステージではほとんど話さない。</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr">
         <is>
           <t>顔は出さない。うなじの小さな四角のタトゥーと、低くまとめたブレイズが後ろ姿の目印。</t>
         </is>
@@ -15637,7 +16266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -15647,6 +16276,9 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -15682,7 +16314,22 @@
       </c>
       <c r="G1" s="19" t="inlineStr">
         <is>
+          <t>作品・曲・時期</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>出会ったとき</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
           <t>受け取ったもの</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>どこに表れているか（声・演奏・曲づくり・見た目）</t>
         </is>
       </c>
     </row>
@@ -15719,7 +16366,22 @@
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
+          <t>アルバム『First Love』（1999）とその表題曲</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>物心ついたころ（2000 年代半ば）からオデルの家の台所で。母が函館に帰省したときに買ってきた CD で、朝の支度の時間に流れていた</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
           <t>母が函館から持ってきた CD で、オデルの台所でいつも流れていた。日本語と英語のあいだを行き来しながら言葉をはっきり置いて歌う人がいると知り、2 つの言語を持っていることは隠すものではないと受け取った。</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>英語の歌の中に日本語を 1 語だけはっきり置く歌詞の決まりと、子音を立てて言葉を 1 音ずつ届ける歌い方に出ている</t>
         </is>
       </c>
     </row>
@@ -15756,7 +16418,22 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
+          <t>アルバム『Songs from the Big Chair』（1985）の 3 曲目「Everybody Wants to Rule the World」</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>4〜5 歳の冬（2006〜07 年）・オデル。父の除雪用ピックアップのカセットデッキに入りっぱなしだったテープで、助手席で何度も聴いた</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
           <t>父のピックアップのカセットデッキに入りっぱなしだったテープ。除雪の朝に何度も聴き、前へ進み続ける推進力と明るいシンセの音色が、夜明けの道の音として体に残った。</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>同じフレーズを繰り返しながら少しずつ開いていく曲の形と、明るいシンセを何層か重ねるイントロに出ている。テンポを急がず前へ進む感じも、除雪の朝の記憶とつながっている</t>
         </is>
       </c>
     </row>
@@ -15793,7 +16470,22 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
+          <t>アルバム『The Bones of What You Believe』（2013）の 1 曲目「The Mother We Share」</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>13 歳の春（2015 年）・フッドリバー。中古のシンセの使い方を動画で調べていて、ライブ映像にたどり着いた</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
           <t>13 歳でシンセを手に入れたころに見つけたアルバム。硬い 8 分のシンセの上で高い声が子音をはっきり立てて歌う形を、そのまま自分の歌い方の手本にした。</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>硬い 8 分のシンセアルペジオを曲の背骨にする作り方と、高い地声で子音を拍の頭に置く歌い方に、いちばん直接に出ている</t>
         </is>
       </c>
     </row>
@@ -15815,22 +16507,37 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>The Lathe of Heaven（天のろくろ）</t>
+          <t>Give Up</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Ursula K. Le Guin</t>
+          <t>The Postal Service</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>ポートランドの古本屋で買った、この街が舞台の小説。知っている通りや橋が物語に出てくるのを読み、自分の住む場所や毎日の道も物語の舞台になると知った。</t>
+          <t>アルバム『Give Up』（2003・シアトルの Sub Pop から発売）の 2 曲目「Such Great Heights」</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>17 歳ごろ（2019 年）・フッドリバー。中学生だった弟 Ken が見つけて、家の車で繰り返し流していた</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>細かく刻む打ち込みの上で、特別ではない日常の言葉をまっすぐ歌っていいと知った。同じ太平洋岸北西部から出た音楽だということも、自分の暮らしと地続きに感じた。</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>ハイハットと小さなシンセの粒を細かく重ねるリズムの作り方と、身の回りの物の名前をそのまま歌う歌詞に出ている</t>
         </is>
       </c>
     </row>
@@ -15852,22 +16559,37 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>旅をする木</t>
+          <t>Autobahn</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>星野道夫</t>
+          <t>Kraftwerk</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>函館の祖母の家の本棚にあった。遠く離れた土地で暮らしながら別の場所に流れている時間を同時に思う書き方に、時差のある家族を持つ自分を重ねた。</t>
+          <t>アルバム『Autobahn』（1974）の A 面全部を使った表題曲（約 22 分）</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>22 歳の冬（2024 年 12 月）・ポートランド。テンポを 84 号線を走りながら決めていると話したら、ルートの最後のカフェの店主（元レコード店員）が開店前にレコードをかけてくれた</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>高速道路を走ることそのものが音楽になりうると知った。変わらない拍の上で景色だけが少しずつ変わっていく長さを、退屈ではなく心地よさとして受け取った。</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>キックを 4 分寄りに置いて揺らさない一定の拍と、展開を急がず音色の出し入れで景色を変えるアレンジに出ている。DNA の motorik pulse もここから来ている</t>
         </is>
       </c>
     </row>
@@ -15889,22 +16611,37 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>映画</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Paterson</t>
+          <t>Jubilee</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Jim Jarmusch</t>
+          <t>Japanese Breakfast</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>毎朝同じ時間に起きてバスを運転し、合間に詩を書く主人公。早朝の仕事と創作が同じ一日の中にあっていいと背中を押され、配送の信号待ちで言葉を拾う今のやり方につながった。</t>
+          <t>アルバム『Jubilee』（2021）の 2 曲目「Be Sweet」</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>19 歳（2021 年の夏）・フッドリバーのパン屋。朝 4 時半からの仕込みの時間に、店のスピーカーで繰り返し流していた</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>同じオレゴンで育ちアジア系の母を持つ人が、暗さではなく明るさで自分を歌っているのを聴き、2 つのルーツを持つことを明るい音で鳴らしていいと思えた。</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>弾むシンセベースと 80 年代風の明るいシンセの組み合わせと、口ずさみやすいサビの言葉の置き方に出ている</t>
         </is>
       </c>
     </row>
@@ -15926,133 +16663,193 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>The Lathe of Heaven（天のろくろ）</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Ursula K. Le Guin</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>長編小説『The Lathe of Heaven』（1971）</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>21 歳の春（2023 年）・ポートランドに移ってすぐ、配送明けに寄った近所の古本屋で</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>ポートランドの古本屋で買った、この街が舞台の小説。知っている通りや橋が物語に出てくるのを読み、自分の住む場所や毎日の道も物語の舞台になると知った。</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>通りの名前や橋を歌詞にそのまま入れる書き方（Alberta・Fremont など）と、自分の配送ルートを歌の舞台にする発想に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>旅をする木</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>星野道夫</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>随筆集『旅をする木』（1995）</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>20 歳（2022 年）・函館の祖母の家。子どものころから本棚で背表紙だけ知っていたのを、祖母と暮らした冬に初めて読んだ</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>函館の祖母の家の本棚にあった。遠く離れた土地で暮らしながら別の場所に流れている時間を同時に思う書き方に、時差のある家族を持つ自分を重ねた。</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>自分の朝と家族の夜を 1 曲の中に同時に置く歌（時差の歌）と、遠くの人に語りかける二人称の視点に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>映画</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Paterson</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Jim Jarmusch</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>映画『Paterson』（2016）</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>21 歳の冬（2023 年）・ポートランド。配送ルートの最後のカフェの店主に勧められ、自宅で配信で観た</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>毎朝同じ時間に起きてバスを運転し、合間に詩を書く主人公。早朝の仕事と創作が同じ一日の中にあっていいと背中を押され、配送の信号待ちで言葉を拾う今のやり方につながった。</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>信号待ちで言葉を拾い午後に書く今の作詞のやり方と、毎日同じ仕事の細部を淡々と並べる歌詞のトーンに出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
           <t>言葉</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Morning is when I am awake and there is a dawn in me.（『Walden』より）</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Henry David Thoreau</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>『Walden』（1854）の章「Where I Lived, and What I Lived For」の一節</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>高校 2 年（2018〜19 年）・フッドリバーの高校の英語の授業で</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>高校の英語の授業で出会った一文。朝は時刻ではなく自分が目を覚ましている状態のことだと受け取り、その年の日の出ノートの表紙の裏に書き写した。</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>declan_moth</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>declan</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Hats</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>The Blue Nile</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>祖父のカセットの 1 本（1989 年の深夜番組の録音）に入っていた。都市の夜を大声で歌わず、低い声と長い間で温度を伝えるやり方を受け取った。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>declan_moth</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>declan</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>I'm Your Man</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Leonard Cohen</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>母が台所でかけていたアルバム。安いシンセとドラムマシンの上で、低い声が語るだけで歌になると知った。移住先がこの人の国だったことにも少し縁を感じている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>declan_moth</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>declan</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Nightcall</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Kavinsky</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>18 歳の秋、コークの映画館で映画『Drive』（2011）を観た帰りに何度も聴いた。太いシンセベースと遅いテンポで夜の道路を描く手触りを、今の夜に鳴らす方法として受け取った。</t>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>朝を時刻ではなく気持ちの状態として書く歌詞と、日の出ノートの表紙の裏に今も書き写していることに出ている</t>
         </is>
       </c>
     </row>
@@ -16074,22 +16871,37 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>言葉</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Postscript（詩集『The Spirit Level』1996 より）</t>
+          <t>Hats</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Seamus Heaney</t>
+          <t>The Blue Nile</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>'You are neither here nor there, / A hurry through which known and strange things pass' ——移住の前に母がくれた詩。風に揺さぶられる車の中の詩で、どちらの国にも属しきらない今の自分の居場所を、そのままでいいと言ってくれた。</t>
+          <t>アルバム『Hats』（1989）の 2 曲目『The Downtown Lights』。祖父のテープでは 1989 年秋の深夜番組の録音に入っている。</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>6〜12 歳の頃（2000 年代のはじめ）、金曜の夜に祖父のセダンでサウス・リング・ロードを回る車内で、名前も知らずに何度も聴いた。曲名と歌い手が分かったのは 2021 年、祖父のテープをデジタル化していたとき。</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>祖父のカセットの 1 本（1989 年の深夜番組の録音）に入っていた。都市の夜を大声で歌わず、低い声と長い間で温度を伝えるやり方を受け取った。</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>A メロを狭い音の動きで語るように歌い、サビで少しだけ開く旋律の形。ゆっくり開いていく和音のパッドと、都市の灯りを大声でなく低い声で描く温度の基準になっている。</t>
         </is>
       </c>
     </row>
@@ -16111,22 +16923,37 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>I'm Your Man</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Colm Tóibín</t>
+          <t>Leonard Cohen</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>出発の前日に妹がくれた小説。故郷を出た人が、帰ったときにどちらにも半分ずつしかいない感覚。大げさに書かず、手紙と天気で気持ちを運ぶ書き方を受け取った。</t>
+          <t>アルバム『I'm Your Man』（1988）。とくに 4 曲目の表題曲。</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>幼少期から小学生の頃（1990 年代の終わり〜2000 年代のはじめ）、メイフィールドの家の台所で母がかけていたのを聴いた。歌い手がカナダ人だと知ったのはトロントに移ってから。</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>母が台所でかけていたアルバム。安いシンセとドラムマシンの上で、低い声が語るだけで歌になると知った。移住先がこの人の国だったことにも少し縁を感じている。</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>1 番の前の 2 小節の語りと、ブリッジの 4 小節の語り。歌と語りの境目を作らず、低い声のまま拍の少し後ろに言葉を置く歌い方に出ている。</t>
         </is>
       </c>
     </row>
@@ -16148,207 +16975,297 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Nightcall</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Kavinsky</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>『Nightcall』（2010）。映画『Drive』（2011）のオープニングで使われた曲。</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>2011 年の秋（18 歳）、コークの映画館で『Drive』を観て、帰り道に何度も聴いた。</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>18 歳の秋、コークの映画館で映画『Drive』（2011）を観た帰りに何度も聴いた。太いシンセベースと遅いテンポで夜の道路を描く手触りを、今の夜に鳴らす方法として受け取った。</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>丸く太いシンセベースと、92〜104 の急がないテンポ。夜の道路の映像に曲を合わせて見せる、顔を出さない映像の型にもつながっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>declan_moth</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Postscript（詩集『The Spirit Level』1996 より）</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Seamus Heaney</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>詩集『The Spirit Level』（1996）の最後の詩『Postscript』。</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>2016 年 9 月、トロントへ発つ前の週に母がくれた。</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>'You are neither here nor there, / A hurry through which known and strange things pass' ——移住の前に母がくれた詩。風に揺さぶられる車の中の詩で、どちらの国にも属しきらない今の自分の居場所を、そのままでいいと言ってくれた。</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>車の中から景色と時刻だけを置き、気持ちの名前を言わずに聴き手に任せる歌詞の書き方。『どちらの家か決めなくていい』という今のテーマの土台になっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>declan_moth</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Colm Tóibín</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>小説『Brooklyn』（2009）。</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>2016 年 9 月 13 日、出発の前日に妹のシアラがくれた。トロント行きの機内で読み終えた。</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>出発の前日に妹がくれた小説。故郷を出た人が、帰ったときにどちらにも半分ずつしかいない感覚。大げさに書かず、手紙と天気で気持ちを運ぶ書き方を受け取った。</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>故郷と移住先の両方を悲劇にしない語り口と、手紙や天気や台所の物で気持ちを運ぶ歌詞の書き方に出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>declan_moth</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
           <t>映画</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Night on Earth</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Jim Jarmusch</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>映画『Night on Earth』（1991）。ロサンゼルス・ニューヨーク・パリ・ローマ・ヘルシンキの同じ夜のタクシーを描く 5 話。</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>2018〜2019 年、ハーバーライト FM の夜勤に就いて間もない頃、局の先輩に勧められて休みの日に観た。</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>局の先輩に教わった 1991 年の映画。同じ夜の同じ時刻に、5 つの都市でタクシーが走る。祖父のタクシーと、自分の 5 時間の時差が 1 本の線でつながった。</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>kino</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>時差の向こうの同じ時刻を 1 曲の中に並べる発想と、車内の会話の間合い。ジャケットに時刻と場所を書き入れる決まりにもつながっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>declan_moth</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Making Love Out of Nothing at All</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Air Supply</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>父が親戚の集まりのカラオケで毎回歌った、フィリピンで愛されたオーストラリアのバンドの曲。2 つの故郷が 1 曲でつながっていると後で気づいた。照れずに大きなメロディを歌い切ること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>kino</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Slave to Love</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Ferry</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Boys and Girls』（1985）の 2 曲目『Slave to Love』。祖父のテープでは 1985 年のラベルの何本にも繰り返し入っている。</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>2021 年の春から夏、父から届いた靴箱のテープを局の制作室で 1 本ずつデジタル化していて、1985 年の録音に何度も出てくるのに気づいた。</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>張らずにささやくような低い声でも、大人の夜の色気と温度は伝わること。柔らかいパッドを何層にも重ねて、声の周りに空気を作る音の作り方。</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>サビの頂点でも声を張らずに息を混ぜて置く歌い方と、A メロ頭の息まじりのささやき。パッドを薄く何層にも重ねて声を包むミックスに出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>declan_moth</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Ang Huling El Bimbo</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Eraserheads</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>2012 年の夏、マニラから来たいとこがギターで教えてくれた曲。昔の友人や台所や路地の固有名詞だけで、青春の終わりを淡々と語る書き方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>kino</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>映画</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>The Castle（1997）</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Rob Sitch</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>空港のそばの家を守る郊外の家族の喜劇。家の価値は値段ではなく暮らしの記憶で決まること。郊外をからかわずに愛するユーモア。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>kino</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Touch This Earth Lightly: Glenn Murcutt in His Own Words（1999）</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Philip Drew</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>学部 2 年の課題図書。大地に軽く触れる建物という考えが、重く支えず軽く持ちこたえる歌の作り方につながった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Plastic Love</t>
+          <t>Violator</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Mariya Takeuchi</t>
+          <t>Depeche Mode</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>2017 年、メルボルンの部屋で動画サイトのおすすめに出てきて、浜松の団地のテレビから流れていた日本語の響きを思い出した。都会の寂しさを明るいグルーヴで包む方法。</t>
+          <t>アルバム『Violator』（1990）。とくに 6 曲目の『Enjoy the Silence』。</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>2012 年、工科カレッジのラジオ実習で局の古い音源を整理していて CD を見つけ、深夜の送出番の空き時間に通して聴いた。</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>低い男声とシンセだけで大きなサビが作れること。アルペジオとベースとパッドに役割をはっきり分ければ、音数が少なくても曲が広がること。</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>16 分のアルペジオに細かさを任せ、低音はシンセベース 1 本だけにする楽器の分担。ギターは 1 本までという決まりと、サビの最終行のオクターブ下のダブルにも出ている。</t>
         </is>
       </c>
     </row>
@@ -16360,7 +17277,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>bia</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -16375,17 +17292,32 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Estrelar</t>
+          <t>Making Love Out of Nothing at All</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Marcos Valle</t>
+          <t>Air Supply</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>サンパウロのアパートで父が日曜の朝に流したレコード。跳ねるベースが体操のように前へ進む明るさ。ベースを始めたとき最初に耳でコピーした。</t>
+          <t>1983 年のベスト盤『Greatest Hits』に新曲として入ったシングル（作詞作曲 Jim Steinman）</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>2002〜2003 年ごろ・4〜5 歳。St Albans の親戚の家のカラオケで、父が毎回締めに歌っていた。オーストラリアのバンドの曲だと知ったのは中等学校に入ってから。</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>父が親戚の集まりのカラオケで毎回歌った、フィリピンで愛されたオーストラリアのバンドの曲。2 つの故郷が 1 曲でつながっていると後で気づいた。照れずに大きなメロディを歌い切ること。</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>サビの頂点の音を照れずに地声で 2 拍伸ばす歌い方と、いちばん高い音に曲中で 1 回だけ届くサビの組み立て。ライブの最後には客が一緒に歌える大きなメロディの曲を必ず置く。</t>
         </is>
       </c>
     </row>
@@ -16397,7 +17329,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>bia</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -16407,22 +17339,37 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>絵</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>大きな曲線の色面の抽象画（サンパウロの美術館で見た連作）</t>
+          <t>Ang Huling El Bimbo</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Tomie Ohtake</t>
+          <t>Eraserheads</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>日本からブラジルへ渡った画家の、1 本の大きな曲線で画面を支える構成。曲を 1 本のベースラインで支えるという考えのもと。</t>
+          <t>アルバム『Cutterpillow』（1995）収録</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>2012 年の夏（12 月）・14 歳。マニラから来たいとこが、部屋でコードを紙に書いて教えてくれた最初の曲の 1 つ。</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>2012 年の夏、マニラから来たいとこがギターで教えてくれた曲。昔の友人や台所や路地の固有名詞だけで、青春の終わりを淡々と語る書き方。</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>感情の言葉を使わず、持ち物や店や地名の固有名詞で場面を埋める歌詞。A メロで同じ音を連打して話すように進むメロディ。</t>
         </is>
       </c>
     </row>
@@ -16434,7 +17381,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>bia</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -16444,22 +17391,37 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>言葉</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Não é o ângulo reto que me atrai, nem a linha reta, dura, inflexível, criada pelo homem. O que me atrai é a curva livre e sensual.</t>
+          <t>How to Make Gravy</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Oscar Niemeyer</t>
+          <t>Paul Kelly</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>高校の美術の先生が黒板に書いた一節。硬い直角ではなく、たわむ曲線で持ちこたえる構造への好み。バンド名の soft の半分はここから。</t>
+          <t>EP『How to Make Gravy』（1996 年 11 月）の表題曲</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>2015 年 12 月・17 歳。祖母が同居を始めた年のクリスマス前に、母の車のラジオで流れた。</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>クリスマスに家族の昼食へ帰れない男が弟へ書く手紙の歌。人の名前と料理と台所の細部だけで、会えない家族を描く書き方。</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>父を説明せず、持ち物（グローブボックス・ロザリオ・給油のレシート）と食べ物で人を描く歌詞。語りかける相手を you に固定して説明しない。</t>
         </is>
       </c>
     </row>
@@ -16471,7 +17433,7 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>bia</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -16481,22 +17443,37 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>映画</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Drive My Car（2021）</t>
+          <t>Salad Days</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>濱口竜介（Ryusuke Hamaguchi）</t>
+          <t>Mac DeMarco</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>2022 年、メルボルンの映画館で、日本語の台詞を字幕を見なくても半分聞き取れたことに泣いた。車の中だから話せることがある、という感覚。</t>
+          <t>アルバム『Salad Days』（2014）の表題曲</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>2014 年の半ば・16 歳。いとこが部屋のスピーカーで流し、揺れるギターの音の出し方を 2 人で調べた。父の工場の閉鎖が発表された年。</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>薄く揺れるクリーンのギターと、疲れや不安を力まずに軽く歌う声。</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>コーラスを薄く常にかけたクリーンのカッティング。重い話ほど明るいテンポで力まずに歌う、キノの話すような歌い方。</t>
         </is>
       </c>
     </row>
@@ -16508,7 +17485,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>tav</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -16518,22 +17495,37 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>映画</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Wandering Eye</t>
+          <t>The Castle（1997）</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Fat Freddy's Drop</t>
+          <t>Rob Sitch</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>2005 年ごろ、父が現場のトラックでずっと流していたニュージーランドのバンドの曲。拍の後ろにゆったり座るグルーヴと、急がないことの強さ。</t>
+          <t>1997 年のオーストラリア映画。メルボルン空港のそばの家が舞台</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>2012 年・14 歳。中等学校の英語の授業で観て、そのあと家族で DVD を何度も観た。</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>空港のそばの家を守る郊外の家族の喜劇。家の価値は値段ではなく暮らしの記憶で決まること。郊外をからかわずに愛するユーモア。</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>郊外の暮らしを笑いながらも見下さない歌詞のユーモア（パイの好みや給油のレシート）。ライブの MC で家族と郊外の話を自虐せずに笑いにする話し方。</t>
         </is>
       </c>
     </row>
@@ -16545,7 +17537,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>tav</t>
+          <t>kino</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -16555,22 +17547,37 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>本</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Weather With You</t>
+          <t>Touch This Earth Lightly: Glenn Murcutt in His Own Words（1999）</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Crowded House</t>
+          <t>Philip Drew</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>移住の日、Napier から空港へ向かう車で母がかけた曲。故郷を離れても天気は連れていける、という気持ちと、男声のハーモニーの重ね方。</t>
+          <t>1999 年刊の建築家の対話の本。学部 2 年の設計課題の参考図書</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>2018 年 3 月・19 歳。学部 2 年の設計の授業で講師に勧められ、大学図書館で借りた。</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>学部 2 年の課題図書。大地に軽く触れる建物という考えが、重く支えず軽く持ちこたえる歌の作り方につながった。</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>ギターを 3 音の小さな和音にして音を重ねすぎず、隙間を残すアレンジ。ジャケットや字幕の細い寸法線だけの軽い見た目。</t>
         </is>
       </c>
     </row>
@@ -16582,7 +17589,7 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>tav</t>
+          <t>bia</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -16597,17 +17604,32 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Dean Town</t>
+          <t>Plastic Love</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Vulfpeck</t>
+          <t>Mariya Takeuchi</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>大学 1 年のとき、製図室でキノとビアに見せた演奏動画。最小の編成でベースとドラムが曲の骨組みになれること。</t>
+          <t>アルバム『VARIETY』（1984）収録。編曲は山下達郎</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>2017 年・20 歳。Carlton のワンルームで、動画サイトのおすすめに出てきた。</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>2017 年、メルボルンの部屋で動画サイトのおすすめに出てきて、浜松の団地のテレビから流れていた日本語の響きを思い出した。都会の寂しさを明るいグルーヴで包む方法。</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>跳ねる 16 分のベースに寂しい言葉を明るく乗せる曲の設計。ビアのハモりの、日本語の歌のような柔らかい母音。</t>
         </is>
       </c>
     </row>
@@ -16619,7 +17641,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>tav</t>
+          <t>bia</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -16629,22 +17651,37 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>映画</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Boy（2010）</t>
+          <t>Estrelar</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Taika Waititi</t>
+          <t>Marcos Valle</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>11 歳のとき、Napier の映画館で家族全員で観た。ニュージーランドの田舎の暮らしを、悲しい話でも笑いながら描くやり方。</t>
+          <t>アルバム『Marcos Valle』（1983）の 1 曲目。Leon Ware との共作</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>2011 年・14 歳。サンパウロ Saúde のアパートで、父が日曜の朝にかけていたレコード。ベースを始めた年に最初に耳でコピーした。</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>サンパウロのアパートで父が日曜の朝に流したレコード。跳ねるベースが体操のように前へ進む明るさ。ベースを始めたとき最初に耳でコピーした。</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>オクターブで跳ねるベースラインと、サビ前に 1 オクターブ上へスライドして戻る癖。体を前へ押すような明るい 16 ビート。</t>
         </is>
       </c>
     </row>
@@ -16656,402 +17693,567 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Jazz Carnival</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Azymuth</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Light as a Feather』（1979）収録</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>2011 年・14 歳。ベースを教えてくれたサンパウロの楽器店の店主が、店のレコードで『ベースが歌っているのを聴け』とかけた。</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>ブラジルの 3 人組の、ベースが主旋律のように歌いながらグルーヴを支える演奏。少人数でも大きく鳴る編成。</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>ギターと同じリフをユニゾンで弾く 2 回目のサビのあとの間奏と、歌の隙間でベースが短く歌うフィル。3 人だけで鳴らす編成への自信。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>都会</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>大貫妙子（Taeko Ohnuki）</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『SUNSHOWER』（1977）の 4 曲目</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>2017 年・20 歳。Plastic Love のあと、70〜80 年代の日本の都会の音楽を掘っていて見つけた。</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>都会の暮らしを少し離れて見つめる歌詞と、細かく動くリズムの上で落ち着いて歌う女声。</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>ハモりで返す 1 行を、熱くならず少し距離を取った声で歌うこと。シンコペーションの多いベースに言葉数の少ないコーラスを乗せるアレンジ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>絵</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>大きな曲線の色面の抽象画（サンパウロの美術館で見た連作）</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Tomie Ohtake</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>1990 年代以降の大きな曲線の色面の抽象画（サンパウロの Instituto Tomie Ohtake の展示）</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>2014 年・17 歳。高校の美術の見学で Pinheiros の Instituto Tomie Ohtake に行った。</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>日本からブラジルへ渡った画家の、1 本の大きな曲線で画面を支える構成。曲を 1 本のベースラインで支えるという考えのもと。</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>曲の断面図を 1 本の曲線のベースラインから描き始める作り方。ジャケットに寸法線を 1 本だけ重ねる見た目の決まり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Não é o ângulo reto que me atrai, nem a linha reta, dura, inflexível, criada pelo homem. O que me atrai é a curva livre e sensual.</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Oscar Niemeyer</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>建築家が自分の曲線の建築について書いた短い詩の冒頭の一節（ブラジルで広く引用される）</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>2015 年・18 歳。サンパウロの高校の美術の先生が黒板に書いた。</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>高校の美術の先生が黒板に書いた一節。硬い直角ではなく、たわむ曲線で持ちこたえる構造への好み。バンド名の soft の半分はここから。</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>バンド名の soft。ベースを直線的に刻まず、スライドで音と音をつなぐ弾き方と、断面図の曲線。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>映画</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Drive My Car（2021）</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>濱口竜介（Ryusuke Hamaguchi）</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>2021 年の日本映画。村上春樹の短編が原作</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>2022 年・25 歳。メルボルンの映画館で 1 人で観た。</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>2022 年、メルボルンの映画館で、日本語の台詞を字幕を見なくても半分聞き取れたことに泣いた。車の中だから話せることがある、という感覚。</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>移動中の車内の会話と沈黙を歌うテーマ。両親をバンに乗せた日の、父が黙って頷き続ける歌の種の書き方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
           <t>tav</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Wandering Eye</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Fat Freddy's Drop</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Based on a True Story』（2005）収録</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>2005〜2006 年・6〜7 歳。Napier で父の現場のトラックの CD で毎日流れていた。</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>2005 年ごろ、父が現場のトラックでずっと流していたニュージーランドのバンドの曲。拍の後ろにゆったり座るグルーヴと、急がないことの強さ。</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>スネアの 2 拍 4 拍をわずかに遅らせて座らせる叩き方と、テンポを上げずに盛り上げるサビ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Weather With You</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Crowded House</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Woodface』（1991）収録</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>2012 年 1 月・13 歳。移住の日に Napier から空港へ向かう車で母がかけた。</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>移住の日、Napier から空港へ向かう車で母がかけた曲。故郷を離れても天気は連れていける、という気持ちと、男声のハーモニーの重ね方。</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>タヴのコーラスの低いユニゾンの重ね方と、離れることを明るい長調で歌う曲への好み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Dean Town</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Vulfpeck</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『The Beautiful Game』（2016）収録・演奏動画</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>2017 年・18 歳。学部 1 年の製図室で、自分のノートパソコンでキノとビアに見せた。</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>大学 1 年のとき、製図室でキノとビアに見せた演奏動画。最小の編成でベースとドラムが曲の骨組みになれること。</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>ギターとベースのユニゾンのリフにドラムがキメで合わせる間奏と、ベースとドラムだけで始まるイントロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Use Me</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Bill Withers</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Still Bill』（1972）収録</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>2013 年・14 歳。Frankston の中等学校のステージバンドの先生が『少ない音で揺らせ』とグルーヴの宿題に出した。</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>同じ短いパターンを繰り返し、強弱だけで揺らすドラム。歌の隙間を埋めない伴奏。</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>A メロで同じ 2 小節を変えずに繰り返し、ハイハットの開け閉めと強弱だけで展開を作る叩き方。フィルを 1 拍以内に収める癖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>映画</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Boy（2010）</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Taika Waititi</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>2010 年のニュージーランド映画</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>2010 年・11 歳。Napier の映画館で家族全員で観た。</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>11 歳のとき、Napier の映画館で家族全員で観た。ニュージーランドの田舎の暮らしを、悲しい話でも笑いながら描くやり方。</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>ライブの MC で悲しい話も笑いながら短く話すタヴの話し方と、動画の字幕の素朴なユーモア。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>本</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Shop Class as Soulcraft（2009）</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>Matthew B. Crawford</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>2009 年刊のアメリカの哲学者の本</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>2021 年・22 歳。父が腰を痛めて代わりに現場に出ていたころ、見習いになるか迷って読んだ。</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>修士を出て見習いになるか迷っていた 2021 年に読んだ。手で作る仕事に頭も誇りも要るという考えが、背中を押した。</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Woodface</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Crowded House</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>父の車のカセット。オタゴの砂利道を 1 時間走るあいだ、兄と後部座席でハモりの真似をした。兄弟の声が重なる気持ちよさと、自分の国の人が作った歌が世界で鳴るという実感。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Submarine Bells</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>The Chills</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>ダニーデンの寄宿学校の上級生が貸してくれた CD。坂と雨の多い自分たちの街から生まれた、少し陰りのある明るいギターの音。自分の町の天気を歌っていいと知った。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Time (The Revelator)</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Gillian Welch</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>大学時代、毛刈り隊の先輩に教わったアルバム。男女 2 人だけで声とギターを重ねる最小の編成と、言葉を急がない歌い方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>To the Is-Land</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Janet Frame</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>オタゴの町で育った作家の自伝。寄宿学校の図書室で読み、貧しさや田舎の暮らしの中にこそ言葉の豊かさがあると知った。自分の土地にも書くことがあると思えた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>絵</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>セントラル・オタゴの風景画（マニオトト平原を描いた作品群）</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Grahame Sydney</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>実家の居間にあった複製画。何もない平原と高い空と、ぽつんと立つ小屋。余白を怖がらないことを受け取った。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>言葉</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>Knit on with confidence and hope, through all crises.</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Elizabeth Zimmermann</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>祖母が編み物の本の見返しに書き写していた一文。手を動かし続ければ、困ったときもなんとかなる。腱鞘炎の冬にも何度も読み返した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Ysbryd Solfa</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Meic Stevens</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>同じソルヴァ生まれの歌い手が、2002 年に村での子ども時代を歌ったアルバム。12 歳のとき父が買ってきた。自分の港の名前が歌になる誇りと、ウェールズ語の歌の柔らかい子音。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Solid Air</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>John Martyn</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>父が作業場で鉋をかけながら回していたレコード。指弾きのギターが波のように反復して揺れる感じと、声を楽器のように滲ませる歌い方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Damien Rice</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>14 歳でギターを買った頃に聴き込んだアルバム。男女の声が小さな部屋で寄り添う距離感と、静かな曲でも熱が伝わること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Under Milk Wood</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Dylan Thomas</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>母が毎年冬に朗読の録音を流していた、ウェールズの小さな漁村の一日を描く声の劇。村の一人ひとりの暮らしの細部を、音と言葉の響きで描く書き方。</t>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>機材ケースや物販の棚や自作のスネアを自分の手で作ること。演奏でも見せる技より持ちこたえる確かさを選ぶ姿勢。</t>
         </is>
       </c>
     </row>
@@ -17063,297 +18265,1197 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Woodface</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Crowded House</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Woodface』（1991）。とくに 5 曲目『Weather With You』と 7 曲目『Four Seasons in One Day』のフィン兄弟の 2 声</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>2000 年前後（4〜6 歳）・オタゴの牧場で父の車のカセットを繰り返し聴いた。砂利道を走る 1 時間、兄と後部座席でハモりの真似をした。</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>父の車のカセット。オタゴの砂利道を 1 時間走るあいだ、兄と後部座席でハモりの真似をした。兄弟の声が重なる気持ちよさと、自分の国の人が作った歌が世界で鳴るという実感。</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>上のハモりを主旋律の 3 度上にぴたりと平行に付ける癖。A メロを 1 人で低く語り、サビで 2 声が開く曲の形。天気を気持ちの比喩にしても重くしない歌詞の温度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Submarine Bells</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>The Chills</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Submarine Bells』（1990）。1 曲目の『Heavenly Pop Hit』</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>2009 年頃（14 歳）・ダニーデンの寄宿学校で、ギターを教えてくれた上級生が CD を貸してくれた。</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>ダニーデンの寄宿学校の上級生が貸してくれた CD。坂と雨の多い自分たちの街から生まれた、少し陰りのある明るいギターの音。自分の町の天気を歌っていいと知った。</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>長調の明るい刻みの中に 1 つだけ陰る和音を置く感覚。歌詞に坂や雨や霜など自分の町の天気をそのまま書き込むこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Time (The Revelator)</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Gillian Welch</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Time (The Revelator)』（2001）。3 曲目の『Dear Someone』</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>2014 年の夏（19 歳）・南島の牧場を回る毛刈り隊の宿舎で、先輩がスマートフォンで流してくれた。</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>大学時代、毛刈り隊の先輩に教わったアルバム。男女 2 人だけで声とギターを重ねる最小の編成と、言葉を急がない歌い方。</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>2 人だけの声とギターを基本の編成にする考え方。言葉を拍の少し後ろに置いて急がない歌い方。ギター 1 本で隙間を残す伴奏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Here's the Tender Coming</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>The Unthanks</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Here's the Tender Coming』（2009）。伝承歌の表題曲</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>2018 年 5 月（23 歳）・ペンリンの毛糸店で働き始めた週に、店主が店の CD プレーヤーで流していた。</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>北イングランドの姉妹が、漁や港の暮らしの伝承歌を少ない伴奏で歌うアルバム。姉妹の声の溶け方と、自分の訛りを隠さずに歌っていいこと。海の仕事を、陸で待つ女性の目線で歌う距離。</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>ニュージーランドの母音を直さずに歌うこと。1 枚に 1 曲は無伴奏の歌い出しを入れること。漁師やギグの漕ぎ手の暮らしを、少し離れて見つめる歌詞の目線。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>To the Is-Land</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Janet Frame</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>自伝 3 部作の第 1 巻『To the Is-Land』（1982）</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>2010 年頃（15 歳）・ダニーデンの寄宿学校の図書室で、消灯前に少しずつ読んだ。</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>オタゴの町で育った作家の自伝。寄宿学校の図書室で読み、貧しさや田舎の暮らしの中にこそ言葉の豊かさがあると知った。自分の土地にも書くことがあると思えた。</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>地名や家の物を恥ずかしがらずに歌詞へ入れること。失敗や貧しさを飾らず、出来事だけで書く語り口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>絵</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>セントラル・オタゴの風景画（マニオトト平原を描いた作品群）</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Grahame Sydney</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>マニオトト平原を描いたテンペラ画の複製（『July on the Maniototo』など）</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>物心ついた頃から・実家の居間の壁に母が掛けていた複製画。</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>実家の居間にあった複製画。何もない平原と高い空と、ぽつんと立つ小屋。余白を怖がらないことを受け取った。</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>イントロとアウトロに音を詰めない余白。ジャケットや写真で上 2/3 を空や壁の余白にする構図。景色を描きすぎず小屋 1 つで語る歌詞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Knit on with confidence and hope, through all crises.</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Elizabeth Zimmermann</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>アメリカの編み物作家の座右の言葉として、編み手のあいだで広く知られる一文</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>2002 年の冬休み（7 歳）・ダニーデンの祖母の家で編み物を習ったとき、本の見返しの書き写しを見た。意味が身に染みたのは腱鞘炎の 2023 年の冬。</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>祖母が編み物の本の見返しに書き写していた一文。手を動かし続ければ、困ったときもなんとかなる。腱鞘炎の冬にも何度も読み返した。</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>つらい出来事を歌う曲でも、最後の行を『編み始める』のような手の動作で前へ向けて終える歌詞の癖。配信の終わりの挨拶。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
           <t>gethin</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Ysbryd Solva</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Meic Stevens</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Ysbryd Solva』（2002・ウェールズ語）</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>2002 年の夏（12 歳）・地元セント・デイヴィッズで全国アイステズヴォッドが開かれた年に、父が買ってきた。</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>同じソルヴァ生まれの歌い手が、2002 年に村での子ども時代を歌ったアルバム。12 歳のとき父が買ってきた。自分の港の名前が歌になる誇りと、ウェールズ語の歌の柔らかい子音。</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>ウェールズ語の柔らかい子音の発音を英語の歌詞にも持ち込む下ハモの声。港の名前や道路の番号をそのまま歌に入れる勇気。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Solid Air</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>John Martyn</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Solid Air』（1973）。1 曲目の表題曲と、テープ・ディレイで指弾きを揺らした 4 曲目『I'd Rather Be the Devil』</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>1990 年代半ば（5 歳頃から）・ソルヴァの父の作業場のレコードプレーヤーで、鉋屑を掃きながら聴いた。</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>父が作業場で鉋をかけながら回していたレコード。指弾きのギターが波のように反復して揺れる感じと、声を楽器のように滲ませる歌い方。</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>親指の低音の反復を崩さず、その上で和音を波のように揺らす指弾きの型。語尾を滲ませて楽器に溶かす下ハモの歌い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Damien Rice</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『O』（2002）。2 曲目『Volcano』の男女の声の掛け合い</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>2004 年（14 歳）・初めてのギターを買った頃、セント・デイヴィッズの中等学校のバンド仲間に CD を借りた。</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>14 歳でギターを買った頃に聴き込んだアルバム。男女の声が小さな部屋で寄り添う距離感と、静かな曲でも熱が伝わること。</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>ブリッジで楽器が抜けて声 2 人と持続音だけになる曲の形。マイクに近づいて小さな声で歌う録り方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Penguin Eggs</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Nic Jones</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Penguin Eggs』（1980）。1 曲目『Canadee-I-O』と 3 曲目『The Humpback Whale』</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>2016 年の冬（26 歳）・木曜のパブのセッションに通い始めた頃、仕切り役の 70 代のアコーディオン弾きに『港の歌をやるならこれを聴け』とレコードを渡された。</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>指弾きの親指が打楽器のように弦を叩く推進力と、変則チューニングで開放弦を鳴らし続ける和音。海と鯨と漁の伝承歌を、感情を足さずに淡々と語る歌い方。</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>右手の親指で低音弦を短く弾いて打楽器の代わりにする奏法。D を基にした変則チューニングで開放弦を鳴らし続ける伴奏。ゲシンのパートの、出来事だけを語る伝承歌のような歌詞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Under Milk Wood</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Dylan Thomas</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>声の劇『Under Milk Wood』。1954 年 1 月に BBC で初めて放送された Richard Burton が語り手の録音</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>子どもの頃（1990 年代）から毎年冬・ソルヴァの台所で母が流していた。</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>母が毎年冬に朗読の録音を流していた、ウェールズの小さな漁村の一日を描く声の劇。村の一人ひとりの暮らしの細部を、音と言葉の響きで描く書き方。</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>ゲシンが書き換える 2〜3 行に多い、港の人の小さな動作を並べる書き方。意味より子音の響きで言葉を選ぶ癖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="38" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>I have seen the sun break through / to illuminate a small field / for a while, and gone my way / and forgotten it.（The Bright Field）</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>R. S. Thomas</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>詩『The Bright Field』（詩集『Laboratories of the Spirit』1975 年）</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>2011 年（21 歳）・ファルマスの専門学校に通っていた頃、町の図書館で借りた詩集で。</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>専門学校の頃、ウェールズの詩人の詩集で出会った一節。ほんの短い光を見過ごさずに立ち止まること。急がない仕事の理由になった。</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>サビの手前で 1 小節だけ立ち止まってハミングする曲の習慣。速くしたがるアイラに対して、遅いテンポを選ぶ理由。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>父のレコード棚のハイライフ（1950〜60 年代の録音）</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>E.T. Mensah &amp; The Tempos</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>代表曲「All For You」（1950 年代の録音。1956 年にアクラでルイ・アームストロングを迎えたときにも演奏された曲）と、同じ頃のダンスバンドの録音</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>2003〜2007 年（6〜10 歳）リーズ・ハーヘルズの長屋で。日曜の朝、父がクマシから持ってきたレコードをかけながら家族 4 人で床を磨いた。</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
         <is>
           <t>日曜の朝、父がクマシから持ってきたレコードをかけながら家族で床を磨いた。管とギターが同じ短い動機を繰り返し、踊る人を急かさないこと。曲に入れる 2 音のギターはここから来ている。</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>各曲に 1 回だけ入れる 2 音のハイライフ風ギターのリフと、声の切れ端のフックを同じ短い動機のまま繰り返して急かさない作り方。管とギターの掛け合いは、2 小節の問いに 2 小節の答えを返す静かなコールアンドレスポンスに残っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B41" s="27" t="inlineStr">
+      <c r="B53" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Untrue（アルバム）</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>Burial</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Untrue』（2007 年・Hyperdub）の 2 曲目「Archangel」</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>2011 年（14 歳）リーズ・ラウンドヘイ。ペッカムのいとこアマが焼いてくれた南ロンドンの夜の電子音楽の CD で、ヘッドホンで夜に聴いた。</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>14 歳のとき、ペッカムのいとこが焼いてくれた CD。生まれた街の夜行バスの音がした。声を細かく切ってピッチを変えると、言葉より気持ちが残ると知った。</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>声を 1 拍ずつ切ってピッチを変え、旋律の代わりに並べる作り方の出発点。曲の下に敷くかすかなレコードノイズと、街灯の流れる窓のような暗く湿った質感にも出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>Can You Feel It</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>Mr. Fingers</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>Mr. Fingers 名義の「Can You Feel It」（1986 年・Trax Records。EP『Washing Machine』に収録されたインストゥルメンタル版）</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>2013 年（16 歳）リーズ・ラウンドヘイの幼なじみの友人の兄の部屋で、レコードで聴いた。</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
         <is>
           <t>16 歳、リーズの友人の兄の部屋で聴いた 80 年代シカゴの録音。歌が無くても、同じ和音の繰り返しが人を前へ進ませる。説教しない温かさがハウスの核だと思った。</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>同じ和音を繰り返しながら前へ進ませるエレピのコードの組み方と、歌の無いハウスの温かさ。終わりのコードを解決しきらずに次の曲へつなぐアウトロもここから来ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B43" s="27" t="inlineStr">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Selected Ambient Works 85–92（アルバム）</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Aphex Twin</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Selected Ambient Works 85–92』（1992 年・Apollo）の 1 曲目「Xtal」</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>2016 年秋（19 歳）シェフィールドの大学の模型工房で、技術職員が夜の作業中に流していた。そのあと卒業まで、夜通し模型を作る晩に繰り返し聴いた。</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>言葉の無い息のような声が、柔らかいビートの上で空気として漂っていること。声は歌わなくても、部屋の温度を決められると知った。</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>声の切れ端を『歌』ではなく背景の空気として置く音量の決め方と、角の取れたキックにテープの揺れを薄くかける質感。100〜118 BPM の柔らかい帯域を選ぶ癖にも出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>There Is Love in You（アルバム）</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Four Tet</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『There Is Love in You』（2010 年・Domino）の 1 曲目「Angel Echoes」</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>2020 年 5 月（23 歳）ロックダウン中のレイトン。SoundCloud に上げた『Plan 03』を聴いたオンラインの宅録仲間が『これ知ってる？』と送ってきた。</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>短い声の断片を楽器のように重ね、ループの中で少しずつ形を変えて旋律にするやり方。</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>曲名から取った 1〜3 語の切れ端を半音ずつ上げながら 4 回繰り返すフックと、16 小節ごとに 1 つだけ切れ端の並びを変えていく展開。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Spaces（アルバム）</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Nils Frahm</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>ライブ録音のアルバム『Spaces』（2013 年・Erased Tapes）の 2 曲目「Says」</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>2023 年秋（26 歳）ファンミが深夜番組の最後にかけたのを聴いた。12 月から父の入院で隔週に乗った夜行バスで、一番多く聴いた。</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>1 つのアルペジオが 8 分かけて少しずつ開いていき、何も起きないようで景色が変わっていくこと。</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>42 分の切れ目のないミックスの組み方と、新しい音を 16 小節ごとに 1 つだけ足し引きする規則。夜行バス 1 本ぶんを途切れずにつなぐ長い作品の構想の土台。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>本</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>Species of Spaces and Other Pieces（さまざまな空間）</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>Georges Perec</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>英訳選集『Species of Spaces and Other Pieces』（1997 年・Penguin Books、ジョン・スタロック編訳）。表題作の原著『Espèces d'espaces』は 1974 年</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>2015 年（18 歳）シェフィールドの大学 1 年。建築学科の読書リストにあり、大学図書館で借りて延長を繰り返した。</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>大学 1 年で読んだ。ページ・ベッド・部屋・通りと、ありふれた空間を一つずつ書き出していく方法。曲名を空間の単位と時刻で付ける癖の元。</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Courtyard, 02:40 や Services at Three のように、空間の単位と時刻を組み合わせて曲名を付ける癖。スケッチブックの平面図の余白に、言葉を部屋の名前のように書き出す習慣にも出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>鑿戶牖以為室，當其無，有室之用。</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>老子『道徳経』第 11 章</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>老子『道徳経』第 11 章（車輪の轂・器・部屋のたとえで『無』の用を説く章）の後半の一句</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>2015 年（18 歳）シェフィールドの大学 1 年の建築史の講義。講師が英訳と並べて黒板に書いた。</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
         <is>
           <t>1 年の建築史の講義で、講師が英訳と並べて黒板に書いた。戸と窓をくり抜いて部屋を作る、部屋が役に立つのは何も無いところ。HOLLOWPLAN という名前の半分はここにある。</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>HOLLOWPLAN という名前と、曲のちょうど真ん中に置く『中庭』の 8 小節。キックとベースを遠ざけても無音にはしない『使うための空白』の考え方そのもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B45" s="27" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>絵（彫刻）</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>House（1993 年。ロンドン東部ボウのテラスハウスの内部をコンクリートで型取りした作品）</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>Rachel Whiteread</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>『House』（1993 年。ボウのグローブ・ロード 193 番地。同年のターナー賞を受け、1994 年 1 月に取り壊された）</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>2018 年（21 歳）ロンドンに来た年、クラーケンウェルの設計事務所の資料棚にあった写真集で知った。</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
         <is>
           <t>ロンドンに来た 2018 年に写真集で知った。家の中の空気をそのまま固めた形。空いているところにも形がある、と模型の仕事で毎日思い出す。</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>曲ごとに作る手のひら大のバルサの『部屋の模型』と、中央を空けたジャケットの構図。音では、残響の尾を部屋の空気の形として残し、空白を『形のあるもの』として扱う編曲に出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="inlineStr">
         <is>
           <t>hollowplan</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>abena</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>映画</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Columbus（2017 年）</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>Kogonada</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>大学 3 年の冬休み、リーズの古い映画館で父と見た唯一の映画（父は途中で寝た）。モダニズムの建物の前で、人が黙って立っている時間を急がない。何も起きない場面の撮り方。</t>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>映画『Columbus』（2017 年・監督と脚本 Kogonada。インディアナ州コロンバスのモダニズム建築を舞台にした長編第 1 作）</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>2018 年 12 月（21 歳）実務研修の年の年末、リーズに帰省した折に古い映画館で父と見た（英国公開は 2018 年 10 月）。</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>実務研修の年の年末、帰省したリーズの古い映画館で父と見た唯一の映画（父は途中で寝た）。モダニズムの建物の前で、人が黙って立っている時間を急がない。何も起きない場面の撮り方。</t>
+        </is>
+      </c>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>何も起きない時間を急がない曲の入り方（イントロ 8 小節で吸う息とローパスのエレピだけ）と、動かないカメラで建物と人を撮るジャケットや動画の静止した構図。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G46"/>
-  <conditionalFormatting sqref="C2:C545">
+  <autoFilter ref="A1:J61"/>
+  <conditionalFormatting sqref="C2:C560">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"提案"</formula>
     </cfRule>
@@ -17370,17 +19472,17 @@
       <formula>"反映済み"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:G545">
+  <conditionalFormatting sqref="A2:J560">
     <cfRule type="expression" priority="6" dxfId="5">
       <formula>$C2="却下"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:G545">
+  <conditionalFormatting sqref="B2:J560">
     <cfRule type="expression" priority="7" dxfId="6">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A545">
+  <conditionalFormatting sqref="A2:A560">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"nao_easterly"</formula>
     </cfRule>
@@ -17398,14 +19500,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D545" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
+    <dataValidation sqref="D2:D560" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
       <formula1>"音楽,本,絵,映画,言葉"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C545" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
+    <dataValidation sqref="C2:C560" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
       <formula1>"提案,採用,保留,却下,反映済み"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アーティスト" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="メンバー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人生年表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="デビューの経緯" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="傷・タトゥー" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="影響" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歌の種" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歌詞の試作" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近況" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考曲の候補" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声と曲づくり" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見た目" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更の提案" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="はじめに" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="アーティスト" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="メンバー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="人生年表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="デビューの経緯" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="傷・タトゥー" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="影響" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="歌の種" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="歌詞の試作" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="近況" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="参考曲の候補" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="声と曲づくり" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="見た目" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="変更の提案" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人生年表'!$A$1:$L$82</definedName>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>テーマの中心は『時間の手触り』（夜勤の時刻・5 時間の時差・カセット）。80 年代の再現ではなく、今の夜を 80 年代の質感で歌う。顔出しなし。本名は設定の中だけで使い、配信名は DECLAN MOTH。</t>
+          <t>テーマの軸は『時間の手触り』（夜勤の時刻・5 時間の時差・カセット）。80 年代の再現ではなく、今の夜を 80 年代の質感で歌う。顔出しなし。本名は設定の中だけで使い、配信名は DECLAN MOTH。</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -17064,14 +17064,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>declan_fay</t>
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>declan</t>
+          <t>abena</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -17086,44 +17086,44 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Slave to Love</t>
+          <t>父のレコード棚のハイライフ（1950〜60 年代の録音）</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Bryan Ferry</t>
+          <t>E.T. Mensah &amp; The Tempos</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Boys and Girls』（1985）の 2 曲目『Slave to Love』。父のテープでは 1985 年のラベルの何本にも繰り返し入っている。</t>
+          <t>代表曲「All For You」（1950 年代の録音。1956 年にアクラでルイ・アームストロングを迎えたときにも演奏された曲）と、同じ頃のダンスバンドの録音</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>2021 年の春から夏、母から届いた靴箱のテープを局の制作室で 1 本ずつデジタル化していて、1985 年の録音に何度も出てくるのに気づいた。</t>
+          <t>2003〜2007 年（6〜10 歳）リーズ・ハーヘルズの長屋で。日曜の朝、父がクマシから持ってきたレコードをかけながら家族 4 人で床を磨いた。</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>張らずにささやくような低い声でも、大人の夜の色気と温度は伝わること。柔らかいパッドを何層にも重ねて、声の周りに空気を作る音の作り方。</t>
+          <t>日曜の朝、父がクマシから持ってきたレコードをかけながら家族で床を磨いた。管とギターが同じ短い動機を繰り返し、踊る人を急かさないこと。曲に入れる 2 音のギターはここから来ている。</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>サビの頂点でも声を張らずに息を混ぜて置く歌い方と、A メロ頭の息まじりのささやき。パッドを薄く何層にも重ねて声を包むミックスに出ている。</t>
+          <t>各曲に 1 回だけ入れる 2 音のハイライフ風ギターのリフと、声の切れ端のフックを同じ短い動機のまま繰り返して急かさない作り方。管とギターの掛け合いは、2 小節の問いに 2 小節の答えを返す静かなコールアンドレスポンスに残っている。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>declan_fay</t>
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>declan</t>
+          <t>abena</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -17138,32 +17138,32 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Violator</t>
+          <t>Untrue（アルバム）</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Depeche Mode</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Violator』（1990）。とくに 6 曲目の『Enjoy the Silence』。</t>
+          <t>アルバム『Untrue』（2007 年・Hyperdub）の 2 曲目「Archangel」</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>2012 年、工科カレッジのラジオ実習で局の古い音源を整理していて CD を見つけ、深夜の送出番の空き時間に通して聴いた。</t>
+          <t>2011 年（14 歳）リーズ・ラウンドヘイ。ペッカムのいとこアマが焼いてくれた南ロンドンの夜の電子音楽の CD で、ヘッドホンで夜に聴いた。</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>低い男声とシンセだけで大きなサビが作れること。アルペジオとベースとパッドに役割をはっきり分ければ、音数が少なくても曲が広がること。</t>
+          <t>14 歳のとき、ペッカムのいとこが焼いてくれた CD。生まれた街の夜行バスの音がした。声を細かく切ってピッチを変えると、言葉より気持ちが残ると知った。</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>16 分のアルペジオに細かさを任せ、低音はシンセベース 1 本だけにする楽器の分担。ギターは 1 本までという決まりと、サビの最終行のオクターブ下のダブルにも出ている。</t>
+          <t>声を 1 拍ずつ切ってピッチを変え、旋律の代わりに並べる作り方の出発点。曲の下に敷くかすかなレコードノイズと、街灯の流れる窓のような暗く湿った質感にも出ている。</t>
         </is>
       </c>
     </row>
@@ -17190,32 +17190,32 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>父のレコード棚のハイライフ（1950〜60 年代の録音）</t>
+          <t>Can You Feel It</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>E.T. Mensah &amp; The Tempos</t>
+          <t>Mr. Fingers</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>代表曲「All For You」（1950 年代の録音。1956 年にアクラでルイ・アームストロングを迎えたときにも演奏された曲）と、同じ頃のダンスバンドの録音</t>
+          <t>Mr. Fingers 名義の「Can You Feel It」（1986 年・Trax Records。EP『Washing Machine』に収録されたインストゥルメンタル版）</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>2003〜2007 年（6〜10 歳）リーズ・ハーヘルズの長屋で。日曜の朝、父がクマシから持ってきたレコードをかけながら家族 4 人で床を磨いた。</t>
+          <t>2013 年（16 歳）リーズ・ラウンドヘイの幼なじみの友人の兄の部屋で、レコードで聴いた。</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>日曜の朝、父がクマシから持ってきたレコードをかけながら家族で床を磨いた。管とギターが同じ短い動機を繰り返し、踊る人を急かさないこと。曲に入れる 2 音のギターはここから来ている。</t>
+          <t>16 歳、リーズの友人の兄の部屋で聴いた 80 年代シカゴの録音。歌が無くても、同じ和音の繰り返しが人を前へ進ませる。説教しない温かさがハウスの核だと思った。</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>各曲に 1 回だけ入れる 2 音のハイライフ風ギターのリフと、声の切れ端のフックを同じ短い動機のまま繰り返して急かさない作り方。管とギターの掛け合いは、2 小節の問いに 2 小節の答えを返す静かなコールアンドレスポンスに残っている。</t>
+          <t>同じ和音を繰り返しながら前へ進ませるエレピのコードの組み方と、歌の無いハウスの温かさ。終わりのコードを解決しきらずに次の曲へつなぐアウトロもここから来ている。</t>
         </is>
       </c>
     </row>
@@ -17237,37 +17237,37 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>本</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Untrue（アルバム）</t>
+          <t>Species of Spaces and Other Pieces（さまざまな空間）</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Georges Perec</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Untrue』（2007 年・Hyperdub）の 2 曲目「Archangel」</t>
+          <t>英訳選集『Species of Spaces and Other Pieces』（1997 年・Penguin Books、ジョン・スタロック編訳）。表題作の原著『Espèces d'espaces』は 1974 年</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>2011 年（14 歳）リーズ・ラウンドヘイ。ペッカムのいとこアマが焼いてくれた南ロンドンの夜の電子音楽の CD で、ヘッドホンで夜に聴いた。</t>
+          <t>2015 年（18 歳）シェフィールドの大学 1 年。建築学科の読書リストにあり、大学図書館で借りて延長を繰り返した。</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>14 歳のとき、ペッカムのいとこが焼いてくれた CD。生まれた街の夜行バスの音がした。声を細かく切ってピッチを変えると、言葉より気持ちが残ると知った。</t>
+          <t>大学 1 年で読んだ。ページ・ベッド・部屋・通りと、ありふれた空間を一つずつ書き出していく方法。曲名を空間の単位と時刻で付ける癖の元。</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>声を 1 拍ずつ切ってピッチを変え、旋律の代わりに並べる作り方の出発点。曲の下に敷くかすかなレコードノイズと、街灯の流れる窓のような暗く湿った質感にも出ている。</t>
+          <t>Courtyard, 02:40 や Services at Three のように、空間の単位と時刻を組み合わせて曲名を付ける癖。スケッチブックの平面図の余白に、言葉を部屋の名前のように書き出す習慣にも出ている。</t>
         </is>
       </c>
     </row>
@@ -17289,37 +17289,37 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>言葉</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Can You Feel It</t>
+          <t>鑿戶牖以為室，當其無，有室之用。</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Mr. Fingers</t>
+          <t>老子『道徳経』第 11 章</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Mr. Fingers 名義の「Can You Feel It」（1986 年・Trax Records。EP『Washing Machine』に収録されたインストゥルメンタル版）</t>
+          <t>老子『道徳経』第 11 章（車輪の轂・器・部屋のたとえで『無』の用を説く章）の後半の一句</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>2013 年（16 歳）リーズ・ラウンドヘイの幼なじみの友人の兄の部屋で、レコードで聴いた。</t>
+          <t>2015 年（18 歳）シェフィールドの大学 1 年の建築史の講義。講師が英訳と並べて黒板に書いた。</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>16 歳、リーズの友人の兄の部屋で聴いた 80 年代シカゴの録音。歌が無くても、同じ和音の繰り返しが人を前へ進ませる。説教しない温かさがハウスの核だと思った。</t>
+          <t>1 年の建築史の講義で、講師が英訳と並べて黒板に書いた。戸と窓をくり抜いて部屋を作る、部屋が役に立つのは何も無いところ。HOLLOWPLAN という名前の半分はここにある。</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>同じ和音を繰り返しながら前へ進ませるエレピのコードの組み方と、歌の無いハウスの温かさ。終わりのコードを解決しきらずに次の曲へつなぐアウトロもここから来ている。</t>
+          <t>HOLLOWPLAN という名前と、曲のちょうど真ん中に置く『中庭』の 8 小節。キックとベースを遠ざけても無音にはしない『使うための空白』の考え方そのもの。</t>
         </is>
       </c>
     </row>
@@ -17341,37 +17341,37 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>絵（彫刻）</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Selected Ambient Works 85–92（アルバム）</t>
+          <t>House（1993 年。ロンドン東部ボウのテラスハウスの内部をコンクリートで型取りした作品）</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Aphex Twin</t>
+          <t>Rachel Whiteread</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Selected Ambient Works 85–92』（1992 年・Apollo）の 1 曲目「Xtal」</t>
+          <t>『House』（1993 年。ボウのグローブ・ロード 193 番地。同年のターナー賞を受け、1994 年 1 月に取り壊された）</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>2016 年秋（19 歳）シェフィールドの大学の模型工房で、技術職員が夜の作業中に流していた。そのあと卒業まで、夜通し模型を作る晩に繰り返し聴いた。</t>
+          <t>2018 年（21 歳）ロンドンに来た年、クラーケンウェルの設計事務所の資料棚にあった写真集で知った。</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>言葉の無い息のような声が、柔らかいビートの上で空気として漂っていること。声は歌わなくても、部屋の温度を決められると知った。</t>
+          <t>ロンドンに来た 2018 年に写真集で知った。家の中の空気をそのまま固めた形。空いているところにも形がある、と模型の仕事で毎日思い出す。</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>声の切れ端を『歌』ではなく背景の空気として置く音量の決め方と、角の取れたキックにテープの揺れを薄くかける質感。100〜118 BPM の柔らかい帯域を選ぶ癖にも出ている。</t>
+          <t>曲ごとに作る手のひら大のバルサの『部屋の模型』と、中央を空けたジャケットの構図。音では、残響の尾を部屋の空気の形として残し、空白を『形のあるもの』として扱う編曲に出ている。</t>
         </is>
       </c>
     </row>
@@ -17393,257 +17393,257 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
+          <t>映画</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Columbus（2017 年）</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Kogonada</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>映画『Columbus』（2017 年・監督と脚本 Kogonada。インディアナ州コロンバスのモダニズム建築を舞台にした長編第 1 作）</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>2018 年 12 月（21 歳）実務研修の年の年末、リーズに帰省した折に古い映画館で父と見た（英国公開は 2018 年 10 月）。</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>実務研修の年の年末、帰省したリーズの古い映画館で父と見た唯一の映画（父は途中で寝た）。モダニズムの建物の前で、人が黙って立っている時間を急がない。何も起きない場面の撮り方。</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>何も起きない時間を急がない曲の入り方（イントロ 8 小節で吸う息とローパスのエレピだけ）と、動かないカメラで建物と人を撮るジャケットや動画の静止した構図。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>There Is Love in You（アルバム）</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Four Tet</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『There Is Love in You』（2010 年・Domino）の 1 曲目「Angel Echoes」</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>2020 年 5 月（23 歳）ロックダウン中のレイトン。SoundCloud に上げた『Plan 03』を聴いたオンラインの宅録仲間が『これ知ってる？』と送ってきた。</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>短い声の断片を楽器のように重ね、ループの中で少しずつ形を変えて旋律にするやり方。</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>曲名から取った 1〜3 語の切れ端を半音ずつ上げながら 4 回繰り返すフックと、16 小節ごとに 1 つだけ切れ端の並びを変えていく展開。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>hollowplan</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>abena</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>First Love</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>宇多田ヒカル</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『First Love』（1999）とその表題曲</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>物心ついたころ（2000 年代半ば）からオデルの家の台所で。母が函館に帰省したときに買ってきた CD で、朝の支度の時間に流れていた</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>母が函館から持ってきた CD で、オデルの台所でいつも流れていた。日本語と英語のあいだを行き来しながら言葉をはっきり置いて歌う人がいると知り、2 つの言語を持っていることは隠すものではないと受け取った。</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>英語の歌の中に日本語を 1 語だけはっきり置く歌詞の決まりと、子音を立てて言葉を 1 音ずつ届ける歌い方に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Spaces（アルバム）</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Nils Frahm</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>ライブ録音のアルバム『Spaces』（2013 年・Erased Tapes）の 2 曲目「Says」</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>2023 年秋（26 歳）ファンミが深夜番組の最後にかけたのを聴いた。12 月から父の入院で隔週に乗った夜行バスで、一番多く聴いた。</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>1 つのアルペジオが 8 分かけて少しずつ開いていき、何も起きないようで景色が変わっていくこと。</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>42 分の切れ目のないミックスの組み方と、新しい音を 16 小節ごとに 1 つだけ足し引きする規則。夜行バス 1 本ぶんを途切れずにつなぐ長い作品の構想の土台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>hollowplan</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>abena</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Songs from the Big Chair</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Tears for Fears</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Songs from the Big Chair』（1985）の 3 曲目「Everybody Wants to Rule the World」</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>4〜5 歳の冬（2006〜07 年）・オデル。父の除雪用ピックアップのカセットデッキに入りっぱなしだったテープで、助手席で何度も聴いた</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>父のピックアップのカセットデッキに入りっぱなしだったテープ。除雪の朝に何度も聴き、前へ進み続ける推進力と明るいシンセの音色が、夜明けの道の音として体に残った。</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>同じフレーズを繰り返しながら少しずつ開いていく曲の形と、明るいシンセを何層か重ねるイントロに出ている。テンポを急がず前へ進む感じも、除雪の朝の記憶とつながっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>The Bones of What You Believe</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>CHVRCHES</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『The Bones of What You Believe』（2013）の 1 曲目「The Mother We Share」</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>13 歳の春（2015 年）・フッドリバー。中古のシンセの使い方を動画で調べていて、ライブ映像にたどり着いた</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>13 歳でシンセを手に入れたころに見つけたアルバム。硬い 8 分のシンセの上で高い声が子音をはっきり立てて歌う形を、そのまま自分の歌い方の手本にした。</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>硬い 8 分のシンセアルペジオを曲の背骨にする作り方と、高い地声で子音を拍の頭に置く歌い方に、いちばん直接に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>本</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Species of Spaces and Other Pieces（さまざまな空間）</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Georges Perec</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>英訳選集『Species of Spaces and Other Pieces』（1997 年・Penguin Books、ジョン・スタロック編訳）。表題作の原著『Espèces d'espaces』は 1974 年</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>2015 年（18 歳）シェフィールドの大学 1 年。建築学科の読書リストにあり、大学図書館で借りて延長を繰り返した。</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>大学 1 年で読んだ。ページ・ベッド・部屋・通りと、ありふれた空間を一つずつ書き出していく方法。曲名を空間の単位と時刻で付ける癖の元。</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>Courtyard, 02:40 や Services at Three のように、空間の単位と時刻を組み合わせて曲名を付ける癖。スケッチブックの平面図の余白に、言葉を部屋の名前のように書き出す習慣にも出ている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>hollowplan</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>abena</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>言葉</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>鑿戶牖以為室，當其無，有室之用。</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>老子『道徳経』第 11 章</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>老子『道徳経』第 11 章（車輪の轂・器・部屋のたとえで『無』の用を説く章）の後半の一句</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>2015 年（18 歳）シェフィールドの大学 1 年の建築史の講義。講師が英訳と並べて黒板に書いた。</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>1 年の建築史の講義で、講師が英訳と並べて黒板に書いた。戸と窓をくり抜いて部屋を作る、部屋が役に立つのは何も無いところ。HOLLOWPLAN という名前の半分はここにある。</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>HOLLOWPLAN という名前と、曲のちょうど真ん中に置く『中庭』の 8 小節。キックとベースを遠ざけても無音にはしない『使うための空白』の考え方そのもの。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="inlineStr">
-        <is>
-          <t>hollowplan</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>abena</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>絵（彫刻）</t>
-        </is>
-      </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>House（1993 年。ロンドン東部ボウのテラスハウスの内部をコンクリートで型取りした作品）</t>
+          <t>The Lathe of Heaven（天のろくろ）</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Rachel Whiteread</t>
+          <t>Ursula K. Le Guin</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>『House』（1993 年。ボウのグローブ・ロード 193 番地。同年のターナー賞を受け、1994 年 1 月に取り壊された）</t>
+          <t>長編小説『The Lathe of Heaven』（1971）</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>2018 年（21 歳）ロンドンに来た年、クラーケンウェルの設計事務所の資料棚にあった写真集で知った。</t>
+          <t>21 歳の春（2023 年）・ポートランドに移ってすぐ、配送明けに寄った近所の古本屋で</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>ロンドンに来た 2018 年に写真集で知った。家の中の空気をそのまま固めた形。空いているところにも形がある、と模型の仕事で毎日思い出す。</t>
+          <t>ポートランドの古本屋で買った、この街が舞台の小説。知っている通りや橋が物語に出てくるのを読み、自分の住む場所や毎日の道も物語の舞台になると知った。</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>曲ごとに作る手のひら大のバルサの『部屋の模型』と、中央を空けたジャケットの構図。音では、残響の尾を部屋の空気の形として残し、空白を『形のあるもの』として扱う編曲に出ている。</t>
+          <t>通りの名前や橋を歌詞にそのまま入れる書き方（Alberta・Fremont など）と、自分の配送ルートを歌の舞台にする発想に出ている</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
-        <is>
-          <t>hollowplan</t>
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>abena</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -17653,37 +17653,37 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>映画</t>
+          <t>本</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Columbus（2017 年）</t>
+          <t>旅をする木</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Kogonada</t>
+          <t>星野道夫</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>映画『Columbus』（2017 年・監督と脚本 Kogonada。インディアナ州コロンバスのモダニズム建築を舞台にした長編第 1 作）</t>
+          <t>随筆集『旅をする木』（1995）</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>2018 年 12 月（21 歳）実務研修の年の年末、リーズに帰省した折に古い映画館で父と見た（英国公開は 2018 年 10 月）。</t>
+          <t>20 歳（2022 年）・函館の祖母の家。子どものころから本棚で背表紙だけ知っていたのを、祖母と暮らした冬に初めて読んだ</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>実務研修の年の年末、帰省したリーズの古い映画館で父と見た唯一の映画（父は途中で寝た）。モダニズムの建物の前で、人が黙って立っている時間を急がない。何も起きない場面の撮り方。</t>
+          <t>函館の祖母の家の本棚にあった。遠く離れた土地で暮らしながら別の場所に流れている時間を同時に思う書き方に、時差のある家族を持つ自分を重ねた。</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>何も起きない時間を急がない曲の入り方（イントロ 8 小節で吸う息とローパスのエレピだけ）と、動かないカメラで建物と人を撮るジャケットや動画の静止した構図。</t>
+          <t>自分の朝と家族の夜を 1 曲の中に同時に置く歌（時差の歌）と、遠くの人に語りかける二人称の視点に出ている</t>
         </is>
       </c>
     </row>
@@ -17705,37 +17705,37 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>映画</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>First Love</t>
+          <t>Paterson</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>宇多田ヒカル</t>
+          <t>Jim Jarmusch</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>アルバム『First Love』（1999）とその表題曲</t>
+          <t>映画『Paterson』（2016）</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>物心ついたころ（2000 年代半ば）からオデルの家の台所で。母が函館に帰省したときに買ってきた CD で、朝の支度の時間に流れていた</t>
+          <t>21 歳の冬（2023 年）・ポートランド。配送ルートの最後のカフェの店主に勧められ、自宅で配信で観た</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>母が函館から持ってきた CD で、オデルの台所でいつも流れていた。日本語と英語のあいだを行き来しながら言葉をはっきり置いて歌う人がいると知り、2 つの言語を持っていることは隠すものではないと受け取った。</t>
+          <t>毎朝同じ時間に起きてバスを運転し、合間に詩を書く主人公。早朝の仕事と創作が同じ一日の中にあっていいと背中を押され、配送の信号待ちで言葉を拾う今のやり方につながった。</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>英語の歌の中に日本語を 1 語だけはっきり置く歌詞の決まりと、子音を立てて言葉を 1 音ずつ届ける歌い方に出ている</t>
+          <t>信号待ちで言葉を拾い午後に書く今の作詞のやり方と、毎日同じ仕事の細部を淡々と並べる歌詞のトーンに出ている</t>
         </is>
       </c>
     </row>
@@ -17757,361 +17757,361 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Morning is when I am awake and there is a dawn in me.（『Walden』より）</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Henry David Thoreau</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>『Walden』（1854）の章「Where I Lived, and What I Lived For」の一節</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>高校 2 年（2018〜19 年）・フッドリバーの高校の英語の授業で</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>高校の英語の授業で出会った一文。朝は時刻ではなく自分が目を覚ましている状態のことだと受け取り、その年の日の出ノートの表紙の裏に書き写した。</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>朝を時刻ではなく気持ちの状態として書く歌詞と、日の出ノートの表紙の裏に今も書き写していることに出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>kino</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Songs from the Big Chair</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Tears for Fears</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Songs from the Big Chair』（1985）の 3 曲目「Everybody Wants to Rule the World」</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>4〜5 歳の冬（2006〜07 年）・オデル。父の除雪用ピックアップのカセットデッキに入りっぱなしだったテープで、助手席で何度も聴いた</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>父のピックアップのカセットデッキに入りっぱなしだったテープ。除雪の朝に何度も聴き、前へ進み続ける推進力と明るいシンセの音色が、夜明けの道の音として体に残った。</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>同じフレーズを繰り返しながら少しずつ開いていく曲の形と、明るいシンセを何層か重ねるイントロに出ている。テンポを急がず前へ進む感じも、除雪の朝の記憶とつながっている</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Making Love Out of Nothing at All</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Air Supply</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>1983 年のベスト盤『Greatest Hits』に新曲として入ったシングル（作詞作曲 Jim Steinman）</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>2002〜2003 年ごろ・4〜5 歳。St Albans の親戚の家のカラオケで、父が毎回締めに歌っていた。オーストラリアのバンドの曲だと知ったのは中等学校に入ってから。</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>父が親戚の集まりのカラオケで毎回歌った、フィリピンで愛されたオーストラリアのバンドの曲。2 つの故郷が 1 曲でつながっていると後で気づいた。照れずに大きなメロディを歌い切ること。</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>サビの頂点の音を照れずに地声で 2 拍伸ばす歌い方と、いちばん高い音に曲中で 1 回だけ届くサビの組み立て。ライブの最後には客が一緒に歌える大きなメロディの曲を必ず置く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>kino</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>The Bones of What You Believe</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>CHVRCHES</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『The Bones of What You Believe』（2013）の 1 曲目「The Mother We Share」</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>13 歳の春（2015 年）・フッドリバー。中古のシンセの使い方を動画で調べていて、ライブ映像にたどり着いた</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>13 歳でシンセを手に入れたころに見つけたアルバム。硬い 8 分のシンセの上で高い声が子音をはっきり立てて歌う形を、そのまま自分の歌い方の手本にした。</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>硬い 8 分のシンセアルペジオを曲の背骨にする作り方と、高い地声で子音を拍の頭に置く歌い方に、いちばん直接に出ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Ang Huling El Bimbo</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Eraserheads</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Cutterpillow』（1995）収録</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>2012 年の夏（12 月）・14 歳。マニラから来たいとこが、部屋でコードを紙に書いて教えてくれた最初の曲の 1 つ。</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>2012 年の夏、マニラから来たいとこがギターで教えてくれた曲。昔の友人や台所や路地の固有名詞だけで、青春の終わりを淡々と語る書き方。</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>感情の言葉を使わず、持ち物や店や地名の固有名詞で場面を埋める歌詞。A メロで同じ音を連打して話すように進むメロディ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>kino</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>映画</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>The Castle（1997）</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Rob Sitch</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>1997 年のオーストラリア映画。メルボルン空港のそばの家が舞台</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>2012 年・14 歳。中等学校の英語の授業で観て、そのあと家族で DVD を何度も観た。</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>空港のそばの家を守る郊外の家族の喜劇。家の価値は値段ではなく暮らしの記憶で決まること。郊外をからかわずに愛するユーモア。</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>郊外の暮らしを笑いながらも見下さない歌詞のユーモア（パイの好みや給油のレシート）。ライブの MC で家族と郊外の話を自虐せずに笑いにする話し方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>kino</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Touch This Earth Lightly: Glenn Murcutt in His Own Words（1999）</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Philip Drew</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>1999 年刊の建築家の対話の本。学部 2 年の設計課題の参考図書</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>2018 年 3 月・19 歳。学部 2 年の設計の授業で講師に勧められ、大学図書館で借りた。</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>学部 2 年の課題図書。大地に軽く触れる建物という考えが、重く支えず軽く持ちこたえる歌の作り方につながった。</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>ギターを 3 音の小さな和音にして音を重ねすぎず、隙間を残すアレンジ。ジャケットや字幕の細い寸法線だけの軽い見た目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>Give Up</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>The Postal Service</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Give Up』（2003・シアトルの Sub Pop から発売）の 2 曲目「Such Great Heights」</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>17 歳ごろ（2019 年）・フッドリバー。中学生だった弟 Ken が見つけて、家の車で繰り返し流していた</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>細かく刻む打ち込みの上で、特別ではない日常の言葉をまっすぐ歌っていいと知った。同じ太平洋岸北西部から出た音楽だということも、自分の暮らしと地続きに感じた。</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>ハイハットと小さなシンセの粒を細かく重ねるリズムの作り方と、身の回りの物の名前をそのまま歌う歌詞に出ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Plastic Love</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Mariya Takeuchi</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『VARIETY』（1984）収録。編曲は山下達郎</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>2017 年・20 歳。Carlton のワンルームで、動画サイトのおすすめに出てきた。</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>2017 年、メルボルンの部屋で動画サイトのおすすめに出てきて、浜松の団地のテレビから流れていた日本語の響きを思い出した。都会の寂しさを明るいグルーヴで包む方法。</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>跳ねる 16 分のベースに寂しい言葉を明るく乗せる曲の設計。ビアのハモりの、日本語の歌のような柔らかい母音。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>bia</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Autobahn</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Kraftwerk</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Autobahn』（1974）の A 面全部を使った表題曲（約 22 分）</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>22 歳の冬（2024 年 12 月）・ポートランド。テンポを 84 号線を走りながら決めていると話したら、ルートの最後のカフェの店主（元レコード店員）が開店前にレコードをかけてくれた</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>高速道路を走ることそのものが音楽になりうると知った。変わらない拍の上で景色だけが少しずつ変わっていく長さを、退屈ではなく心地よさとして受け取った。</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>キックを 4 分寄りに置いて揺らさない一定の拍と、展開を急がず音色の出し入れで景色を変えるアレンジに出ている。DNA の motorik pulse もここから来ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Jubilee</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Japanese Breakfast</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Jubilee』（2021）の 2 曲目「Be Sweet」</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>19 歳（2021 年の夏）・フッドリバーのパン屋。朝 4 時半からの仕込みの時間に、店のスピーカーで繰り返し流していた</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>同じオレゴンで育ちアジア系の母を持つ人が、暗さではなく明るさで自分を歌っているのを聴き、2 つのルーツを持つことを明るい音で鳴らしていいと思えた。</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>弾むシンセベースと 80 年代風の明るいシンセの組み合わせと、口ずさみやすいサビの言葉の置き方に出ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>The Lathe of Heaven（天のろくろ）</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Ursula K. Le Guin</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>長編小説『The Lathe of Heaven』（1971）</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>21 歳の春（2023 年）・ポートランドに移ってすぐ、配送明けに寄った近所の古本屋で</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>ポートランドの古本屋で買った、この街が舞台の小説。知っている通りや橋が物語に出てくるのを読み、自分の住む場所や毎日の道も物語の舞台になると知った。</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
-        <is>
-          <t>通りの名前や橋を歌詞にそのまま入れる書き方（Alberta・Fremont など）と、自分の配送ルートを歌の舞台にする発想に出ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>旅をする木</t>
+          <t>Estrelar</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>星野道夫</t>
+          <t>Marcos Valle</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>随筆集『旅をする木』（1995）</t>
+          <t>アルバム『Marcos Valle』（1983）の 1 曲目。Leon Ware との共作</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>20 歳（2022 年）・函館の祖母の家。子どものころから本棚で背表紙だけ知っていたのを、祖母と暮らした冬に初めて読んだ</t>
+          <t>2011 年・14 歳。サンパウロ Saúde のアパートで、父が日曜の朝にかけていたレコード。ベースを始めた年に最初に耳でコピーした。</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>函館の祖母の家の本棚にあった。遠く離れた土地で暮らしながら別の場所に流れている時間を同時に思う書き方に、時差のある家族を持つ自分を重ねた。</t>
+          <t>サンパウロのアパートで父が日曜の朝に流したレコード。跳ねるベースが体操のように前へ進む明るさ。ベースを始めたとき最初に耳でコピーした。</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>自分の朝と家族の夜を 1 曲の中に同時に置く歌（時差の歌）と、遠くの人に語りかける二人称の視点に出ている</t>
+          <t>オクターブで跳ねるベースラインと、サビ前に 1 オクターブ上へスライドして戻る癖。体を前へ押すような明るい 16 ビート。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>bia</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -18121,49 +18121,49 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>映画</t>
+          <t>絵</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Paterson</t>
+          <t>大きな曲線の色面の抽象画（サンパウロの美術館で見た連作）</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Jim Jarmusch</t>
+          <t>Tomie Ohtake</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>映画『Paterson』（2016）</t>
+          <t>1990 年代以降の大きな曲線の色面の抽象画（サンパウロの Instituto Tomie Ohtake の展示）</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>21 歳の冬（2023 年）・ポートランド。配送ルートの最後のカフェの店主に勧められ、自宅で配信で観た</t>
+          <t>2014 年・17 歳。高校の美術の見学で Pinheiros の Instituto Tomie Ohtake に行った。</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>毎朝同じ時間に起きてバスを運転し、合間に詩を書く主人公。早朝の仕事と創作が同じ一日の中にあっていいと背中を押され、配送の信号待ちで言葉を拾う今のやり方につながった。</t>
+          <t>日本からブラジルへ渡った画家の、1 本の大きな曲線で画面を支える構成。曲を 1 本のベースラインで支えるという考えのもと。</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>信号待ちで言葉を拾い午後に書く今の作詞のやり方と、毎日同じ仕事の細部を淡々と並べる歌詞のトーンに出ている</t>
+          <t>曲の断面図を 1 本の曲線のベースラインから描き始める作り方。ジャケットに寸法線を 1 本だけ重ねる見た目の決まり。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
-        <is>
-          <t>nao_easterly</t>
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>bia</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -18178,32 +18178,32 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Morning is when I am awake and there is a dawn in me.（『Walden』より）</t>
+          <t>Não é o ângulo reto que me atrai, nem a linha reta, dura, inflexível, criada pelo homem. O que me atrai é a curva livre e sensual.</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Henry David Thoreau</t>
+          <t>Oscar Niemeyer</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>『Walden』（1854）の章「Where I Lived, and What I Lived For」の一節</t>
+          <t>建築家が自分の曲線の建築について書いた短い詩の冒頭の一節（ブラジルで広く引用される）</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>高校 2 年（2018〜19 年）・フッドリバーの高校の英語の授業で</t>
+          <t>2015 年・18 歳。サンパウロの高校の美術の先生が黒板に書いた。</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>高校の英語の授業で出会った一文。朝は時刻ではなく自分が目を覚ましている状態のことだと受け取り、その年の日の出ノートの表紙の裏に書き写した。</t>
+          <t>高校の美術の先生が黒板に書いた一節。硬い直角ではなく、たわむ曲線で持ちこたえる構造への好み。バンド名の soft の半分はここから。</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>朝を時刻ではなく気持ちの状態として書く歌詞と、日の出ノートの表紙の裏に今も書き写していることに出ている</t>
+          <t>バンド名の soft。ベースを直線的に刻まず、スライドで音と音をつなぐ弾き方と、断面図の曲線。</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18215,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>kino</t>
+          <t>bia</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -18225,37 +18225,37 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>映画</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Making Love Out of Nothing at All</t>
+          <t>Drive My Car（2021）</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Air Supply</t>
+          <t>濱口竜介（Ryusuke Hamaguchi）</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>1983 年のベスト盤『Greatest Hits』に新曲として入ったシングル（作詞作曲 Jim Steinman）</t>
+          <t>2021 年の日本映画。村上春樹の短編が原作</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>2002〜2003 年ごろ・4〜5 歳。St Albans の親戚の家のカラオケで、父が毎回締めに歌っていた。オーストラリアのバンドの曲だと知ったのは中等学校に入ってから。</t>
+          <t>2022 年・25 歳。メルボルンの映画館で 1 人で観た。</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>父が親戚の集まりのカラオケで毎回歌った、フィリピンで愛されたオーストラリアのバンドの曲。2 つの故郷が 1 曲でつながっていると後で気づいた。照れずに大きなメロディを歌い切ること。</t>
+          <t>2022 年、メルボルンの映画館で、日本語の台詞を字幕を見なくても半分聞き取れたことに泣いた。車の中だから話せることがある、という感覚。</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>サビの頂点の音を照れずに地声で 2 拍伸ばす歌い方と、いちばん高い音に曲中で 1 回だけ届くサビの組み立て。ライブの最後には客が一緒に歌える大きなメロディの曲を必ず置く。</t>
+          <t>移動中の車内の会話と沈黙を歌うテーマ。両親をバンに乗せた日の、父が黙って頷き続ける歌の種の書き方。</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>kino</t>
+          <t>tav</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -18282,32 +18282,32 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ang Huling El Bimbo</t>
+          <t>Wandering Eye</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Eraserheads</t>
+          <t>Fat Freddy's Drop</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Cutterpillow』（1995）収録</t>
+          <t>アルバム『Based on a True Story』（2005）収録</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>2012 年の夏（12 月）・14 歳。マニラから来たいとこが、部屋でコードを紙に書いて教えてくれた最初の曲の 1 つ。</t>
+          <t>2005〜2006 年・6〜7 歳。Napier で父の現場のトラックの CD で毎日流れていた。</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>2012 年の夏、マニラから来たいとこがギターで教えてくれた曲。昔の友人や台所や路地の固有名詞だけで、青春の終わりを淡々と語る書き方。</t>
+          <t>2005 年ごろ、父が現場のトラックでずっと流していたニュージーランドのバンドの曲。拍の後ろにゆったり座るグルーヴと、急がないことの強さ。</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>感情の言葉を使わず、持ち物や店や地名の固有名詞で場面を埋める歌詞。A メロで同じ音を連打して話すように進むメロディ。</t>
+          <t>スネアの 2 拍 4 拍をわずかに遅らせて座らせる叩き方と、テンポを上げずに盛り上げるサビ。</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>kino</t>
+          <t>tav</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -18334,32 +18334,32 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>How to Make Gravy</t>
+          <t>Weather With You</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Paul Kelly</t>
+          <t>Crowded House</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>EP『How to Make Gravy』（1996 年 11 月）の表題曲</t>
+          <t>アルバム『Woodface』（1991）収録</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>2015 年 12 月・17 歳。祖母が同居を始めた年のクリスマス前に、母の車のラジオで流れた。</t>
+          <t>2012 年 1 月・13 歳。移住の日に Napier から空港へ向かう車で母がかけた。</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>クリスマスに家族の昼食へ帰れない男が弟へ書く手紙の歌。人の名前と料理と台所の細部だけで、会えない家族を描く書き方。</t>
+          <t>移住の日、Napier から空港へ向かう車で母がかけた曲。故郷を離れても天気は連れていける、という気持ちと、男声のハーモニーの重ね方。</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>父を説明せず、持ち物（グローブボックス・ロザリオ・給油のレシート）と食べ物で人を描く歌詞。語りかける相手を you に固定して説明しない。</t>
+          <t>タヴのコーラスの低いユニゾンの重ね方と、離れることを明るい長調で歌う曲への好み。</t>
         </is>
       </c>
     </row>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>kino</t>
+          <t>tav</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -18386,32 +18386,32 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Salad Days</t>
+          <t>Dean Town</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Mac DeMarco</t>
+          <t>Vulfpeck</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>アルバム『Salad Days』（2014）の表題曲</t>
+          <t>アルバム『The Beautiful Game』（2016）収録・演奏動画</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>2014 年の半ば・16 歳。いとこが部屋のスピーカーで流し、揺れるギターの音の出し方を 2 人で調べた。父の工場の閉鎖が発表された年。</t>
+          <t>2017 年・18 歳。学部 1 年の製図室で、自分のノートパソコンでキノとビアに見せた。</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>薄く揺れるクリーンのギターと、疲れや不安を力まずに軽く歌う声。</t>
+          <t>大学 1 年のとき、製図室でキノとビアに見せた演奏動画。最小の編成でベースとドラムが曲の骨組みになれること。</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>コーラスを薄く常にかけたクリーンのカッティング。重い話ほど明るいテンポで力まずに歌う、キノの話すような歌い方。</t>
+          <t>ギターとベースのユニゾンのリフにドラムがキメで合わせる間奏と、ベースとドラムだけで始まるイントロ。</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>kino</t>
+          <t>tav</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -18438,32 +18438,32 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>The Castle（1997）</t>
+          <t>Boy（2010）</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Rob Sitch</t>
+          <t>Taika Waititi</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>1997 年のオーストラリア映画。メルボルン空港のそばの家が舞台</t>
+          <t>2010 年のニュージーランド映画</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>2012 年・14 歳。中等学校の英語の授業で観て、そのあと家族で DVD を何度も観た。</t>
+          <t>2010 年・11 歳。Napier の映画館で家族全員で観た。</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>空港のそばの家を守る郊外の家族の喜劇。家の価値は値段ではなく暮らしの記憶で決まること。郊外をからかわずに愛するユーモア。</t>
+          <t>11 歳のとき、Napier の映画館で家族全員で観た。ニュージーランドの田舎の暮らしを、悲しい話でも笑いながら描くやり方。</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>郊外の暮らしを笑いながらも見下さない歌詞のユーモア（パイの好みや給油のレシート）。ライブの MC で家族と郊外の話を自虐せずに笑いにする話し方。</t>
+          <t>ライブの MC で悲しい話も笑いながら短く話すタヴの話し方と、動画の字幕の素朴なユーモア。</t>
         </is>
       </c>
     </row>
@@ -18475,1295 +18475,1295 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Shop Class as Soulcraft（2009）</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Matthew B. Crawford</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>2009 年刊のアメリカの哲学者の本</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>2021 年・22 歳。父が腰を痛めて代わりに現場に出ていたころ、見習いになるか迷って読んだ。</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>修士を出て見習いになるか迷っていた 2021 年に読んだ。手で作る仕事に頭も誇りも要るという考えが、背中を押した。</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>機材ケースや物販の棚や自作のスネアを自分の手で作ること。演奏でも見せる技より持ちこたえる確かさを選ぶ姿勢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Woodface</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Crowded House</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Woodface』（1991）。とくに 5 曲目『Weather With You』と 7 曲目『Four Seasons in One Day』のフィン兄弟の 2 声</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>2000 年前後（4〜6 歳）・オタゴの牧場で父の車のカセットを繰り返し聴いた。砂利道を走る 1 時間、兄と後部座席でハモりの真似をした。</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>父の車のカセット。オタゴの砂利道を 1 時間走るあいだ、兄と後部座席でハモりの真似をした。兄弟の声が重なる気持ちよさと、自分の国の人が作った歌が世界で鳴るという実感。</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>上のハモりを主旋律の 3 度上にぴたりと平行に付ける癖。A メロを 1 人で低く語り、サビで 2 声が開く曲の形。天気を気持ちの比喩にしても重くしない歌詞の温度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Submarine Bells</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>The Chills</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Submarine Bells』（1990）。1 曲目の『Heavenly Pop Hit』</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>2009 年頃（14 歳）・ダニーデンの寄宿学校で、ギターを教えてくれた上級生が CD を貸してくれた。</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>ダニーデンの寄宿学校の上級生が貸してくれた CD。坂と雨の多い自分たちの街から生まれた、少し陰りのある明るいギターの音。自分の町の天気を歌っていいと知った。</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>長調の明るい刻みの中に 1 つだけ陰る和音を置く感覚。歌詞に坂や雨や霜など自分の町の天気をそのまま書き込むこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Time (The Revelator)</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Gillian Welch</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Time (The Revelator)』（2001）。3 曲目の『Dear Someone』</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>2014 年の夏（19 歳）・南島の牧場を回る毛刈り隊の宿舎で、先輩がスマートフォンで流してくれた。</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>大学時代、毛刈り隊の先輩に教わったアルバム。男女 2 人だけで声とギターを重ねる最小の編成と、言葉を急がない歌い方。</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>2 人だけの声とギターを基本の編成にする考え方。言葉を拍の少し後ろに置いて急がない歌い方。ギター 1 本で隙間を残す伴奏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>To the Is-Land</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Janet Frame</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>自伝 3 部作の第 1 巻『To the Is-Land』（1982）</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>2010 年頃（15 歳）・ダニーデンの寄宿学校の図書室で、消灯前に少しずつ読んだ。</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>オタゴの町で育った作家の自伝。寄宿学校の図書室で読み、貧しさや田舎の暮らしの中にこそ言葉の豊かさがあると知った。自分の土地にも書くことがあると思えた。</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>地名や家の物を恥ずかしがらずに歌詞へ入れること。失敗や貧しさを飾らず、出来事だけで書く語り口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>絵</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>セントラル・オタゴの風景画（マニオトト平原を描いた作品群）</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Grahame Sydney</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>マニオトト平原を描いたテンペラ画の複製（『July on the Maniototo』など）</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>物心ついた頃から・実家の居間の壁に母が掛けていた複製画。</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>実家の居間にあった複製画。何もない平原と高い空と、ぽつんと立つ小屋。余白を怖がらないことを受け取った。</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>イントロとアウトロに音を詰めない余白。ジャケットや写真で上 2/3 を空や壁の余白にする構図。景色を描きすぎず小屋 1 つで語る歌詞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Knit on with confidence and hope, through all crises.</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Elizabeth Zimmermann</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>アメリカの編み物作家の座右の言葉として、編み手のあいだで広く知られる一文</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>2002 年の冬休み（7 歳）・ダニーデンの祖母の家で編み物を習ったとき、本の見返しの書き写しを見た。意味が身に染みたのは腱鞘炎の 2023 年の冬。</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>祖母が編み物の本の見返しに書き写していた一文。手を動かし続ければ、困ったときもなんとかなる。腱鞘炎の冬にも何度も読み返した。</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>つらい出来事を歌う曲でも、最後の行を『編み始める』のような手の動作で前へ向けて終える歌詞の癖。配信の終わりの挨拶。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Ysbryd Solva</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Meic Stevens</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Ysbryd Solva』（2002・ウェールズ語）</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>2002 年の夏（12 歳）・地元セント・デイヴィッズで全国アイステズヴォッドが開かれた年に、父が買ってきた。</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>同じソルヴァ生まれの歌い手が、2002 年に村での子ども時代を歌ったアルバム。12 歳のとき父が買ってきた。自分の港の名前が歌になる誇りと、ウェールズ語の歌の柔らかい子音。</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>ウェールズ語の柔らかい子音の発音を英語の歌詞にも持ち込む下ハモの声。港の名前や道路の番号をそのまま歌に入れる勇気。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Solid Air</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>John Martyn</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Solid Air』（1973）。1 曲目の表題曲と、テープ・ディレイで指弾きを揺らした 4 曲目『I'd Rather Be the Devil』</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>1990 年代半ば（5 歳頃から）・ソルヴァの父の作業場のレコードプレーヤーで、鉋屑を掃きながら聴いた。</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>父が作業場で鉋をかけながら回していたレコード。指弾きのギターが波のように反復して揺れる感じと、声を楽器のように滲ませる歌い方。</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>親指の低音の反復を崩さず、その上で和音を波のように揺らす指弾きの型。語尾を滲ませて楽器に溶かす下ハモの歌い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Damien Rice</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『O』（2002）。2 曲目『Volcano』の男女の声の掛け合い</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>2004 年（14 歳）・初めてのギターを買った頃、セント・デイヴィッズの中等学校のバンド仲間に CD を借りた。</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>14 歳でギターを買った頃に聴き込んだアルバム。男女の声が小さな部屋で寄り添う距離感と、静かな曲でも熱が伝わること。</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>ブリッジで楽器が抜けて声 2 人と持続音だけになる曲の形。マイクに近づいて小さな声で歌う録り方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>本</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Under Milk Wood</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Dylan Thomas</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>声の劇『Under Milk Wood』。1954 年 1 月に BBC で初めて放送された Richard Burton が語り手の録音</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>子どもの頃（1990 年代）から毎年冬・ソルヴァの台所で母が流していた。</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>母が毎年冬に朗読の録音を流していた、ウェールズの小さな漁村の一日を描く声の劇。村の一人ひとりの暮らしの細部を、音と言葉の響きで描く書き方。</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>ゲシンが書き換える 2〜3 行に多い、港の人の小さな動作を並べる書き方。意味より子音の響きで言葉を選ぶ癖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>tidewool</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>gethin</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>言葉</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>I have seen the sun break through / to illuminate a small field / for a while, and gone my way / and forgotten it.（The Bright Field）</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>R. S. Thomas</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>詩『The Bright Field』（詩集『Laboratories of the Spirit』1975 年）</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>2011 年（21 歳）・ファルマスの専門学校に通っていた頃、町の図書館で借りた詩集で。</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>専門学校の頃、ウェールズの詩人の詩集で出会った一節。ほんの短い光を見過ごさずに立ち止まること。急がない仕事の理由になった。</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>サビの手前で 1 小節だけ立ち止まってハミングする曲の習慣。速くしたがるアイラに対して、遅いテンポを選ぶ理由。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>declan_fay</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Slave to Love</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Ferry</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Boys and Girls』（1985）の 2 曲目『Slave to Love』。父のテープでは 1985 年のラベルの何本にも繰り返し入っている。</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>2021 年の春から夏、母から届いた靴箱のテープを局の制作室で 1 本ずつデジタル化していて、1985 年の録音に何度も出てくるのに気づいた。</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>張らずにささやくような低い声でも、大人の夜の色気と温度は伝わること。柔らかいパッドを何層にも重ねて、声の周りに空気を作る音の作り方。</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>サビの頂点でも声を張らずに息を混ぜて置く歌い方と、A メロ頭の息まじりのささやき。パッドを薄く何層にも重ねて声を包むミックスに出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>declan_fay</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>declan</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Violator</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Violator』（1990）。とくに 6 曲目の『Enjoy the Silence』。</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>2012 年、工科カレッジのラジオ実習で局の古い音源を整理していて CD を見つけ、深夜の送出番の空き時間に通して聴いた。</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>低い男声とシンセだけで大きなサビが作れること。アルペジオとベースとパッドに役割をはっきり分ければ、音数が少なくても曲が広がること。</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>16 分のアルペジオに細かさを任せ、低音はシンセベース 1 本だけにする楽器の分担。ギターは 1 本までという決まりと、サビの最終行のオクターブ下のダブルにも出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Selected Ambient Works 85–92（アルバム）</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Aphex Twin</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Selected Ambient Works 85–92』（1992 年・Apollo）の 1 曲目「Xtal」</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>2016 年秋（19 歳）シェフィールドの大学の模型工房で、技術職員が夜の作業中に流していた。そのあと卒業まで、夜通し模型を作る晩に繰り返し聴いた。</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>言葉の無い息のような声が、柔らかいビートの上で空気として漂っていること。声は歌わなくても、部屋の温度を決められると知った。</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>声の切れ端を『歌』ではなく背景の空気として置く音量の決め方と、角の取れたキックにテープの揺れを薄くかける質感。100〜118 BPM の柔らかい帯域を選ぶ癖にも出ている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>There Is Love in You（アルバム）</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Four Tet</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『There Is Love in You』（2010 年・Domino）の 1 曲目「Angel Echoes」</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>2020 年 5 月（23 歳）ロックダウン中のレイトン。SoundCloud に上げた『Plan 03』を聴いたオンラインの宅録仲間が『これ知ってる？』と送ってきた。</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>短い声の断片を楽器のように重ね、ループの中で少しずつ形を変えて旋律にするやり方。</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>曲名から取った 1〜3 語の切れ端を半音ずつ上げながら 4 回繰り返すフックと、16 小節ごとに 1 つだけ切れ端の並びを変えていく展開。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>hollowplan</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>abena</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Spaces（アルバム）</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Nils Frahm</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>ライブ録音のアルバム『Spaces』（2013 年・Erased Tapes）の 2 曲目「Says」</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>2023 年秋（26 歳）ファンミが深夜番組の最後にかけたのを聴いた。12 月から父の入院で隔週に乗った夜行バスで、一番多く聴いた。</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>1 つのアルペジオが 8 分かけて少しずつ開いていき、何も起きないようで景色が変わっていくこと。</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>42 分の切れ目のないミックスの組み方と、新しい音を 16 小節ごとに 1 つだけ足し引きする規則。夜行バス 1 本ぶんを途切れずにつなぐ長い作品の構想の土台。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Give Up</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>The Postal Service</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Give Up』（2003・シアトルの Sub Pop から発売）の 2 曲目「Such Great Heights」</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>17 歳ごろ（2019 年）・フッドリバー。中学生だった弟 Ken が見つけて、家の車で繰り返し流していた</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>細かく刻む打ち込みの上で、特別ではない日常の言葉をまっすぐ歌っていいと知った。同じ太平洋岸北西部から出た音楽だということも、自分の暮らしと地続きに感じた。</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>ハイハットと小さなシンセの粒を細かく重ねるリズムの作り方と、身の回りの物の名前をそのまま歌う歌詞に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Autobahn</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Kraftwerk</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Autobahn』（1974）の A 面全部を使った表題曲（約 22 分）</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>22 歳の冬（2024 年 12 月）・ポートランド。テンポを 84 号線を走りながら決めていると話したら、ルートの最後のカフェの店主（元レコード店員）が開店前にレコードをかけてくれた</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>高速道路を走ることそのものが音楽になりうると知った。変わらない拍の上で景色だけが少しずつ変わっていく長さを、退屈ではなく心地よさとして受け取った。</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>キックを 4 分寄りに置いて揺らさない一定の拍と、展開を急がず音色の出し入れで景色を変えるアレンジに出ている。DNA の motorik pulse もここから来ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>nao_easterly</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>Jubilee</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Japanese Breakfast</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Jubilee』（2021）の 2 曲目「Be Sweet」</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>19 歳（2021 年の夏）・フッドリバーのパン屋。朝 4 時半からの仕込みの時間に、店のスピーカーで繰り返し流していた</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>同じオレゴンで育ちアジア系の母を持つ人が、暗さではなく明るさで自分を歌っているのを聴き、2 つのルーツを持つことを明るい音で鳴らしていいと思えた。</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>弾むシンセベースと 80 年代風の明るいシンセの組み合わせと、口ずさみやすいサビの言葉の置き方に出ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
           <t>kino</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Touch This Earth Lightly: Glenn Murcutt in His Own Words（1999）</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Philip Drew</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>1999 年刊の建築家の対話の本。学部 2 年の設計課題の参考図書</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>2018 年 3 月・19 歳。学部 2 年の設計の授業で講師に勧められ、大学図書館で借りた。</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>学部 2 年の課題図書。大地に軽く触れる建物という考えが、重く支えず軽く持ちこたえる歌の作り方につながった。</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>ギターを 3 音の小さな和音にして音を重ねすぎず、隙間を残すアレンジ。ジャケットや字幕の細い寸法線だけの軽い見た目。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>How to Make Gravy</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Paul Kelly</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>EP『How to Make Gravy』（1996 年 11 月）の表題曲</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>2015 年 12 月・17 歳。祖母が同居を始めた年のクリスマス前に、母の車のラジオで流れた。</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>クリスマスに家族の昼食へ帰れない男が弟へ書く手紙の歌。人の名前と料理と台所の細部だけで、会えない家族を描く書き方。</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>父を説明せず、持ち物（グローブボックス・ロザリオ・給油のレシート）と食べ物で人を描く歌詞。語りかける相手を you に固定して説明しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="38" t="inlineStr">
         <is>
           <t>soft_cantilever</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>kino</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Salad Days</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Salad Days』（2014）の表題曲</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>2014 年の半ば・16 歳。いとこが部屋のスピーカーで流し、揺れるギターの音の出し方を 2 人で調べた。父の工場の閉鎖が発表された年。</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>薄く揺れるクリーンのギターと、疲れや不安を力まずに軽く歌う声。</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>コーラスを薄く常にかけたクリーンのカッティング。重い話ほど明るいテンポで力まずに歌う、キノの話すような歌い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t>soft_cantilever</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>bia</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Plastic Love</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Mariya Takeuchi</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『VARIETY』（1984）収録。編曲は山下達郎</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>2017 年・20 歳。Carlton のワンルームで、動画サイトのおすすめに出てきた。</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>2017 年、メルボルンの部屋で動画サイトのおすすめに出てきて、浜松の団地のテレビから流れていた日本語の響きを思い出した。都会の寂しさを明るいグルーヴで包む方法。</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>跳ねる 16 分のベースに寂しい言葉を明るく乗せる曲の設計。ビアのハモりの、日本語の歌のような柔らかい母音。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Jazz Carnival</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Azymuth</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『Light as a Feather』（1979）収録</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>2011 年・14 歳。ベースを教えてくれたサンパウロの楽器店の店主が、店のレコードで『ベースが歌っているのを聴け』とかけた。</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>ブラジルの 3 人組の、ベースが主旋律のように歌いながらグルーヴを支える演奏。少人数でも大きく鳴る編成。</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>ギターと同じリフをユニゾンで弾く 2 回目のサビのあとの間奏と、歌の隙間でベースが短く歌うフィル。3 人だけで鳴らす編成への自信。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="38" t="inlineStr">
         <is>
           <t>soft_cantilever</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>bia</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Estrelar</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Marcos Valle</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Marcos Valle』（1983）の 1 曲目。Leon Ware との共作</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>2011 年・14 歳。サンパウロ Saúde のアパートで、父が日曜の朝にかけていたレコード。ベースを始めた年に最初に耳でコピーした。</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>サンパウロのアパートで父が日曜の朝に流したレコード。跳ねるベースが体操のように前へ進む明るさ。ベースを始めたとき最初に耳でコピーした。</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>オクターブで跳ねるベースラインと、サビ前に 1 オクターブ上へスライドして戻る癖。体を前へ押すような明るい 16 ビート。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>都会</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>大貫妙子（Taeko Ohnuki）</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>アルバム『SUNSHOWER』（1977）の 4 曲目</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>2017 年・20 歳。Plastic Love のあと、70〜80 年代の日本の都会の音楽を掘っていて見つけた。</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>都会の暮らしを少し離れて見つめる歌詞と、細かく動くリズムの上で落ち着いて歌う女声。</t>
+        </is>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>ハモりで返す 1 行を、熱くならず少し距離を取った声で歌うこと。シンコペーションの多いベースに言葉数の少ないコーラスを乗せるアレンジ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="38" t="inlineStr">
         <is>
           <t>soft_cantilever</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>tav</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>音楽</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Jazz Carnival</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Azymuth</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Light as a Feather』（1979）収録</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>2011 年・14 歳。ベースを教えてくれたサンパウロの楽器店の店主が、店のレコードで『ベースが歌っているのを聴け』とかけた。</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>ブラジルの 3 人組の、ベースが主旋律のように歌いながらグルーヴを支える演奏。少人数でも大きく鳴る編成。</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>ギターと同じリフをユニゾンで弾く 2 回目のサビのあとの間奏と、歌の隙間でベースが短く歌うフィル。3 人だけで鳴らす編成への自信。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>都会</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>大貫妙子（Taeko Ohnuki）</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『SUNSHOWER』（1977）の 4 曲目</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>2017 年・20 歳。Plastic Love のあと、70〜80 年代の日本の都会の音楽を掘っていて見つけた。</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>都会の暮らしを少し離れて見つめる歌詞と、細かく動くリズムの上で落ち着いて歌う女声。</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>ハモりで返す 1 行を、熱くならず少し距離を取った声で歌うこと。シンコペーションの多いベースに言葉数の少ないコーラスを乗せるアレンジ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>絵</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>大きな曲線の色面の抽象画（サンパウロの美術館で見た連作）</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Tomie Ohtake</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>1990 年代以降の大きな曲線の色面の抽象画（サンパウロの Instituto Tomie Ohtake の展示）</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>2014 年・17 歳。高校の美術の見学で Pinheiros の Instituto Tomie Ohtake に行った。</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>日本からブラジルへ渡った画家の、1 本の大きな曲線で画面を支える構成。曲を 1 本のベースラインで支えるという考えのもと。</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>曲の断面図を 1 本の曲線のベースラインから描き始める作り方。ジャケットに寸法線を 1 本だけ重ねる見た目の決まり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>言葉</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Não é o ângulo reto que me atrai, nem a linha reta, dura, inflexível, criada pelo homem. O que me atrai é a curva livre e sensual.</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Oscar Niemeyer</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>建築家が自分の曲線の建築について書いた短い詩の冒頭の一節（ブラジルで広く引用される）</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>2015 年・18 歳。サンパウロの高校の美術の先生が黒板に書いた。</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>高校の美術の先生が黒板に書いた一節。硬い直角ではなく、たわむ曲線で持ちこたえる構造への好み。バンド名の soft の半分はここから。</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>バンド名の soft。ベースを直線的に刻まず、スライドで音と音をつなぐ弾き方と、断面図の曲線。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="inlineStr">
-        <is>
-          <t>bia</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>映画</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Drive My Car（2021）</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>濱口竜介（Ryusuke Hamaguchi）</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>2021 年の日本映画。村上春樹の短編が原作</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>2022 年・25 歳。メルボルンの映画館で 1 人で観た。</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>2022 年、メルボルンの映画館で、日本語の台詞を字幕を見なくても半分聞き取れたことに泣いた。車の中だから話せることがある、という感覚。</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>移動中の車内の会話と沈黙を歌うテーマ。両親をバンに乗せた日の、父が黙って頷き続ける歌の種の書き方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Wandering Eye</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Fat Freddy's Drop</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Based on a True Story』（2005）収録</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>2005〜2006 年・6〜7 歳。Napier で父の現場のトラックの CD で毎日流れていた。</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>2005 年ごろ、父が現場のトラックでずっと流していたニュージーランドのバンドの曲。拍の後ろにゆったり座るグルーヴと、急がないことの強さ。</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>スネアの 2 拍 4 拍をわずかに遅らせて座らせる叩き方と、テンポを上げずに盛り上げるサビ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Weather With You</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Crowded House</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Woodface』（1991）収録</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>2012 年 1 月・13 歳。移住の日に Napier から空港へ向かう車で母がかけた。</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>移住の日、Napier から空港へ向かう車で母がかけた曲。故郷を離れても天気は連れていける、という気持ちと、男声のハーモニーの重ね方。</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>タヴのコーラスの低いユニゾンの重ね方と、離れることを明るい長調で歌う曲への好み。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Dean Town</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Vulfpeck</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『The Beautiful Game』（2016）収録・演奏動画</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>2017 年・18 歳。学部 1 年の製図室で、自分のノートパソコンでキノとビアに見せた。</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>大学 1 年のとき、製図室でキノとビアに見せた演奏動画。最小の編成でベースとドラムが曲の骨組みになれること。</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>ギターとベースのユニゾンのリフにドラムがキメで合わせる間奏と、ベースとドラムだけで始まるイントロ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>Use Me</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>Bill Withers</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>アルバム『Still Bill』（1972）収録</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>2013 年・14 歳。Frankston の中等学校のステージバンドの先生が『少ない音で揺らせ』とグルーヴの宿題に出した。</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I59" s="12" t="inlineStr">
         <is>
           <t>同じ短いパターンを繰り返し、強弱だけで揺らすドラム。歌の隙間を埋めない伴奏。</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J59" s="12" t="inlineStr">
         <is>
           <t>A メロで同じ 2 小節を変えずに繰り返し、ハイハットの開け閉めと強弱だけで展開を作る叩き方。フィルを 1 拍以内に収める癖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>映画</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Boy（2010）</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Taika Waititi</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>2010 年のニュージーランド映画</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>2010 年・11 歳。Napier の映画館で家族全員で観た。</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>11 歳のとき、Napier の映画館で家族全員で観た。ニュージーランドの田舎の暮らしを、悲しい話でも笑いながら描くやり方。</t>
-        </is>
-      </c>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>ライブの MC で悲しい話も笑いながら短く話すタヴの話し方と、動画の字幕の素朴なユーモア。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="38" t="inlineStr">
-        <is>
-          <t>soft_cantilever</t>
-        </is>
-      </c>
-      <c r="B48" s="27" t="inlineStr">
-        <is>
-          <t>tav</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Shop Class as Soulcraft（2009）</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Matthew B. Crawford</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>2009 年刊のアメリカの哲学者の本</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>2021 年・22 歳。父が腰を痛めて代わりに現場に出ていたころ、見習いになるか迷って読んだ。</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>修士を出て見習いになるか迷っていた 2021 年に読んだ。手で作る仕事に頭も誇りも要るという考えが、背中を押した。</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>機材ケースや物販の棚や自作のスネアを自分の手で作ること。演奏でも見せる技より持ちこたえる確かさを選ぶ姿勢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Woodface</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Crowded House</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Woodface』（1991）。とくに 5 曲目『Weather With You』と 7 曲目『Four Seasons in One Day』のフィン兄弟の 2 声</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>2000 年前後（4〜6 歳）・オタゴの牧場で父の車のカセットを繰り返し聴いた。砂利道を走る 1 時間、兄と後部座席でハモりの真似をした。</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>父の車のカセット。オタゴの砂利道を 1 時間走るあいだ、兄と後部座席でハモりの真似をした。兄弟の声が重なる気持ちよさと、自分の国の人が作った歌が世界で鳴るという実感。</t>
-        </is>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>上のハモりを主旋律の 3 度上にぴたりと平行に付ける癖。A メロを 1 人で低く語り、サビで 2 声が開く曲の形。天気を気持ちの比喩にしても重くしない歌詞の温度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Submarine Bells</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>The Chills</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Submarine Bells』（1990）。1 曲目の『Heavenly Pop Hit』</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>2009 年頃（14 歳）・ダニーデンの寄宿学校で、ギターを教えてくれた上級生が CD を貸してくれた。</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>ダニーデンの寄宿学校の上級生が貸してくれた CD。坂と雨の多い自分たちの街から生まれた、少し陰りのある明るいギターの音。自分の町の天気を歌っていいと知った。</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>長調の明るい刻みの中に 1 つだけ陰る和音を置く感覚。歌詞に坂や雨や霜など自分の町の天気をそのまま書き込むこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>Time (The Revelator)</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Gillian Welch</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Time (The Revelator)』（2001）。3 曲目の『Dear Someone』</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>2014 年の夏（19 歳）・南島の牧場を回る毛刈り隊の宿舎で、先輩がスマートフォンで流してくれた。</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>大学時代、毛刈り隊の先輩に教わったアルバム。男女 2 人だけで声とギターを重ねる最小の編成と、言葉を急がない歌い方。</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>2 人だけの声とギターを基本の編成にする考え方。言葉を拍の少し後ろに置いて急がない歌い方。ギター 1 本で隙間を残す伴奏。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>Here's the Tender Coming</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>The Unthanks</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Here's the Tender Coming』（2009）。伝承歌の表題曲</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
-          <t>2018 年 5 月（23 歳）・ペンリンの毛糸店で働き始めた週に、店主が店の CD プレーヤーで流していた。</t>
-        </is>
-      </c>
-      <c r="I52" s="12" t="inlineStr">
-        <is>
-          <t>北イングランドの姉妹が、漁や港の暮らしの伝承歌を少ない伴奏で歌うアルバム。姉妹の声の溶け方と、自分の訛りを隠さずに歌っていいこと。海の仕事を、陸で待つ女性の目線で歌う距離。</t>
-        </is>
-      </c>
-      <c r="J52" s="12" t="inlineStr">
-        <is>
-          <t>ニュージーランドの母音を直さずに歌うこと。1 枚に 1 曲は無伴奏の歌い出しを入れること。漁師やギグの漕ぎ手の暮らしを、少し離れて見つめる歌詞の目線。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>本</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>To the Is-Land</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>Janet Frame</t>
-        </is>
-      </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>自伝 3 部作の第 1 巻『To the Is-Land』（1982）</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
-          <t>2010 年頃（15 歳）・ダニーデンの寄宿学校の図書室で、消灯前に少しずつ読んだ。</t>
-        </is>
-      </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>オタゴの町で育った作家の自伝。寄宿学校の図書室で読み、貧しさや田舎の暮らしの中にこそ言葉の豊かさがあると知った。自分の土地にも書くことがあると思えた。</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>地名や家の物を恥ずかしがらずに歌詞へ入れること。失敗や貧しさを飾らず、出来事だけで書く語り口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B54" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>絵</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>セントラル・オタゴの風景画（マニオトト平原を描いた作品群）</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Grahame Sydney</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>マニオトト平原を描いたテンペラ画の複製（『July on the Maniototo』など）</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>物心ついた頃から・実家の居間の壁に母が掛けていた複製画。</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>実家の居間にあった複製画。何もない平原と高い空と、ぽつんと立つ小屋。余白を怖がらないことを受け取った。</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="inlineStr">
-        <is>
-          <t>イントロとアウトロに音を詰めない余白。ジャケットや写真で上 2/3 を空や壁の余白にする構図。景色を描きすぎず小屋 1 つで語る歌詞。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B55" s="27" t="inlineStr">
-        <is>
-          <t>isla</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>言葉</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>Knit on with confidence and hope, through all crises.</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Elizabeth Zimmermann</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>アメリカの編み物作家の座右の言葉として、編み手のあいだで広く知られる一文</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>2002 年の冬休み（7 歳）・ダニーデンの祖母の家で編み物を習ったとき、本の見返しの書き写しを見た。意味が身に染みたのは腱鞘炎の 2023 年の冬。</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>祖母が編み物の本の見返しに書き写していた一文。手を動かし続ければ、困ったときもなんとかなる。腱鞘炎の冬にも何度も読み返した。</t>
-        </is>
-      </c>
-      <c r="J55" s="12" t="inlineStr">
-        <is>
-          <t>つらい出来事を歌う曲でも、最後の行を『編み始める』のような手の動作で前へ向けて終える歌詞の癖。配信の終わりの挨拶。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B56" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Ysbryd Solva</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Meic Stevens</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Ysbryd Solva』（2002・ウェールズ語）</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>2002 年の夏（12 歳）・地元セント・デイヴィッズで全国アイステズヴォッドが開かれた年に、父が買ってきた。</t>
-        </is>
-      </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>同じソルヴァ生まれの歌い手が、2002 年に村での子ども時代を歌ったアルバム。12 歳のとき父が買ってきた。自分の港の名前が歌になる誇りと、ウェールズ語の歌の柔らかい子音。</t>
-        </is>
-      </c>
-      <c r="J56" s="12" t="inlineStr">
-        <is>
-          <t>ウェールズ語の柔らかい子音の発音を英語の歌詞にも持ち込む下ハモの声。港の名前や道路の番号をそのまま歌に入れる勇気。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Solid Air</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>John Martyn</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Solid Air』（1973）。1 曲目の表題曲と、テープ・ディレイで指弾きを揺らした 4 曲目『I'd Rather Be the Devil』</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>1990 年代半ば（5 歳頃から）・ソルヴァの父の作業場のレコードプレーヤーで、鉋屑を掃きながら聴いた。</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>父が作業場で鉋をかけながら回していたレコード。指弾きのギターが波のように反復して揺れる感じと、声を楽器のように滲ませる歌い方。</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>親指の低音の反復を崩さず、その上で和音を波のように揺らす指弾きの型。語尾を滲ませて楽器に溶かす下ハモの歌い方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Damien Rice</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『O』（2002）。2 曲目『Volcano』の男女の声の掛け合い</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>2004 年（14 歳）・初めてのギターを買った頃、セント・デイヴィッズの中等学校のバンド仲間に CD を借りた。</t>
-        </is>
-      </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>14 歳でギターを買った頃に聴き込んだアルバム。男女の声が小さな部屋で寄り添う距離感と、静かな曲でも熱が伝わること。</t>
-        </is>
-      </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>ブリッジで楽器が抜けて声 2 人と持続音だけになる曲の形。マイクに近づいて小さな声で歌う録り方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>tidewool</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>gethin</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>音楽</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>Penguin Eggs</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Nic Jones</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>アルバム『Penguin Eggs』（1980）。1 曲目『Canadee-I-O』と 3 曲目『The Humpback Whale』</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>2016 年の冬（26 歳）・木曜のパブのセッションに通い始めた頃、仕切り役の 70 代のアコーディオン弾きに『港の歌をやるならこれを聴け』とレコードを渡された。</t>
-        </is>
-      </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>指弾きの親指が打楽器のように弦を叩く推進力と、変則チューニングで開放弦を鳴らし続ける和音。海と鯨と漁の伝承歌を、感情を足さずに淡々と語る歌い方。</t>
-        </is>
-      </c>
-      <c r="J59" s="12" t="inlineStr">
-        <is>
-          <t>右手の親指で低音弦を短く弾いて打楽器の代わりにする奏法。D を基にした変則チューニングで開放弦を鳴らし続ける伴奏。ゲシンのパートの、出来事だけを語る伝承歌のような歌詞。</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>gethin</t>
+          <t>isla</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -19785,37 +19785,37 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Under Milk Wood</t>
+          <t>Here's the Tender Coming</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Dylan Thomas</t>
+          <t>The Unthanks</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>声の劇『Under Milk Wood』。1954 年 1 月に BBC で初めて放送された Richard Burton が語り手の録音</t>
+          <t>アルバム『Here's the Tender Coming』（2009）。伝承歌の表題曲</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>子どもの頃（1990 年代）から毎年冬・ソルヴァの台所で母が流していた。</t>
+          <t>2018 年 5 月（23 歳）・ペンリンの毛糸店で働き始めた週に、店主が店の CD プレーヤーで流していた。</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>母が毎年冬に朗読の録音を流していた、ウェールズの小さな漁村の一日を描く声の劇。村の一人ひとりの暮らしの細部を、音と言葉の響きで描く書き方。</t>
+          <t>北イングランドの姉妹が、漁や港の暮らしの伝承歌を少ない伴奏で歌うアルバム。姉妹の声の溶け方と、自分の訛りを隠さずに歌っていいこと。海の仕事を、陸で待つ女性の目線で歌う距離。</t>
         </is>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>ゲシンが書き換える 2〜3 行に多い、港の人の小さな動作を並べる書き方。意味より子音の響きで言葉を選ぶ癖。</t>
+          <t>ニュージーランドの母音を直さずに歌うこと。1 枚に 1 曲は無伴奏の歌い出しを入れること。漁師やギグの漕ぎ手の暮らしを、少し離れて見つめる歌詞の目線。</t>
         </is>
       </c>
     </row>
@@ -19837,37 +19837,37 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>言葉</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>I have seen the sun break through / to illuminate a small field / for a while, and gone my way / and forgotten it.（The Bright Field）</t>
+          <t>Penguin Eggs</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>R. S. Thomas</t>
+          <t>Nic Jones</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>詩『The Bright Field』（詩集『Laboratories of the Spirit』1975 年）</t>
+          <t>アルバム『Penguin Eggs』（1980）。1 曲目『Canadee-I-O』と 3 曲目『The Humpback Whale』</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>2011 年（21 歳）・ファルマスの専門学校に通っていた頃、町の図書館で借りた詩集で。</t>
+          <t>2016 年の冬（26 歳）・木曜のパブのセッションに通い始めた頃、仕切り役の 70 代のアコーディオン弾きに『港の歌をやるならこれを聴け』とレコードを渡された。</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>専門学校の頃、ウェールズの詩人の詩集で出会った一節。ほんの短い光を見過ごさずに立ち止まること。急がない仕事の理由になった。</t>
+          <t>指弾きの親指が打楽器のように弦を叩く推進力と、変則チューニングで開放弦を鳴らし続ける和音。海と鯨と漁の伝承歌を、感情を足さずに淡々と語る歌い方。</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>サビの手前で 1 小節だけ立ち止まってハミングする曲の習慣。速くしたがるアイラに対して、遅いテンポを選ぶ理由。</t>
+          <t>右手の親指で低音弦を短く弾いて打楽器の代わりにする奏法。D を基にした変則チューニングで開放弦を鳴らし続ける伴奏。ゲシンのパートの、出来事だけを語る伝承歌のような歌詞。</t>
         </is>
       </c>
     </row>

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>本名デクラン・トゥーミー。幼少期の頃、町で小さな発表会があったときに母のピアノに合わせて歌を披露し喝采を浴びた時のホームビデオで撮影していた父が「まるで妖精のようだ」と言っていた場面からFay（妖精の意）を掛け合わせた。。トロントのラジオ局で深夜の小さな番組のパーソナリティーを務めていた際に「夜の癒ややし担当＝Fay」深夜の小さな番組のパーソナリティーを務めていた際にとして、リスナーの間からあだ名でそう呼ばれていた。</t>
+          <t>本名デクラン・トゥーミー。幼い頃、町の小さな発表会で母のピアノに合わせて歌い拍手を浴びたとき、ホームビデオを撮っていた父が『まるで妖精のようだ』と言った。その場面から Fay（妖精の意）を名前に掛け合わせた。トロントのラジオ局で深夜の小さな番組のパーソナリティーを務めていた頃、リスナーの間で『夜の癒やし担当＝Fay』というあだ名で呼ばれていたことも重なっている。</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -6949,7 +6949,11 @@
           <t>性別</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>女性</t>
@@ -6977,7 +6981,11 @@
           <t>生年月日（現在の年齢）</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>1993-02-04（33 歳）</t>
+        </is>
+      </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
           <t>1997-03-11（29 歳）</t>
@@ -7005,7 +7013,11 @@
           <t>曲で使用するメインの楽器</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>アナログ・ポリシンセのパッドとアルペジオ、1980 年代のドラムマシン（ゲートのかかったスネア）、低く温かいバリトンの声</t>
+        </is>
+      </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
           <t>1970 年代のエレクトリックピアノ（9th と 11th の和音）、サンプラーで切って並べた息と声の切れ端、柔らかい四つ打ちのドラム、丸いサブベース</t>
@@ -7423,7 +7435,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>本人。局の古い制作室と自宅の窓際の机で、4 つの和音のパッドを先に決め、ベースとアルペジオを重ねる。メロディは運転中の鼻歌をスマートフォンに録って拾う。祖父のテープのヒスや車内の音を薄く混ぜて仕上げる。</t>
+          <t>本人。局の古い制作室と自宅の窓際の机で、4 つの和音のパッドを先に決め、ベースとアルペジオを重ねる。メロディは運転中の鼻歌をスマートフォンに録って拾う。父が残したテープのヒスや車内の音を薄く混ぜて仕上げる。</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -7563,7 +7575,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>トロントに来て 10 年目の秋。週 4 日、19 時から 3 時まで局の送出卓に座り、帰りにガーディナーを走ってから、金曜と土曜は 4 時過ぎにイネスをパン屋まで送る。昼に眠り午後に起きる暮らしには慣れたが、時差のせいでコークの家族と話せる時間は短く、父が朝 7 時に撮って送ってくる空の写真を深夜 2 時の休憩に見るのが日課になっている。祖父の 43 本のテープはすべてデジタルにし終え、そこから拾った音を曲に混ぜている。最初のシングルを出すと決め、毎晩の休憩に歌詞を 1 行ずつ直している。</t>
+          <t>トロントに来て 10 年目の秋。週 4 日、19 時から 3 時まで局の送出卓に座り、帰りにガーディナーを走ってから、金曜と土曜は 4 時過ぎにイネスをパン屋まで送る。昼に眠り午後に起きる暮らしには慣れたが、時差のせいでコークの家族と話せる時間は短く、母が朝 7 時に撮って送ってくる空の写真を深夜 2 時の休憩に見るのが日課になっている。父が残した 43 本のテープはすべてデジタルにし終え、そこから拾った音を曲に混ぜている。最初のシングルを出すと決め、毎晩の休憩に歌詞を 1 行ずつ直している。</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -7639,7 +7651,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>DECLAN MOTH is Declan Twomey, a Cork-born baritone who has spent ten years working nights in Toronto — first driving a bakery van at 2 a.m., now running the overnight desk at a small community radio station. As a boy who wouldn't sleep, he rode along on his grandfather's late drives around Cork's ring road, a box of cassettes taped off late-night radio at his feet; when his grandfather died, those 43 tapes crossed the Atlantic in a shoebox, and their hiss is still in every mix. His songs are slow, warm synthwave for the stretch between last call and first light: analog pads, a gated snare, a voice that sounds like it's riding in the passenger seat, and always a time on the clock. Put it on when you're driving home and everyone else is asleep.</t>
+          <t>DECLAN FAY is Declan Twomey, a Cork-born baritone who has spent ten years working nights in Toronto — first driving a newspaper delivery van at 2 a.m., now running the overnight desk at a small community radio station. His father drove a taxi through Cork's late hours and taped the radio as he went; he died when Declan was nine, and nineteen years later those 43 cassettes crossed the Atlantic in a shoebox. Their hiss is still in every mix. The name came to him twice: once from his father's voice on an old home video, and again from the night-shift listeners who started calling him their Fay. His songs are slow, warm synthwave for the stretch between last call and first light: analog pads, a gated snare, a voice that sounds like it's riding in the passenger seat, and always a time on the clock. Put it on when you're driving home and everyone else is asleep.</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -7683,7 +7695,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>テーマの軸は『時間の手触り』（夜勤の時刻・5 時間の時差・カセット）。80 年代の再現ではなく、今の夜を 80 年代の質感で歌う。顔出しなし。本名は設定の中だけで使い、配信名は DECLAN MOTH。</t>
+          <t>テーマの中心は『時間の手触り』（夜勤の時刻・5 時間の時差・カセット）。80 年代の再現ではなく、今の夜を 80 年代の質感で歌う。顔出しなし。本名は設定の中だけで使い、配信名は DECLAN FAY。</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -7817,7 +7829,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -10203,7 +10215,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="13" t="n">
@@ -10261,7 +10273,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
@@ -10319,7 +10331,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
@@ -10373,7 +10385,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -10427,7 +10439,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D6" s="13" t="n">
@@ -10485,7 +10497,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D7" s="13" t="n">
@@ -10543,7 +10555,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D8" s="13" t="n">
@@ -10601,7 +10613,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D9" s="13" t="n">
@@ -10659,7 +10671,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D10" s="13" t="n">
@@ -10717,7 +10729,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
@@ -10775,7 +10787,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D12" s="13" t="n">
@@ -10833,7 +10845,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D13" s="13" t="n">
@@ -10887,7 +10899,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D14" s="13" t="n">
@@ -14923,7 +14935,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -14960,7 +14972,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -14997,7 +15009,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -15034,7 +15046,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -15071,7 +15083,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -16044,7 +16056,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -16086,7 +16098,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -16764,7 +16776,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -16816,7 +16828,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -16868,7 +16880,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -16920,7 +16932,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -16972,7 +16984,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -17024,7 +17036,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -19104,7 +19116,7 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -19156,7 +19168,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -20006,7 +20018,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="27" t="inlineStr">
@@ -20053,7 +20065,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
@@ -20100,7 +20112,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
@@ -20147,7 +20159,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -20194,7 +20206,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -20241,7 +20253,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -20288,7 +20300,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -20335,7 +20347,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -20382,7 +20394,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -22091,7 +22103,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C2" s="27" t="inlineStr">
@@ -22134,7 +22146,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -3736,22 +3736,22 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
     </row>
@@ -5437,22 +5437,22 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
     </row>
@@ -6752,22 +6752,22 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
     </row>
@@ -7834,37 +7834,37 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D16" s="13" t="n">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D24" s="13" t="n">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D26" s="13" t="n">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D28" s="13" t="n">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D30" s="13" t="n">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D32" s="13" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D33" s="13" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D34" s="13" t="n">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D35" s="13" t="n">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D36" s="13" t="n">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D37" s="13" t="n">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D38" s="13" t="n">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D44" s="13" t="n">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D45" s="13" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D46" s="13" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D47" s="13" t="n">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D48" s="13" t="n">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D50" s="13" t="n">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D51" s="13" t="n">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D52" s="13" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D53" s="13" t="n">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D54" s="13" t="n">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D55" s="13" t="n">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D56" s="13" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D57" s="13" t="n">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D58" s="13" t="n">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D59" s="13" t="n">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D60" s="13" t="n">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D61" s="13" t="n">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D62" s="13" t="n">
@@ -13685,7 +13685,7 @@
       <c r="B63" s="27" t="inlineStr"/>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D63" s="13" t="n">
@@ -13739,7 +13739,7 @@
       <c r="B64" s="27" t="inlineStr"/>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D64" s="13" t="n">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D65" s="13" t="n">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D66" s="13" t="n">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D67" s="13" t="n">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D68" s="13" t="n">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D69" s="13" t="n">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D70" s="13" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D71" s="13" t="n">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D72" s="13" t="n">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D73" s="13" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D74" s="13" t="n">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D75" s="13" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D76" s="13" t="n">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D77" s="13" t="n">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D78" s="13" t="n">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D79" s="13" t="n">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D80" s="13" t="n">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D81" s="13" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D82" s="13" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -20864,7 +20864,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -21240,7 +21240,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -21569,7 +21569,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -21616,7 +21616,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
@@ -21804,7 +21804,7 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -22357,7 +22357,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -6924,22 +6924,22 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>本体</t>
+          <t>Postdog Records</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>本体</t>
+          <t>Postdog Records</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>本体</t>
+          <t>Postdog Records</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>本体</t>
+          <t>Postdog Records</t>
         </is>
       </c>
     </row>

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -5322,7 +5322,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>相手の曲に 3 人のバンド演奏で入る（生のベースとドラムを足し、ビアのハモりを重ねる）。NAO EASTERLY とは朝の東行きから昼のハイウェイへ続く 2 部作、HOLLOWPLAN にはベースとドラムの素材を渡して長距離区間のつなぎに組み直してもらう。</t>
+          <t>相手の曲に 3 人のバンド演奏で入る（生のベースとドラムを足し、ビアのハモりを重ねる）。VERNALIGHT とは朝の東行きから昼のハイウェイへ続く 2 部作、HOLLOWPLAN にはベースとドラムの素材を渡して長距離区間のつなぎに組み直してもらう。</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D1" s="22" t="inlineStr">
         <is>
-          <t>NAO EASTERLY</t>
+          <t>VERNALIGHT</t>
         </is>
       </c>
       <c r="E1" s="23" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>ナオ・イースタリー</t>
+          <t>ヴァーナライト</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Easterly は英語で「東から吹く風」と「東へ向かう」の両方を指す。冬にコロンビア川の峡谷からポートランドへ吹き出す東風は冷たく乾いていて、決まって澄んだ晴れの朝を連れてくる。春分（太陽が真東から昇る日）に生まれ、毎朝東へ走る本人が、本名の Harlan より方角の名前のほうが自分に近いと感じて付けた。</t>
+          <t>vernal（春の・春分の）と light（光）をつなげた造語。春分は太陽が真東から昇る日で、本人はその日の明け方に生まれた。毎朝東へ走り、配送ルートの終わりで日の出を迎える本人が、本名の Harlan より、自分が生まれた朝の光の名前のほうが自分に近いと感じて付けた。冬にコロンビア川の峡谷から吹き出す東風が連れてくる、澄んだ晴れの朝の光でもある。</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Nao Easterly grew up between the pear orchards of Hood River, Oregon, and her grandmother's harbor town of Hakodate, Japan. Her first sunrise was seen from the passenger seat of her father's snowplow pickup, a thermos of cocoa between her knees, and she has been waking before dawn ever since. Now she drives a bakery delivery van through Portland at 3:30 a.m. and writes bright, clear-voiced synth-pop about the hour when only the early shift is awake. Her songs end where her route does: eastbound on the interstate, right as the sun comes up.</t>
+          <t>VERNALIGHT is the solo project of Nao, who grew up between the pear orchards of Hood River, Oregon, and her grandmother's harbor town of Hakodate, Japan. She was born at dawn on the spring equinox, one of the two mornings a year the sun rises due east, and the name is for that light. The first sunrise she remembers was seen from the passenger seat of her father's snowplow pickup, a thermos of cocoa between her knees, and she has been waking before dawn ever since. Now she drives a bakery delivery van through Portland at 3:30 a.m. and writes bright, clear-voiced synth-pop about the hour when only the early shift is awake. Her songs end where her route does: eastbound on the interstate, right as the sun comes up.</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>本名は Nao Kudo Harlan（日本の戸籍名は工藤奈央）。日米の二重国籍で、日本の国籍をどうするかの届けは書いたまま引き出しにしまってある。顔は出さないが、手元・後ろ姿・車内は毎回同じ人として撮る。投稿と配信は日本時間とアメリカ時間それぞれの朝 6 時に合わせる。</t>
+          <t>本名は Nao Kudo Harlan（日本の戸籍名は工藤奈央）。日米の二重国籍で、日本の国籍をどうするかの届けは書いたまま引き出しにしまってある。顔は出さないが、手元・後ろ姿・車内は毎回同じ人として撮る。投稿と配信は日本時間とアメリカ時間それぞれの朝 6 時に合わせる。旧名 NAO EASTERLY（2026-10-13 に改名。イギリスの歌手「NAO」と検索で並ぶのを避けるため。VERNALIGHT は Web 検索で同じ名前なし）。</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D1" s="22" t="inlineStr">
         <is>
-          <t>Nao Easterly（ナオ・イースタリー）／本名 Nao Kudo Harlan（工藤奈央）</t>
+          <t>Nao（ナオ）／本名 Nao Kudo Harlan（工藤奈央）</t>
         </is>
       </c>
       <c r="E1" s="23" t="inlineStr">

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -21,6 +21,7 @@
     <sheet name="声と曲づくり" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="見た目" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="変更の提案" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="詰まっているところ" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人生年表'!$A$1:$L$82</definedName>
@@ -40,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +113,12 @@
       <b val="1"/>
       <color rgb="001F4E99"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -225,8 +230,38 @@
         <fgColor rgb="00EFEDE8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F3B4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEFD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3EEF9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -242,11 +277,25 @@
         <color rgb="00D9D6CF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -384,6 +433,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6689,6 +6759,572 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>順番</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="inlineStr">
+        <is>
+          <t>詰まっていること</t>
+        </is>
+      </c>
+      <c r="C1" s="56" t="inlineStr">
+        <is>
+          <t>なぜ必要か</t>
+        </is>
+      </c>
+      <c r="D1" s="56" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E1" s="56" t="inlineStr">
+        <is>
+          <t>次の一歩</t>
+        </is>
+      </c>
+      <c r="F1" s="56" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="G1" s="56" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="57" t="inlineStr">
+        <is>
+          <t>Suno のプランの確認</t>
+        </is>
+      </c>
+      <c r="C2" s="57" t="inlineStr">
+        <is>
+          <t>配信に使えるのは Pro か Premier のプランで作った曲だけ</t>
+        </is>
+      </c>
+      <c r="D2" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E2" s="57" t="inlineStr">
+        <is>
+          <t>Suno の設定画面で今のプランを確かめる</t>
+        </is>
+      </c>
+      <c r="F2" s="58" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G2" s="57" t="inlineStr">
+        <is>
+          <t>Pro プラン（2026-10-13 確認）。作った曲は配信に使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="57" t="inlineStr">
+        <is>
+          <t>DistroKid のプランの確認</t>
+        </is>
+      </c>
+      <c r="C3" s="57" t="inlineStr">
+        <is>
+          <t>5 組ぶんのアーティスト名を使うため、名前を 5 つ以上持てるプランが要る</t>
+        </is>
+      </c>
+      <c r="D3" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E3" s="57" t="inlineStr">
+        <is>
+          <t>DistroKid の Account／Upgrade のページで確かめる</t>
+        </is>
+      </c>
+      <c r="F3" s="58" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G3" s="57" t="inlineStr">
+        <is>
+          <t>Ultimate（アーティスト名 5 つ）に加入中（2026-10-13 確認）。新しい組を足すときは、その前に名前の数が多い段へ上げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="57" t="inlineStr">
+        <is>
+          <t>名前の重複確認（Postdog Records と 5 組）</t>
+        </is>
+      </c>
+      <c r="C4" s="57" t="inlineStr">
+        <is>
+          <t>同じ名前がすでにあると、別人のページに曲が混ざる</t>
+        </is>
+      </c>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E4" s="57" t="inlineStr">
+        <is>
+          <t>これから新しく付ける名前は、私が先に Web 検索（Spotify・Bandcamp・SoundCloud を含む）で同じ名前がないか確かめてからお見せする</t>
+        </is>
+      </c>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-13 オーナーが Spotify で確認：6 つとも同じ名前なし。同日 NAO EASTERLY を VERNALIGHT に改名。今の 5 組：DECLAN FAY・HOLLOWPLAN・VERNALIGHT・SOFT CANTILEVER・TIDEWOOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>Suno で 5 曲を作る</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>配信する音源そのもの</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>作業書の PDR-001 から順に、1 曲 2〜4 テイク</t>
+        </is>
+      </c>
+      <c r="F5" s="59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G5" s="57" t="inlineStr">
+        <is>
+          <t>作業書：SSD の 管理表/作業書_デビュー5曲.pdf（Google ドキュメントからの書き出し）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="inlineStr">
+        <is>
+          <t>ジャケットとアーティスト写真（自動）</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="inlineStr">
+        <is>
+          <t>配信と各サービスのプロフィールに必要</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="inlineStr">
+        <is>
+          <t>Mac で python3 scripts/kit_images.py。画像は SSD の アーティスト情報/&lt;アーティスト名&gt;/写真・ジャケット に自動で入る</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>いま確認中</t>
+        </is>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-13 OpenAI の鍵を登録・接続確認済み。写真は人物が主役・目元を隠す（決定 10・11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="inlineStr">
+        <is>
+          <t>テイクを選ぶ</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>出す 1 本を決める</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>作業書の「聴いて選ぶ基準」で 1 本ずつ選び、WAV で保存</t>
+        </is>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G7" s="57" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="inlineStr">
+        <is>
+          <t>DistroKid に登録</t>
+        </is>
+      </c>
+      <c r="C8" s="57" t="inlineStr">
+        <is>
+          <t>公開の予約</t>
+        </is>
+      </c>
+      <c r="D8" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E8" s="57" t="inlineStr">
+        <is>
+          <t>作業書の表どおりに入力。公開日はいちばん早い日</t>
+        </is>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G8" s="57" t="inlineStr">
+        <is>
+          <t>作詞作曲者の欄は本名</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="inlineStr">
+        <is>
+          <t>配信後の記録</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="inlineStr">
+        <is>
+          <t>管理表と配信の予定を合わせる</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="inlineStr">
+        <is>
+          <t>DistroKid の ISRC と選んだテイクを教える</t>
+        </is>
+      </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G9" s="57" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>10 月 28 日の自動配信枠の調整</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="inlineStr">
+        <is>
+          <t>デビューの 5 曲と重ならないようにする</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>私</t>
+        </is>
+      </c>
+      <c r="E10" s="57" t="inlineStr">
+        <is>
+          <t>デビューの 5 曲が出たら、その枠を 2 曲目として作り直す</t>
+        </is>
+      </c>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>待ち</t>
+        </is>
+      </c>
+      <c r="G10" s="57" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="57" t="inlineStr">
+        <is>
+          <t>参考曲の購入と解析（11 曲以上）</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="inlineStr">
+        <is>
+          <t>毎週の自動制作が参考曲の特徴を使う</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E11" s="57" t="inlineStr">
+        <is>
+          <t>「参考曲の候補」タブの曲から購入し、music-label/out/references/ に置く</t>
+        </is>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G11" s="57" t="inlineStr">
+        <is>
+          <t>デビューには不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="57" t="inlineStr">
+        <is>
+          <t>自動化の鍵の設定</t>
+        </is>
+      </c>
+      <c r="C12" s="57" t="inlineStr">
+        <is>
+          <t>毎週の制作と配信を自動で回すため</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E12" s="57" t="inlineStr">
+        <is>
+          <t>Mac で python3 scripts/setup_keys.py</t>
+        </is>
+      </c>
+      <c r="F12" s="62" t="inlineStr">
+        <is>
+          <t>一部完了</t>
+        </is>
+      </c>
+      <c r="G12" s="57" t="inlineStr">
+        <is>
+          <t>OpenAI の鍵は登録・接続確認済み（2026-10-13）。ほかの鍵はデビューには不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>作業を Mac に移す</t>
+        </is>
+      </c>
+      <c r="C13" s="57" t="inlineStr">
+        <is>
+          <t>画像の生成・毎週の自動実行・音源と画像の受け渡しのため</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="E13" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G13" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-13 Mac のターミナルで動いている</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>毎週の自動の流れの試験</t>
+        </is>
+      </c>
+      <c r="C14" s="57" t="inlineStr">
+        <is>
+          <t>ブリーフからジャケット・登録シート・SNS の準備までを毎週自動で回すため</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>Mac で python3 scripts/trial.py --all --skip-youtube --cleanup-after → ✕ 0 件なら python3 scripts/schedule.py install</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>いま確認中</t>
+        </is>
+      </c>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-14 クラウド（鍵なし）で 5 組とも ✕ 0 件。Suno と DistroKid は規約で自動操作が禁止なので人の作業のまま</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>管理表と素材を SSD（DS72）に移す</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="inlineStr">
+        <is>
+          <t>アーティストの情報・写真・ジャケット・楽曲を物理的に手元で保管するため</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
+        <is>
+          <t>あなた → 私</t>
+        </is>
+      </c>
+      <c r="E15" s="57" t="inlineStr">
+        <is>
+          <t>SSD をつないで python3 scripts/archive_sync.py --check → python3 scripts/archive_sync.py。Google のシート・ドキュメント・ドライブの画像はオーナーが移す</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>いま確認中</t>
+        </is>
+      </c>
+      <c r="G15" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-14 決定 13・14。管理表の正本は SSD の 管理表/アーティスト情報.xlsx（このファイル）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7742,7 +8378,7 @@
       <formula1>"ソロ,デュオ,バンド,ボーカルグループ,プロデューサー"</formula1>
     </dataValidation>
     <dataValidation sqref="B8:Z8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
-      <formula1>"本体,sleep,morning,focus,move"</formula1>
+      <formula1>"Postdog Records,sleep,morning,focus,move"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:Z2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選べる値" error="一覧から選んでください（空欄も可）" type="list">
       <formula1>"提案,採用,保留,却下,反映済み"</formula1>

--- a/music-label/artists.xlsx
+++ b/music-label/artists.xlsx
@@ -6948,7 +6948,7 @@
       </c>
       <c r="E5" s="57" t="inlineStr">
         <is>
-          <t>作業書の PDR-001 から順に、1 曲 2〜4 テイク</t>
+          <t>python3 scripts/publish.py suno --open のページから Suno に貼って Create（押すのはあなた）</t>
         </is>
       </c>
       <c r="F5" s="59" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="G5" s="57" t="inlineStr">
         <is>
-          <t>作業書：SSD の 管理表/作業書_デビュー5曲.pdf（Google ドキュメントからの書き出し）</t>
+          <t>決定 17。進み具合はダッシュボード（dashboard.py）で組ごとに見られる</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B7" s="57" t="inlineStr">
         <is>
-          <t>テイクを選ぶ</t>
+          <t>テイクを選ぶ（Suno のいいね）</t>
         </is>
       </c>
       <c r="C7" s="57" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="D7" s="57" t="inlineStr">
         <is>
-          <t>あなた</t>
+          <t>あなた → 自動</t>
         </is>
       </c>
       <c r="E7" s="57" t="inlineStr">
         <is>
-          <t>作業書の「聴いて選ぶ基準」で 1 本ずつ選び、WAV で保存</t>
+          <t>いいねした 1 本をダウンロードして「ダウンロード/SUNO楽曲」へ。そこから自動で取り込み・音量・公開セット</t>
         </is>
       </c>
       <c r="F7" s="59" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="D8" s="57" t="inlineStr">
         <is>
-          <t>あなた</t>
+          <t>Claude → あなた</t>
         </is>
       </c>
       <c r="E8" s="57" t="inlineStr">
         <is>
-          <t>作業書の表どおりに入力。公開日はいちばん早い日</t>
+          <t>通知が来たら Claude in Chrome をつなぐ → Claude が下書きを入れ、最後の登録ボタンはあなた</t>
         </is>
       </c>
       <c r="F8" s="59" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="D9" s="57" t="inlineStr">
         <is>
-          <t>あなた → 私</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="E9" s="57" t="inlineStr">
         <is>
-          <t>DistroKid の ISRC と選んだテイクを教える</t>
+          <t>自動：毎日 Spotify で配信を確かめ、ISRC・UPC・配信 URL を楽曲管理シートに入れる（Spotify の鍵が要る）</t>
         </is>
       </c>
       <c r="F9" s="59" t="inlineStr">
@@ -7130,10 +7130,14 @@
       </c>
       <c r="F10" s="61" t="inlineStr">
         <is>
-          <t>待ち</t>
-        </is>
-      </c>
-      <c r="G10" s="57" t="n"/>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G10" s="57" t="inlineStr">
+        <is>
+          <t>2026-10-16 決定 17：デビュー曲を登録するまで毎週の制作を止め、登録した配信週をデビュー週にする</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="57" t="inlineStr">
